--- a/excel/Заказы.xlsx
+++ b/excel/Заказы.xlsx
@@ -2022,7 +2022,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2070,6 +2070,12 @@
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12519,35 +12525,35 @@
       <c r="H2" s="10">
         <v>0.254</v>
       </c>
-      <c r="I2" s="12">
-        <v>1</v>
-      </c>
-      <c r="J2" s="12">
+      <c r="I2" s="17">
+        <v>1</v>
+      </c>
+      <c r="J2" s="17">
         <v>3</v>
       </c>
-      <c r="K2" s="12">
-        <v>7</v>
-      </c>
-      <c r="L2" s="12">
-        <v>1</v>
-      </c>
-      <c r="M2" s="12">
+      <c r="K2" s="17">
+        <v>7</v>
+      </c>
+      <c r="L2" s="17">
+        <v>1</v>
+      </c>
+      <c r="M2" s="17">
         <v>6</v>
       </c>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="13"/>
-      <c r="V2" s="13"/>
-      <c r="W2" s="12"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="12"/>
-      <c r="AA2" s="12"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="18"/>
+      <c r="V2" s="18"/>
+      <c r="W2" s="17"/>
+      <c r="X2" s="17"/>
+      <c r="Y2" s="17"/>
+      <c r="Z2" s="17"/>
+      <c r="AA2" s="17"/>
       <c r="AB2" s="13" t="s">
         <v>20</v>
       </c>
@@ -12583,35 +12589,35 @@
       <c r="H3" s="10">
         <v>0.254</v>
       </c>
-      <c r="I3" s="12">
-        <v>1</v>
-      </c>
-      <c r="J3" s="12">
-        <v>2</v>
-      </c>
-      <c r="K3" s="12">
-        <v>8</v>
-      </c>
-      <c r="L3" s="12">
+      <c r="I3" s="17">
+        <v>1</v>
+      </c>
+      <c r="J3" s="17">
+        <v>2</v>
+      </c>
+      <c r="K3" s="17">
+        <v>8</v>
+      </c>
+      <c r="L3" s="17">
         <v>4</v>
       </c>
-      <c r="M3" s="12">
-        <v>7</v>
-      </c>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="12"/>
-      <c r="S3" s="12"/>
-      <c r="T3" s="12"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="13"/>
-      <c r="W3" s="12"/>
-      <c r="X3" s="12"/>
-      <c r="Y3" s="12"/>
-      <c r="Z3" s="12"/>
-      <c r="AA3" s="12"/>
+      <c r="M3" s="17">
+        <v>7</v>
+      </c>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
+      <c r="U3" s="18"/>
+      <c r="V3" s="18"/>
+      <c r="W3" s="17"/>
+      <c r="X3" s="17"/>
+      <c r="Y3" s="17"/>
+      <c r="Z3" s="17"/>
+      <c r="AA3" s="17"/>
       <c r="AB3" s="13" t="s">
         <v>20</v>
       </c>
@@ -12647,31 +12653,31 @@
       <c r="H4" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I4" s="12">
-        <v>20</v>
-      </c>
-      <c r="J4" s="12">
+      <c r="I4" s="17">
+        <v>20</v>
+      </c>
+      <c r="J4" s="17">
         <v>6</v>
       </c>
-      <c r="K4" s="12">
-        <v>8</v>
-      </c>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="12"/>
-      <c r="T4" s="12"/>
-      <c r="U4" s="13"/>
-      <c r="V4" s="13"/>
-      <c r="W4" s="12"/>
-      <c r="X4" s="12"/>
-      <c r="Y4" s="12"/>
-      <c r="Z4" s="12"/>
-      <c r="AA4" s="12"/>
+      <c r="K4" s="17">
+        <v>8</v>
+      </c>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="17"/>
+      <c r="U4" s="18"/>
+      <c r="V4" s="18"/>
+      <c r="W4" s="17"/>
+      <c r="X4" s="17"/>
+      <c r="Y4" s="17"/>
+      <c r="Z4" s="17"/>
+      <c r="AA4" s="17"/>
       <c r="AB4" s="13" t="s">
         <v>20</v>
       </c>
@@ -12707,31 +12713,31 @@
       <c r="H5" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="17">
         <v>37</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="17">
         <v>4</v>
       </c>
-      <c r="K5" s="12">
-        <v>8</v>
-      </c>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="13"/>
-      <c r="V5" s="13"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="12"/>
-      <c r="Y5" s="12"/>
-      <c r="Z5" s="12"/>
-      <c r="AA5" s="12"/>
+      <c r="K5" s="17">
+        <v>8</v>
+      </c>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="18"/>
+      <c r="V5" s="18"/>
+      <c r="W5" s="17"/>
+      <c r="X5" s="17"/>
+      <c r="Y5" s="17"/>
+      <c r="Z5" s="17"/>
+      <c r="AA5" s="17"/>
       <c r="AB5" s="13" t="s">
         <v>20</v>
       </c>
@@ -12767,31 +12773,31 @@
       <c r="H6" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="17">
         <v>37</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="17">
         <v>4</v>
       </c>
-      <c r="K6" s="12">
-        <v>8</v>
-      </c>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="13"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="12"/>
-      <c r="Z6" s="12"/>
-      <c r="AA6" s="12"/>
+      <c r="K6" s="17">
+        <v>8</v>
+      </c>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="18"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="17"/>
+      <c r="Z6" s="17"/>
+      <c r="AA6" s="17"/>
       <c r="AB6" s="13" t="s">
         <v>20</v>
       </c>
@@ -12827,31 +12833,31 @@
       <c r="H7" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="17">
         <v>5</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="17">
         <v>6</v>
       </c>
-      <c r="K7" s="12">
-        <v>8</v>
-      </c>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="13"/>
-      <c r="V7" s="13"/>
-      <c r="W7" s="12"/>
-      <c r="X7" s="12"/>
-      <c r="Y7" s="12"/>
-      <c r="Z7" s="12"/>
-      <c r="AA7" s="12"/>
+      <c r="K7" s="17">
+        <v>8</v>
+      </c>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="17"/>
+      <c r="T7" s="17"/>
+      <c r="U7" s="18"/>
+      <c r="V7" s="18"/>
+      <c r="W7" s="17"/>
+      <c r="X7" s="17"/>
+      <c r="Y7" s="17"/>
+      <c r="Z7" s="17"/>
+      <c r="AA7" s="17"/>
       <c r="AB7" s="13" t="s">
         <v>20</v>
       </c>
@@ -12887,31 +12893,31 @@
       <c r="H8" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="17">
         <v>5</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="17">
         <v>6</v>
       </c>
-      <c r="K8" s="12">
-        <v>8</v>
-      </c>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
-      <c r="U8" s="13"/>
-      <c r="V8" s="13"/>
-      <c r="W8" s="12"/>
-      <c r="X8" s="12"/>
-      <c r="Y8" s="12"/>
-      <c r="Z8" s="12"/>
-      <c r="AA8" s="12"/>
+      <c r="K8" s="17">
+        <v>8</v>
+      </c>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="17"/>
+      <c r="T8" s="17"/>
+      <c r="U8" s="18"/>
+      <c r="V8" s="18"/>
+      <c r="W8" s="17"/>
+      <c r="X8" s="17"/>
+      <c r="Y8" s="17"/>
+      <c r="Z8" s="17"/>
+      <c r="AA8" s="17"/>
       <c r="AB8" s="13" t="s">
         <v>20</v>
       </c>
@@ -12947,31 +12953,31 @@
       <c r="H9" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I9" s="12">
-        <v>1</v>
-      </c>
-      <c r="J9" s="12">
+      <c r="I9" s="17">
+        <v>1</v>
+      </c>
+      <c r="J9" s="17">
         <v>4</v>
       </c>
-      <c r="K9" s="12">
-        <v>7</v>
-      </c>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
-      <c r="U9" s="13"/>
-      <c r="V9" s="13"/>
-      <c r="W9" s="12"/>
-      <c r="X9" s="12"/>
-      <c r="Y9" s="12"/>
-      <c r="Z9" s="12"/>
-      <c r="AA9" s="12"/>
+      <c r="K9" s="17">
+        <v>7</v>
+      </c>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="17"/>
+      <c r="U9" s="18"/>
+      <c r="V9" s="18"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="17"/>
+      <c r="Y9" s="17"/>
+      <c r="Z9" s="17"/>
+      <c r="AA9" s="17"/>
       <c r="AB9" s="13" t="s">
         <v>20</v>
       </c>
@@ -13007,31 +13013,31 @@
       <c r="H10" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I10" s="12">
-        <v>7</v>
-      </c>
-      <c r="J10" s="12">
-        <v>7</v>
-      </c>
-      <c r="K10" s="12">
-        <v>7</v>
-      </c>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="13"/>
-      <c r="V10" s="13"/>
-      <c r="W10" s="12"/>
-      <c r="X10" s="12"/>
-      <c r="Y10" s="12"/>
-      <c r="Z10" s="12"/>
-      <c r="AA10" s="12"/>
+      <c r="I10" s="17">
+        <v>7</v>
+      </c>
+      <c r="J10" s="17">
+        <v>7</v>
+      </c>
+      <c r="K10" s="17">
+        <v>7</v>
+      </c>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="17"/>
+      <c r="U10" s="18"/>
+      <c r="V10" s="18"/>
+      <c r="W10" s="17"/>
+      <c r="X10" s="17"/>
+      <c r="Y10" s="17"/>
+      <c r="Z10" s="17"/>
+      <c r="AA10" s="17"/>
       <c r="AB10" s="13" t="s">
         <v>20</v>
       </c>
@@ -13067,35 +13073,35 @@
       <c r="H11" s="10">
         <v>0.254</v>
       </c>
-      <c r="I11" s="12">
-        <v>1</v>
-      </c>
-      <c r="J11" s="12">
-        <v>2</v>
-      </c>
-      <c r="K11" s="12">
-        <v>7</v>
-      </c>
-      <c r="L11" s="12">
-        <v>2</v>
-      </c>
-      <c r="M11" s="12">
+      <c r="I11" s="17">
+        <v>1</v>
+      </c>
+      <c r="J11" s="17">
+        <v>2</v>
+      </c>
+      <c r="K11" s="17">
+        <v>7</v>
+      </c>
+      <c r="L11" s="17">
+        <v>2</v>
+      </c>
+      <c r="M11" s="17">
         <v>6</v>
       </c>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="13"/>
-      <c r="V11" s="13"/>
-      <c r="W11" s="12"/>
-      <c r="X11" s="12"/>
-      <c r="Y11" s="12"/>
-      <c r="Z11" s="12"/>
-      <c r="AA11" s="12"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="18"/>
+      <c r="V11" s="18"/>
+      <c r="W11" s="17"/>
+      <c r="X11" s="17"/>
+      <c r="Y11" s="17"/>
+      <c r="Z11" s="17"/>
+      <c r="AA11" s="17"/>
       <c r="AB11" s="13" t="s">
         <v>20</v>
       </c>
@@ -13131,31 +13137,31 @@
       <c r="H12" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I12" s="12">
-        <v>1</v>
-      </c>
-      <c r="J12" s="12">
+      <c r="I12" s="17">
+        <v>1</v>
+      </c>
+      <c r="J12" s="17">
         <v>4</v>
       </c>
-      <c r="K12" s="12">
-        <v>7</v>
-      </c>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="13"/>
-      <c r="V12" s="13"/>
-      <c r="W12" s="12"/>
-      <c r="X12" s="12"/>
-      <c r="Y12" s="12"/>
-      <c r="Z12" s="12"/>
-      <c r="AA12" s="12"/>
+      <c r="K12" s="17">
+        <v>7</v>
+      </c>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="18"/>
+      <c r="V12" s="18"/>
+      <c r="W12" s="17"/>
+      <c r="X12" s="17"/>
+      <c r="Y12" s="17"/>
+      <c r="Z12" s="17"/>
+      <c r="AA12" s="17"/>
       <c r="AB12" s="13" t="s">
         <v>20</v>
       </c>
@@ -13191,31 +13197,31 @@
       <c r="H13" s="10">
         <v>0.254</v>
       </c>
-      <c r="I13" s="12">
-        <v>1</v>
-      </c>
-      <c r="J13" s="12">
+      <c r="I13" s="17">
+        <v>1</v>
+      </c>
+      <c r="J13" s="17">
         <v>4</v>
       </c>
-      <c r="K13" s="12">
-        <v>7</v>
-      </c>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="12"/>
-      <c r="T13" s="12"/>
-      <c r="U13" s="13"/>
-      <c r="V13" s="13"/>
-      <c r="W13" s="12"/>
-      <c r="X13" s="12"/>
-      <c r="Y13" s="12"/>
-      <c r="Z13" s="12"/>
-      <c r="AA13" s="12"/>
+      <c r="K13" s="17">
+        <v>7</v>
+      </c>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="17"/>
+      <c r="U13" s="18"/>
+      <c r="V13" s="18"/>
+      <c r="W13" s="17"/>
+      <c r="X13" s="17"/>
+      <c r="Y13" s="17"/>
+      <c r="Z13" s="17"/>
+      <c r="AA13" s="17"/>
       <c r="AB13" s="13" t="s">
         <v>20</v>
       </c>
@@ -13251,35 +13257,35 @@
       <c r="H14" s="10">
         <v>0.254</v>
       </c>
-      <c r="I14" s="12">
-        <v>1</v>
-      </c>
-      <c r="J14" s="12">
+      <c r="I14" s="17">
+        <v>1</v>
+      </c>
+      <c r="J14" s="17">
         <v>3</v>
       </c>
-      <c r="K14" s="12">
-        <v>7</v>
-      </c>
-      <c r="L14" s="12">
-        <v>1</v>
-      </c>
-      <c r="M14" s="12">
+      <c r="K14" s="17">
+        <v>7</v>
+      </c>
+      <c r="L14" s="17">
+        <v>1</v>
+      </c>
+      <c r="M14" s="17">
         <v>6</v>
       </c>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="12"/>
-      <c r="U14" s="13"/>
-      <c r="V14" s="13"/>
-      <c r="W14" s="12"/>
-      <c r="X14" s="12"/>
-      <c r="Y14" s="12"/>
-      <c r="Z14" s="12"/>
-      <c r="AA14" s="12"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="17"/>
+      <c r="T14" s="17"/>
+      <c r="U14" s="18"/>
+      <c r="V14" s="18"/>
+      <c r="W14" s="17"/>
+      <c r="X14" s="17"/>
+      <c r="Y14" s="17"/>
+      <c r="Z14" s="17"/>
+      <c r="AA14" s="17"/>
       <c r="AB14" s="13" t="s">
         <v>20</v>
       </c>
@@ -13315,35 +13321,35 @@
       <c r="H15" s="10">
         <v>0.254</v>
       </c>
-      <c r="I15" s="12">
-        <v>1</v>
-      </c>
-      <c r="J15" s="12">
+      <c r="I15" s="17">
+        <v>1</v>
+      </c>
+      <c r="J15" s="17">
         <v>5</v>
       </c>
-      <c r="K15" s="12">
-        <v>8</v>
-      </c>
-      <c r="L15" s="12">
-        <v>1</v>
-      </c>
-      <c r="M15" s="12">
-        <v>7</v>
-      </c>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="12"/>
-      <c r="Q15" s="12"/>
-      <c r="R15" s="12"/>
-      <c r="S15" s="12"/>
-      <c r="T15" s="12"/>
-      <c r="U15" s="13"/>
-      <c r="V15" s="13"/>
-      <c r="W15" s="12"/>
-      <c r="X15" s="12"/>
-      <c r="Y15" s="12"/>
-      <c r="Z15" s="12"/>
-      <c r="AA15" s="12"/>
+      <c r="K15" s="17">
+        <v>8</v>
+      </c>
+      <c r="L15" s="17">
+        <v>1</v>
+      </c>
+      <c r="M15" s="17">
+        <v>7</v>
+      </c>
+      <c r="N15" s="18"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="17"/>
+      <c r="T15" s="17"/>
+      <c r="U15" s="18"/>
+      <c r="V15" s="18"/>
+      <c r="W15" s="17"/>
+      <c r="X15" s="17"/>
+      <c r="Y15" s="17"/>
+      <c r="Z15" s="17"/>
+      <c r="AA15" s="17"/>
       <c r="AB15" s="13" t="s">
         <v>20</v>
       </c>
@@ -13379,31 +13385,31 @@
       <c r="H16" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I16" s="12">
-        <v>1</v>
-      </c>
-      <c r="J16" s="12">
+      <c r="I16" s="17">
+        <v>1</v>
+      </c>
+      <c r="J16" s="17">
         <v>4</v>
       </c>
-      <c r="K16" s="12">
-        <v>7</v>
-      </c>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13"/>
-      <c r="P16" s="12"/>
-      <c r="Q16" s="12"/>
-      <c r="R16" s="12"/>
-      <c r="S16" s="12"/>
-      <c r="T16" s="12"/>
-      <c r="U16" s="13"/>
-      <c r="V16" s="13"/>
-      <c r="W16" s="12"/>
-      <c r="X16" s="12"/>
-      <c r="Y16" s="12"/>
-      <c r="Z16" s="12"/>
-      <c r="AA16" s="12"/>
+      <c r="K16" s="17">
+        <v>7</v>
+      </c>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="17"/>
+      <c r="T16" s="17"/>
+      <c r="U16" s="18"/>
+      <c r="V16" s="18"/>
+      <c r="W16" s="17"/>
+      <c r="X16" s="17"/>
+      <c r="Y16" s="17"/>
+      <c r="Z16" s="17"/>
+      <c r="AA16" s="17"/>
       <c r="AB16" s="13" t="s">
         <v>20</v>
       </c>
@@ -13439,31 +13445,31 @@
       <c r="H17" s="10">
         <v>0.44</v>
       </c>
-      <c r="I17" s="12">
-        <v>1</v>
-      </c>
-      <c r="J17" s="12">
-        <v>7</v>
-      </c>
-      <c r="K17" s="12">
-        <v>8</v>
-      </c>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="12"/>
-      <c r="T17" s="12"/>
-      <c r="U17" s="13"/>
-      <c r="V17" s="13"/>
-      <c r="W17" s="12"/>
-      <c r="X17" s="12"/>
-      <c r="Y17" s="12"/>
-      <c r="Z17" s="12"/>
-      <c r="AA17" s="12"/>
+      <c r="I17" s="17">
+        <v>1</v>
+      </c>
+      <c r="J17" s="17">
+        <v>7</v>
+      </c>
+      <c r="K17" s="17">
+        <v>8</v>
+      </c>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="17"/>
+      <c r="T17" s="17"/>
+      <c r="U17" s="18"/>
+      <c r="V17" s="18"/>
+      <c r="W17" s="17"/>
+      <c r="X17" s="17"/>
+      <c r="Y17" s="17"/>
+      <c r="Z17" s="17"/>
+      <c r="AA17" s="17"/>
       <c r="AB17" s="13" t="s">
         <v>20</v>
       </c>
@@ -13499,31 +13505,31 @@
       <c r="H18" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="17">
         <v>12</v>
       </c>
-      <c r="J18" s="12">
-        <v>8</v>
-      </c>
-      <c r="K18" s="12">
-        <v>8</v>
-      </c>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="12"/>
-      <c r="S18" s="12"/>
-      <c r="T18" s="12"/>
-      <c r="U18" s="13"/>
-      <c r="V18" s="13"/>
-      <c r="W18" s="12"/>
-      <c r="X18" s="12"/>
-      <c r="Y18" s="12"/>
-      <c r="Z18" s="12"/>
-      <c r="AA18" s="12"/>
+      <c r="J18" s="17">
+        <v>8</v>
+      </c>
+      <c r="K18" s="17">
+        <v>8</v>
+      </c>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="17"/>
+      <c r="T18" s="17"/>
+      <c r="U18" s="18"/>
+      <c r="V18" s="18"/>
+      <c r="W18" s="17"/>
+      <c r="X18" s="17"/>
+      <c r="Y18" s="17"/>
+      <c r="Z18" s="17"/>
+      <c r="AA18" s="17"/>
       <c r="AB18" s="13" t="s">
         <v>20</v>
       </c>
@@ -13559,31 +13565,31 @@
       <c r="H19" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="17">
         <v>5</v>
       </c>
-      <c r="J19" s="12">
-        <v>8</v>
-      </c>
-      <c r="K19" s="12">
-        <v>8</v>
-      </c>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="12"/>
-      <c r="Q19" s="12"/>
-      <c r="R19" s="12"/>
-      <c r="S19" s="12"/>
-      <c r="T19" s="12"/>
-      <c r="U19" s="13"/>
-      <c r="V19" s="13"/>
-      <c r="W19" s="12"/>
-      <c r="X19" s="12"/>
-      <c r="Y19" s="12"/>
-      <c r="Z19" s="12"/>
-      <c r="AA19" s="12"/>
+      <c r="J19" s="17">
+        <v>8</v>
+      </c>
+      <c r="K19" s="17">
+        <v>8</v>
+      </c>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="17"/>
+      <c r="U19" s="18"/>
+      <c r="V19" s="18"/>
+      <c r="W19" s="17"/>
+      <c r="X19" s="17"/>
+      <c r="Y19" s="17"/>
+      <c r="Z19" s="17"/>
+      <c r="AA19" s="17"/>
       <c r="AB19" s="13" t="s">
         <v>20</v>
       </c>
@@ -13619,31 +13625,31 @@
       <c r="H20" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I20" s="12">
-        <v>1</v>
-      </c>
-      <c r="J20" s="12">
+      <c r="I20" s="17">
+        <v>1</v>
+      </c>
+      <c r="J20" s="17">
         <v>6</v>
       </c>
-      <c r="K20" s="12">
-        <v>7</v>
-      </c>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="12"/>
-      <c r="Q20" s="12"/>
-      <c r="R20" s="12"/>
-      <c r="S20" s="12"/>
-      <c r="T20" s="12"/>
-      <c r="U20" s="13"/>
-      <c r="V20" s="13"/>
-      <c r="W20" s="12"/>
-      <c r="X20" s="12"/>
-      <c r="Y20" s="12"/>
-      <c r="Z20" s="12"/>
-      <c r="AA20" s="12"/>
+      <c r="K20" s="17">
+        <v>7</v>
+      </c>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="18"/>
+      <c r="V20" s="18"/>
+      <c r="W20" s="17"/>
+      <c r="X20" s="17"/>
+      <c r="Y20" s="17"/>
+      <c r="Z20" s="17"/>
+      <c r="AA20" s="17"/>
       <c r="AB20" s="13" t="s">
         <v>20</v>
       </c>
@@ -13679,35 +13685,35 @@
       <c r="H21" s="10">
         <v>0.254</v>
       </c>
-      <c r="I21" s="12">
-        <v>1</v>
-      </c>
-      <c r="J21" s="12">
-        <v>2</v>
-      </c>
-      <c r="K21" s="12">
-        <v>8</v>
-      </c>
-      <c r="L21" s="12">
-        <v>1</v>
-      </c>
-      <c r="M21" s="12">
-        <v>7</v>
-      </c>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="12"/>
-      <c r="Q21" s="12"/>
-      <c r="R21" s="12"/>
-      <c r="S21" s="12"/>
-      <c r="T21" s="12"/>
-      <c r="U21" s="13"/>
-      <c r="V21" s="13"/>
-      <c r="W21" s="12"/>
-      <c r="X21" s="12"/>
-      <c r="Y21" s="12"/>
-      <c r="Z21" s="12"/>
-      <c r="AA21" s="12"/>
+      <c r="I21" s="17">
+        <v>1</v>
+      </c>
+      <c r="J21" s="17">
+        <v>2</v>
+      </c>
+      <c r="K21" s="17">
+        <v>8</v>
+      </c>
+      <c r="L21" s="17">
+        <v>1</v>
+      </c>
+      <c r="M21" s="17">
+        <v>7</v>
+      </c>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+      <c r="U21" s="18"/>
+      <c r="V21" s="18"/>
+      <c r="W21" s="17"/>
+      <c r="X21" s="17"/>
+      <c r="Y21" s="17"/>
+      <c r="Z21" s="17"/>
+      <c r="AA21" s="17"/>
       <c r="AB21" s="13" t="s">
         <v>20</v>
       </c>
@@ -13743,31 +13749,31 @@
       <c r="H22" s="10">
         <v>0.254</v>
       </c>
-      <c r="I22" s="12">
-        <v>1</v>
-      </c>
-      <c r="J22" s="12">
+      <c r="I22" s="17">
+        <v>1</v>
+      </c>
+      <c r="J22" s="17">
         <v>4</v>
       </c>
-      <c r="K22" s="12">
-        <v>7</v>
-      </c>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="13"/>
-      <c r="O22" s="13"/>
-      <c r="P22" s="12"/>
-      <c r="Q22" s="12"/>
-      <c r="R22" s="12"/>
-      <c r="S22" s="12"/>
-      <c r="T22" s="12"/>
-      <c r="U22" s="13"/>
-      <c r="V22" s="13"/>
-      <c r="W22" s="12"/>
-      <c r="X22" s="12"/>
-      <c r="Y22" s="12"/>
-      <c r="Z22" s="12"/>
-      <c r="AA22" s="12"/>
+      <c r="K22" s="17">
+        <v>7</v>
+      </c>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="17"/>
+      <c r="T22" s="17"/>
+      <c r="U22" s="18"/>
+      <c r="V22" s="18"/>
+      <c r="W22" s="17"/>
+      <c r="X22" s="17"/>
+      <c r="Y22" s="17"/>
+      <c r="Z22" s="17"/>
+      <c r="AA22" s="17"/>
       <c r="AB22" s="13" t="s">
         <v>20</v>
       </c>
@@ -13803,31 +13809,31 @@
       <c r="H23" s="10">
         <v>0.44</v>
       </c>
-      <c r="I23" s="12">
-        <v>1</v>
-      </c>
-      <c r="J23" s="12">
-        <v>7</v>
-      </c>
-      <c r="K23" s="12">
-        <v>8</v>
-      </c>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="12"/>
-      <c r="Q23" s="12"/>
-      <c r="R23" s="12"/>
-      <c r="S23" s="12"/>
-      <c r="T23" s="12"/>
-      <c r="U23" s="13"/>
-      <c r="V23" s="13"/>
-      <c r="W23" s="12"/>
-      <c r="X23" s="12"/>
-      <c r="Y23" s="12"/>
-      <c r="Z23" s="12"/>
-      <c r="AA23" s="12"/>
+      <c r="I23" s="17">
+        <v>1</v>
+      </c>
+      <c r="J23" s="17">
+        <v>7</v>
+      </c>
+      <c r="K23" s="17">
+        <v>8</v>
+      </c>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="17"/>
+      <c r="S23" s="17"/>
+      <c r="T23" s="17"/>
+      <c r="U23" s="18"/>
+      <c r="V23" s="18"/>
+      <c r="W23" s="17"/>
+      <c r="X23" s="17"/>
+      <c r="Y23" s="17"/>
+      <c r="Z23" s="17"/>
+      <c r="AA23" s="17"/>
       <c r="AB23" s="13" t="s">
         <v>20</v>
       </c>
@@ -13863,31 +13869,31 @@
       <c r="H24" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I24" s="12">
+      <c r="I24" s="17">
         <v>12</v>
       </c>
-      <c r="J24" s="12">
-        <v>8</v>
-      </c>
-      <c r="K24" s="12">
-        <v>8</v>
-      </c>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="13"/>
-      <c r="P24" s="12"/>
-      <c r="Q24" s="12"/>
-      <c r="R24" s="12"/>
-      <c r="S24" s="12"/>
-      <c r="T24" s="12"/>
-      <c r="U24" s="13"/>
-      <c r="V24" s="13"/>
-      <c r="W24" s="12"/>
-      <c r="X24" s="12"/>
-      <c r="Y24" s="12"/>
-      <c r="Z24" s="12"/>
-      <c r="AA24" s="12"/>
+      <c r="J24" s="17">
+        <v>8</v>
+      </c>
+      <c r="K24" s="17">
+        <v>8</v>
+      </c>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="17"/>
+      <c r="S24" s="17"/>
+      <c r="T24" s="17"/>
+      <c r="U24" s="18"/>
+      <c r="V24" s="18"/>
+      <c r="W24" s="17"/>
+      <c r="X24" s="17"/>
+      <c r="Y24" s="17"/>
+      <c r="Z24" s="17"/>
+      <c r="AA24" s="17"/>
       <c r="AB24" s="13" t="s">
         <v>20</v>
       </c>
@@ -13923,31 +13929,31 @@
       <c r="H25" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I25" s="12">
+      <c r="I25" s="17">
         <v>5</v>
       </c>
-      <c r="J25" s="12">
+      <c r="J25" s="17">
         <v>4</v>
       </c>
-      <c r="K25" s="12">
-        <v>8</v>
-      </c>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="13"/>
-      <c r="O25" s="13"/>
-      <c r="P25" s="12"/>
-      <c r="Q25" s="12"/>
-      <c r="R25" s="12"/>
-      <c r="S25" s="12"/>
-      <c r="T25" s="12"/>
-      <c r="U25" s="13"/>
-      <c r="V25" s="13"/>
-      <c r="W25" s="12"/>
-      <c r="X25" s="12"/>
-      <c r="Y25" s="12"/>
-      <c r="Z25" s="12"/>
-      <c r="AA25" s="12"/>
+      <c r="K25" s="17">
+        <v>8</v>
+      </c>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="17"/>
+      <c r="T25" s="17"/>
+      <c r="U25" s="18"/>
+      <c r="V25" s="18"/>
+      <c r="W25" s="17"/>
+      <c r="X25" s="17"/>
+      <c r="Y25" s="17"/>
+      <c r="Z25" s="17"/>
+      <c r="AA25" s="17"/>
       <c r="AB25" s="13" t="s">
         <v>20</v>
       </c>
@@ -13983,35 +13989,35 @@
       <c r="H26" s="10">
         <v>0.254</v>
       </c>
-      <c r="I26" s="12">
-        <v>1</v>
-      </c>
-      <c r="J26" s="12">
-        <v>2</v>
-      </c>
-      <c r="K26" s="12">
-        <v>7</v>
-      </c>
-      <c r="L26" s="12">
-        <v>2</v>
-      </c>
-      <c r="M26" s="12">
+      <c r="I26" s="17">
+        <v>1</v>
+      </c>
+      <c r="J26" s="17">
+        <v>2</v>
+      </c>
+      <c r="K26" s="17">
+        <v>7</v>
+      </c>
+      <c r="L26" s="17">
+        <v>2</v>
+      </c>
+      <c r="M26" s="17">
         <v>6</v>
       </c>
-      <c r="N26" s="13"/>
-      <c r="O26" s="13"/>
-      <c r="P26" s="12"/>
-      <c r="Q26" s="12"/>
-      <c r="R26" s="12"/>
-      <c r="S26" s="12"/>
-      <c r="T26" s="12"/>
-      <c r="U26" s="13"/>
-      <c r="V26" s="13"/>
-      <c r="W26" s="12"/>
-      <c r="X26" s="12"/>
-      <c r="Y26" s="12"/>
-      <c r="Z26" s="12"/>
-      <c r="AA26" s="12"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
+      <c r="R26" s="17"/>
+      <c r="S26" s="17"/>
+      <c r="T26" s="17"/>
+      <c r="U26" s="18"/>
+      <c r="V26" s="18"/>
+      <c r="W26" s="17"/>
+      <c r="X26" s="17"/>
+      <c r="Y26" s="17"/>
+      <c r="Z26" s="17"/>
+      <c r="AA26" s="17"/>
       <c r="AB26" s="13" t="s">
         <v>20</v>
       </c>
@@ -14047,31 +14053,31 @@
       <c r="H27" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I27" s="12">
-        <v>7</v>
-      </c>
-      <c r="J27" s="12">
+      <c r="I27" s="17">
+        <v>7</v>
+      </c>
+      <c r="J27" s="17">
         <v>4</v>
       </c>
-      <c r="K27" s="12">
-        <v>8</v>
-      </c>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="13"/>
-      <c r="O27" s="13"/>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="12"/>
-      <c r="R27" s="12"/>
-      <c r="S27" s="12"/>
-      <c r="T27" s="12"/>
-      <c r="U27" s="13"/>
-      <c r="V27" s="13"/>
-      <c r="W27" s="12"/>
-      <c r="X27" s="12"/>
-      <c r="Y27" s="12"/>
-      <c r="Z27" s="12"/>
-      <c r="AA27" s="12"/>
+      <c r="K27" s="17">
+        <v>8</v>
+      </c>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="17"/>
+      <c r="T27" s="17"/>
+      <c r="U27" s="18"/>
+      <c r="V27" s="18"/>
+      <c r="W27" s="17"/>
+      <c r="X27" s="17"/>
+      <c r="Y27" s="17"/>
+      <c r="Z27" s="17"/>
+      <c r="AA27" s="17"/>
       <c r="AB27" s="13" t="s">
         <v>20</v>
       </c>
@@ -14107,31 +14113,31 @@
       <c r="H28" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I28" s="12">
+      <c r="I28" s="17">
         <v>39</v>
       </c>
-      <c r="J28" s="12">
+      <c r="J28" s="17">
         <v>4</v>
       </c>
-      <c r="K28" s="12">
-        <v>8</v>
-      </c>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="13"/>
-      <c r="O28" s="13"/>
-      <c r="P28" s="12"/>
-      <c r="Q28" s="12"/>
-      <c r="R28" s="12"/>
-      <c r="S28" s="12"/>
-      <c r="T28" s="12"/>
-      <c r="U28" s="13"/>
-      <c r="V28" s="13"/>
-      <c r="W28" s="12"/>
-      <c r="X28" s="12"/>
-      <c r="Y28" s="12"/>
-      <c r="Z28" s="12"/>
-      <c r="AA28" s="12"/>
+      <c r="K28" s="17">
+        <v>8</v>
+      </c>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17"/>
+      <c r="T28" s="17"/>
+      <c r="U28" s="18"/>
+      <c r="V28" s="18"/>
+      <c r="W28" s="17"/>
+      <c r="X28" s="17"/>
+      <c r="Y28" s="17"/>
+      <c r="Z28" s="17"/>
+      <c r="AA28" s="17"/>
       <c r="AB28" s="13" t="s">
         <v>20</v>
       </c>
@@ -14167,31 +14173,31 @@
       <c r="H29" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I29" s="12">
+      <c r="I29" s="17">
         <v>39</v>
       </c>
-      <c r="J29" s="12">
+      <c r="J29" s="17">
         <v>4</v>
       </c>
-      <c r="K29" s="12">
-        <v>8</v>
-      </c>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13"/>
-      <c r="P29" s="12"/>
-      <c r="Q29" s="12"/>
-      <c r="R29" s="12"/>
-      <c r="S29" s="12"/>
-      <c r="T29" s="12"/>
-      <c r="U29" s="13"/>
-      <c r="V29" s="13"/>
-      <c r="W29" s="12"/>
-      <c r="X29" s="12"/>
-      <c r="Y29" s="12"/>
-      <c r="Z29" s="12"/>
-      <c r="AA29" s="12"/>
+      <c r="K29" s="17">
+        <v>8</v>
+      </c>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="18"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="18"/>
+      <c r="V29" s="18"/>
+      <c r="W29" s="17"/>
+      <c r="X29" s="17"/>
+      <c r="Y29" s="17"/>
+      <c r="Z29" s="17"/>
+      <c r="AA29" s="17"/>
       <c r="AB29" s="13" t="s">
         <v>20</v>
       </c>
@@ -14227,31 +14233,31 @@
       <c r="H30" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I30" s="12">
-        <v>7</v>
-      </c>
-      <c r="J30" s="12">
+      <c r="I30" s="17">
+        <v>7</v>
+      </c>
+      <c r="J30" s="17">
         <v>3</v>
       </c>
-      <c r="K30" s="12">
-        <v>8</v>
-      </c>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="13"/>
-      <c r="O30" s="13"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="12"/>
-      <c r="T30" s="12"/>
-      <c r="U30" s="13"/>
-      <c r="V30" s="13"/>
-      <c r="W30" s="12"/>
-      <c r="X30" s="12"/>
-      <c r="Y30" s="12"/>
-      <c r="Z30" s="12"/>
-      <c r="AA30" s="12"/>
+      <c r="K30" s="17">
+        <v>8</v>
+      </c>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="18"/>
+      <c r="O30" s="18"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="17"/>
+      <c r="S30" s="17"/>
+      <c r="T30" s="17"/>
+      <c r="U30" s="18"/>
+      <c r="V30" s="18"/>
+      <c r="W30" s="17"/>
+      <c r="X30" s="17"/>
+      <c r="Y30" s="17"/>
+      <c r="Z30" s="17"/>
+      <c r="AA30" s="17"/>
       <c r="AB30" s="13" t="s">
         <v>20</v>
       </c>
@@ -14287,31 +14293,31 @@
       <c r="H31" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I31" s="12">
+      <c r="I31" s="17">
         <v>5</v>
       </c>
-      <c r="J31" s="12">
+      <c r="J31" s="17">
         <v>3</v>
       </c>
-      <c r="K31" s="12">
-        <v>7</v>
-      </c>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="13"/>
-      <c r="O31" s="13"/>
-      <c r="P31" s="12"/>
-      <c r="Q31" s="12"/>
-      <c r="R31" s="12"/>
-      <c r="S31" s="12"/>
-      <c r="T31" s="12"/>
-      <c r="U31" s="13"/>
-      <c r="V31" s="13"/>
-      <c r="W31" s="12"/>
-      <c r="X31" s="12"/>
-      <c r="Y31" s="12"/>
-      <c r="Z31" s="12"/>
-      <c r="AA31" s="12"/>
+      <c r="K31" s="17">
+        <v>7</v>
+      </c>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="18"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="17"/>
+      <c r="R31" s="17"/>
+      <c r="S31" s="17"/>
+      <c r="T31" s="17"/>
+      <c r="U31" s="18"/>
+      <c r="V31" s="18"/>
+      <c r="W31" s="17"/>
+      <c r="X31" s="17"/>
+      <c r="Y31" s="17"/>
+      <c r="Z31" s="17"/>
+      <c r="AA31" s="17"/>
       <c r="AB31" s="13" t="s">
         <v>20</v>
       </c>
@@ -14347,31 +14353,31 @@
       <c r="H32" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I32" s="12">
+      <c r="I32" s="17">
         <v>5</v>
       </c>
-      <c r="J32" s="12">
+      <c r="J32" s="17">
         <v>4</v>
       </c>
-      <c r="K32" s="12">
-        <v>8</v>
-      </c>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
-      <c r="N32" s="13"/>
-      <c r="O32" s="13"/>
-      <c r="P32" s="12"/>
-      <c r="Q32" s="12"/>
-      <c r="R32" s="12"/>
-      <c r="S32" s="12"/>
-      <c r="T32" s="12"/>
-      <c r="U32" s="13"/>
-      <c r="V32" s="13"/>
-      <c r="W32" s="12"/>
-      <c r="X32" s="12"/>
-      <c r="Y32" s="12"/>
-      <c r="Z32" s="12"/>
-      <c r="AA32" s="12"/>
+      <c r="K32" s="17">
+        <v>8</v>
+      </c>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17"/>
+      <c r="S32" s="17"/>
+      <c r="T32" s="17"/>
+      <c r="U32" s="18"/>
+      <c r="V32" s="18"/>
+      <c r="W32" s="17"/>
+      <c r="X32" s="17"/>
+      <c r="Y32" s="17"/>
+      <c r="Z32" s="17"/>
+      <c r="AA32" s="17"/>
       <c r="AB32" s="13" t="s">
         <v>20</v>
       </c>
@@ -14407,35 +14413,35 @@
       <c r="H33" s="10">
         <v>0.254</v>
       </c>
-      <c r="I33" s="12">
-        <v>1</v>
-      </c>
-      <c r="J33" s="12">
-        <v>2</v>
-      </c>
-      <c r="K33" s="12">
-        <v>7</v>
-      </c>
-      <c r="L33" s="12">
-        <v>2</v>
-      </c>
-      <c r="M33" s="12">
+      <c r="I33" s="17">
+        <v>1</v>
+      </c>
+      <c r="J33" s="17">
+        <v>2</v>
+      </c>
+      <c r="K33" s="17">
+        <v>7</v>
+      </c>
+      <c r="L33" s="17">
+        <v>2</v>
+      </c>
+      <c r="M33" s="17">
         <v>6</v>
       </c>
-      <c r="N33" s="13"/>
-      <c r="O33" s="13"/>
-      <c r="P33" s="12"/>
-      <c r="Q33" s="12"/>
-      <c r="R33" s="12"/>
-      <c r="S33" s="12"/>
-      <c r="T33" s="12"/>
-      <c r="U33" s="13"/>
-      <c r="V33" s="13"/>
-      <c r="W33" s="12"/>
-      <c r="X33" s="12"/>
-      <c r="Y33" s="12"/>
-      <c r="Z33" s="12"/>
-      <c r="AA33" s="12"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="18"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="17"/>
+      <c r="S33" s="17"/>
+      <c r="T33" s="17"/>
+      <c r="U33" s="18"/>
+      <c r="V33" s="18"/>
+      <c r="W33" s="17"/>
+      <c r="X33" s="17"/>
+      <c r="Y33" s="17"/>
+      <c r="Z33" s="17"/>
+      <c r="AA33" s="17"/>
       <c r="AB33" s="13" t="s">
         <v>20</v>
       </c>
@@ -14471,35 +14477,35 @@
       <c r="H34" s="10">
         <v>0.254</v>
       </c>
-      <c r="I34" s="12">
-        <v>1</v>
-      </c>
-      <c r="J34" s="12">
-        <v>2</v>
-      </c>
-      <c r="K34" s="12">
-        <v>7</v>
-      </c>
-      <c r="L34" s="12">
-        <v>2</v>
-      </c>
-      <c r="M34" s="12">
+      <c r="I34" s="17">
+        <v>1</v>
+      </c>
+      <c r="J34" s="17">
+        <v>2</v>
+      </c>
+      <c r="K34" s="17">
+        <v>7</v>
+      </c>
+      <c r="L34" s="17">
+        <v>2</v>
+      </c>
+      <c r="M34" s="17">
         <v>6</v>
       </c>
-      <c r="N34" s="13"/>
-      <c r="O34" s="13"/>
-      <c r="P34" s="12"/>
-      <c r="Q34" s="12"/>
-      <c r="R34" s="12"/>
-      <c r="S34" s="12"/>
-      <c r="T34" s="12"/>
-      <c r="U34" s="13"/>
-      <c r="V34" s="13"/>
-      <c r="W34" s="12"/>
-      <c r="X34" s="12"/>
-      <c r="Y34" s="12"/>
-      <c r="Z34" s="12"/>
-      <c r="AA34" s="12"/>
+      <c r="N34" s="18"/>
+      <c r="O34" s="18"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
+      <c r="T34" s="17"/>
+      <c r="U34" s="18"/>
+      <c r="V34" s="18"/>
+      <c r="W34" s="17"/>
+      <c r="X34" s="17"/>
+      <c r="Y34" s="17"/>
+      <c r="Z34" s="17"/>
+      <c r="AA34" s="17"/>
       <c r="AB34" s="13" t="s">
         <v>20</v>
       </c>
@@ -14535,35 +14541,35 @@
       <c r="H35" s="10">
         <v>0.254</v>
       </c>
-      <c r="I35" s="12">
-        <v>1</v>
-      </c>
-      <c r="J35" s="12">
-        <v>2</v>
-      </c>
-      <c r="K35" s="12">
-        <v>8</v>
-      </c>
-      <c r="L35" s="12">
+      <c r="I35" s="17">
+        <v>1</v>
+      </c>
+      <c r="J35" s="17">
+        <v>2</v>
+      </c>
+      <c r="K35" s="17">
+        <v>8</v>
+      </c>
+      <c r="L35" s="17">
         <v>4</v>
       </c>
-      <c r="M35" s="12">
-        <v>7</v>
-      </c>
-      <c r="N35" s="13"/>
-      <c r="O35" s="13"/>
-      <c r="P35" s="12"/>
-      <c r="Q35" s="12"/>
-      <c r="R35" s="12"/>
-      <c r="S35" s="12"/>
-      <c r="T35" s="12"/>
-      <c r="U35" s="13"/>
-      <c r="V35" s="13"/>
-      <c r="W35" s="12"/>
-      <c r="X35" s="12"/>
-      <c r="Y35" s="12"/>
-      <c r="Z35" s="12"/>
-      <c r="AA35" s="12"/>
+      <c r="M35" s="17">
+        <v>7</v>
+      </c>
+      <c r="N35" s="18"/>
+      <c r="O35" s="18"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="17"/>
+      <c r="S35" s="17"/>
+      <c r="T35" s="17"/>
+      <c r="U35" s="18"/>
+      <c r="V35" s="18"/>
+      <c r="W35" s="17"/>
+      <c r="X35" s="17"/>
+      <c r="Y35" s="17"/>
+      <c r="Z35" s="17"/>
+      <c r="AA35" s="17"/>
       <c r="AB35" s="13" t="s">
         <v>20</v>
       </c>
@@ -14599,35 +14605,35 @@
       <c r="H36" s="10">
         <v>0.254</v>
       </c>
-      <c r="I36" s="12">
-        <v>1</v>
-      </c>
-      <c r="J36" s="12">
-        <v>2</v>
-      </c>
-      <c r="K36" s="12">
-        <v>8</v>
-      </c>
-      <c r="L36" s="12">
+      <c r="I36" s="17">
+        <v>1</v>
+      </c>
+      <c r="J36" s="17">
+        <v>2</v>
+      </c>
+      <c r="K36" s="17">
+        <v>8</v>
+      </c>
+      <c r="L36" s="17">
         <v>4</v>
       </c>
-      <c r="M36" s="12">
-        <v>7</v>
-      </c>
-      <c r="N36" s="13"/>
-      <c r="O36" s="13"/>
-      <c r="P36" s="12"/>
-      <c r="Q36" s="12"/>
-      <c r="R36" s="12"/>
-      <c r="S36" s="12"/>
-      <c r="T36" s="12"/>
-      <c r="U36" s="13"/>
-      <c r="V36" s="13"/>
-      <c r="W36" s="12"/>
-      <c r="X36" s="12"/>
-      <c r="Y36" s="12"/>
-      <c r="Z36" s="12"/>
-      <c r="AA36" s="12"/>
+      <c r="M36" s="17">
+        <v>7</v>
+      </c>
+      <c r="N36" s="18"/>
+      <c r="O36" s="18"/>
+      <c r="P36" s="17"/>
+      <c r="Q36" s="17"/>
+      <c r="R36" s="17"/>
+      <c r="S36" s="17"/>
+      <c r="T36" s="17"/>
+      <c r="U36" s="18"/>
+      <c r="V36" s="18"/>
+      <c r="W36" s="17"/>
+      <c r="X36" s="17"/>
+      <c r="Y36" s="17"/>
+      <c r="Z36" s="17"/>
+      <c r="AA36" s="17"/>
       <c r="AB36" s="13" t="s">
         <v>20</v>
       </c>
@@ -14663,35 +14669,35 @@
       <c r="H37" s="10">
         <v>0.254</v>
       </c>
-      <c r="I37" s="12">
-        <v>1</v>
-      </c>
-      <c r="J37" s="12">
-        <v>2</v>
-      </c>
-      <c r="K37" s="12">
-        <v>7</v>
-      </c>
-      <c r="L37" s="12">
-        <v>2</v>
-      </c>
-      <c r="M37" s="12">
+      <c r="I37" s="17">
+        <v>1</v>
+      </c>
+      <c r="J37" s="17">
+        <v>2</v>
+      </c>
+      <c r="K37" s="17">
+        <v>7</v>
+      </c>
+      <c r="L37" s="17">
+        <v>2</v>
+      </c>
+      <c r="M37" s="17">
         <v>6</v>
       </c>
-      <c r="N37" s="13"/>
-      <c r="O37" s="13"/>
-      <c r="P37" s="12"/>
-      <c r="Q37" s="12"/>
-      <c r="R37" s="12"/>
-      <c r="S37" s="12"/>
-      <c r="T37" s="12"/>
-      <c r="U37" s="13"/>
-      <c r="V37" s="13"/>
-      <c r="W37" s="12"/>
-      <c r="X37" s="12"/>
-      <c r="Y37" s="12"/>
-      <c r="Z37" s="12"/>
-      <c r="AA37" s="12"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="17"/>
+      <c r="U37" s="18"/>
+      <c r="V37" s="18"/>
+      <c r="W37" s="17"/>
+      <c r="X37" s="17"/>
+      <c r="Y37" s="17"/>
+      <c r="Z37" s="17"/>
+      <c r="AA37" s="17"/>
       <c r="AB37" s="13" t="s">
         <v>20</v>
       </c>
@@ -14727,41 +14733,41 @@
       <c r="H38" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I38" s="12">
+      <c r="I38" s="17">
         <v>12</v>
       </c>
-      <c r="J38" s="12">
-        <v>8</v>
-      </c>
-      <c r="K38" s="12">
-        <v>8</v>
-      </c>
-      <c r="L38" s="12"/>
-      <c r="M38" s="12"/>
-      <c r="N38" s="10">
-        <v>1</v>
-      </c>
-      <c r="O38" s="10">
+      <c r="J38" s="17">
+        <v>8</v>
+      </c>
+      <c r="K38" s="17">
+        <v>8</v>
+      </c>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="18">
+        <v>1</v>
+      </c>
+      <c r="O38" s="18">
         <v>0.40400000000000003</v>
       </c>
-      <c r="P38" s="12">
-        <v>7</v>
-      </c>
-      <c r="Q38" s="12">
+      <c r="P38" s="17">
+        <v>7</v>
+      </c>
+      <c r="Q38" s="17">
         <v>4</v>
       </c>
-      <c r="R38" s="12">
-        <v>8</v>
-      </c>
-      <c r="S38" s="12"/>
-      <c r="T38" s="12"/>
-      <c r="U38" s="13"/>
-      <c r="V38" s="13"/>
-      <c r="W38" s="12"/>
-      <c r="X38" s="12"/>
-      <c r="Y38" s="12"/>
-      <c r="Z38" s="12"/>
-      <c r="AA38" s="12"/>
+      <c r="R38" s="17">
+        <v>8</v>
+      </c>
+      <c r="S38" s="17"/>
+      <c r="T38" s="17"/>
+      <c r="U38" s="18"/>
+      <c r="V38" s="18"/>
+      <c r="W38" s="17"/>
+      <c r="X38" s="17"/>
+      <c r="Y38" s="17"/>
+      <c r="Z38" s="17"/>
+      <c r="AA38" s="17"/>
       <c r="AB38" s="13" t="s">
         <v>20</v>
       </c>
@@ -14797,41 +14803,41 @@
       <c r="H39" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I39" s="12">
+      <c r="I39" s="17">
         <v>12</v>
       </c>
-      <c r="J39" s="12">
-        <v>8</v>
-      </c>
-      <c r="K39" s="12">
-        <v>8</v>
-      </c>
-      <c r="L39" s="12"/>
-      <c r="M39" s="12"/>
-      <c r="N39" s="10">
-        <v>1</v>
-      </c>
-      <c r="O39" s="10">
+      <c r="J39" s="17">
+        <v>8</v>
+      </c>
+      <c r="K39" s="17">
+        <v>8</v>
+      </c>
+      <c r="L39" s="17"/>
+      <c r="M39" s="17"/>
+      <c r="N39" s="18">
+        <v>1</v>
+      </c>
+      <c r="O39" s="18">
         <v>0.40400000000000003</v>
       </c>
-      <c r="P39" s="12">
-        <v>7</v>
-      </c>
-      <c r="Q39" s="12">
+      <c r="P39" s="17">
+        <v>7</v>
+      </c>
+      <c r="Q39" s="17">
         <v>4</v>
       </c>
-      <c r="R39" s="12">
-        <v>8</v>
-      </c>
-      <c r="S39" s="12"/>
-      <c r="T39" s="12"/>
-      <c r="U39" s="13"/>
-      <c r="V39" s="13"/>
-      <c r="W39" s="12"/>
-      <c r="X39" s="12"/>
-      <c r="Y39" s="12"/>
-      <c r="Z39" s="12"/>
-      <c r="AA39" s="12"/>
+      <c r="R39" s="17">
+        <v>8</v>
+      </c>
+      <c r="S39" s="17"/>
+      <c r="T39" s="17"/>
+      <c r="U39" s="18"/>
+      <c r="V39" s="18"/>
+      <c r="W39" s="17"/>
+      <c r="X39" s="17"/>
+      <c r="Y39" s="17"/>
+      <c r="Z39" s="17"/>
+      <c r="AA39" s="17"/>
       <c r="AB39" s="13" t="s">
         <v>20</v>
       </c>
@@ -14867,35 +14873,35 @@
       <c r="H40" s="10">
         <v>0.254</v>
       </c>
-      <c r="I40" s="12">
-        <v>1</v>
-      </c>
-      <c r="J40" s="12">
-        <v>2</v>
-      </c>
-      <c r="K40" s="12">
-        <v>8</v>
-      </c>
-      <c r="L40" s="12">
+      <c r="I40" s="17">
+        <v>1</v>
+      </c>
+      <c r="J40" s="17">
+        <v>2</v>
+      </c>
+      <c r="K40" s="17">
+        <v>8</v>
+      </c>
+      <c r="L40" s="17">
         <v>4</v>
       </c>
-      <c r="M40" s="12">
-        <v>7</v>
-      </c>
-      <c r="N40" s="13"/>
-      <c r="O40" s="13"/>
-      <c r="P40" s="12"/>
-      <c r="Q40" s="12"/>
-      <c r="R40" s="12"/>
-      <c r="S40" s="12"/>
-      <c r="T40" s="12"/>
-      <c r="U40" s="13"/>
-      <c r="V40" s="13"/>
-      <c r="W40" s="12"/>
-      <c r="X40" s="12"/>
-      <c r="Y40" s="12"/>
-      <c r="Z40" s="12"/>
-      <c r="AA40" s="12"/>
+      <c r="M40" s="17">
+        <v>7</v>
+      </c>
+      <c r="N40" s="18"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
+      <c r="R40" s="17"/>
+      <c r="S40" s="17"/>
+      <c r="T40" s="17"/>
+      <c r="U40" s="18"/>
+      <c r="V40" s="18"/>
+      <c r="W40" s="17"/>
+      <c r="X40" s="17"/>
+      <c r="Y40" s="17"/>
+      <c r="Z40" s="17"/>
+      <c r="AA40" s="17"/>
       <c r="AB40" s="13" t="s">
         <v>20</v>
       </c>
@@ -14931,35 +14937,35 @@
       <c r="H41" s="10">
         <v>0.254</v>
       </c>
-      <c r="I41" s="12">
-        <v>1</v>
-      </c>
-      <c r="J41" s="12">
-        <v>2</v>
-      </c>
-      <c r="K41" s="12">
-        <v>7</v>
-      </c>
-      <c r="L41" s="12">
-        <v>2</v>
-      </c>
-      <c r="M41" s="12">
+      <c r="I41" s="17">
+        <v>1</v>
+      </c>
+      <c r="J41" s="17">
+        <v>2</v>
+      </c>
+      <c r="K41" s="17">
+        <v>7</v>
+      </c>
+      <c r="L41" s="17">
+        <v>2</v>
+      </c>
+      <c r="M41" s="17">
         <v>6</v>
       </c>
-      <c r="N41" s="13"/>
-      <c r="O41" s="13"/>
-      <c r="P41" s="12"/>
-      <c r="Q41" s="12"/>
-      <c r="R41" s="12"/>
-      <c r="S41" s="12"/>
-      <c r="T41" s="12"/>
-      <c r="U41" s="13"/>
-      <c r="V41" s="13"/>
-      <c r="W41" s="12"/>
-      <c r="X41" s="12"/>
-      <c r="Y41" s="12"/>
-      <c r="Z41" s="12"/>
-      <c r="AA41" s="12"/>
+      <c r="N41" s="18"/>
+      <c r="O41" s="18"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="17"/>
+      <c r="R41" s="17"/>
+      <c r="S41" s="17"/>
+      <c r="T41" s="17"/>
+      <c r="U41" s="18"/>
+      <c r="V41" s="18"/>
+      <c r="W41" s="17"/>
+      <c r="X41" s="17"/>
+      <c r="Y41" s="17"/>
+      <c r="Z41" s="17"/>
+      <c r="AA41" s="17"/>
       <c r="AB41" s="13" t="s">
         <v>20</v>
       </c>
@@ -14995,35 +15001,35 @@
       <c r="H42" s="10">
         <v>0.254</v>
       </c>
-      <c r="I42" s="12">
-        <v>1</v>
-      </c>
-      <c r="J42" s="12">
-        <v>2</v>
-      </c>
-      <c r="K42" s="12">
-        <v>8</v>
-      </c>
-      <c r="L42" s="12">
+      <c r="I42" s="17">
+        <v>1</v>
+      </c>
+      <c r="J42" s="17">
+        <v>2</v>
+      </c>
+      <c r="K42" s="17">
+        <v>8</v>
+      </c>
+      <c r="L42" s="17">
         <v>4</v>
       </c>
-      <c r="M42" s="12">
-        <v>7</v>
-      </c>
-      <c r="N42" s="13"/>
-      <c r="O42" s="13"/>
-      <c r="P42" s="12"/>
-      <c r="Q42" s="12"/>
-      <c r="R42" s="12"/>
-      <c r="S42" s="12"/>
-      <c r="T42" s="12"/>
-      <c r="U42" s="13"/>
-      <c r="V42" s="13"/>
-      <c r="W42" s="12"/>
-      <c r="X42" s="12"/>
-      <c r="Y42" s="12"/>
-      <c r="Z42" s="12"/>
-      <c r="AA42" s="12"/>
+      <c r="M42" s="17">
+        <v>7</v>
+      </c>
+      <c r="N42" s="18"/>
+      <c r="O42" s="18"/>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="17"/>
+      <c r="R42" s="17"/>
+      <c r="S42" s="17"/>
+      <c r="T42" s="17"/>
+      <c r="U42" s="18"/>
+      <c r="V42" s="18"/>
+      <c r="W42" s="17"/>
+      <c r="X42" s="17"/>
+      <c r="Y42" s="17"/>
+      <c r="Z42" s="17"/>
+      <c r="AA42" s="17"/>
       <c r="AB42" s="13" t="s">
         <v>20</v>
       </c>
@@ -15059,31 +15065,31 @@
       <c r="H43" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I43" s="12">
-        <v>1</v>
-      </c>
-      <c r="J43" s="12">
+      <c r="I43" s="17">
+        <v>1</v>
+      </c>
+      <c r="J43" s="17">
         <v>6</v>
       </c>
-      <c r="K43" s="12">
-        <v>7</v>
-      </c>
-      <c r="L43" s="12"/>
-      <c r="M43" s="12"/>
-      <c r="N43" s="13"/>
-      <c r="O43" s="13"/>
-      <c r="P43" s="12"/>
-      <c r="Q43" s="12"/>
-      <c r="R43" s="12"/>
-      <c r="S43" s="12"/>
-      <c r="T43" s="12"/>
-      <c r="U43" s="13"/>
-      <c r="V43" s="13"/>
-      <c r="W43" s="12"/>
-      <c r="X43" s="12"/>
-      <c r="Y43" s="12"/>
-      <c r="Z43" s="12"/>
-      <c r="AA43" s="12"/>
+      <c r="K43" s="17">
+        <v>7</v>
+      </c>
+      <c r="L43" s="17"/>
+      <c r="M43" s="17"/>
+      <c r="N43" s="18"/>
+      <c r="O43" s="18"/>
+      <c r="P43" s="17"/>
+      <c r="Q43" s="17"/>
+      <c r="R43" s="17"/>
+      <c r="S43" s="17"/>
+      <c r="T43" s="17"/>
+      <c r="U43" s="18"/>
+      <c r="V43" s="18"/>
+      <c r="W43" s="17"/>
+      <c r="X43" s="17"/>
+      <c r="Y43" s="17"/>
+      <c r="Z43" s="17"/>
+      <c r="AA43" s="17"/>
       <c r="AB43" s="13" t="s">
         <v>20</v>
       </c>
@@ -15119,35 +15125,35 @@
       <c r="H44" s="10">
         <v>0.254</v>
       </c>
-      <c r="I44" s="12">
-        <v>1</v>
-      </c>
-      <c r="J44" s="12">
-        <v>1</v>
-      </c>
-      <c r="K44" s="12">
-        <v>8</v>
-      </c>
-      <c r="L44" s="12">
-        <v>2</v>
-      </c>
-      <c r="M44" s="12">
-        <v>7</v>
-      </c>
-      <c r="N44" s="13"/>
-      <c r="O44" s="13"/>
-      <c r="P44" s="12"/>
-      <c r="Q44" s="12"/>
-      <c r="R44" s="12"/>
-      <c r="S44" s="12"/>
-      <c r="T44" s="12"/>
-      <c r="U44" s="13"/>
-      <c r="V44" s="13"/>
-      <c r="W44" s="12"/>
-      <c r="X44" s="12"/>
-      <c r="Y44" s="12"/>
-      <c r="Z44" s="12"/>
-      <c r="AA44" s="12"/>
+      <c r="I44" s="17">
+        <v>1</v>
+      </c>
+      <c r="J44" s="17">
+        <v>1</v>
+      </c>
+      <c r="K44" s="17">
+        <v>8</v>
+      </c>
+      <c r="L44" s="17">
+        <v>2</v>
+      </c>
+      <c r="M44" s="17">
+        <v>7</v>
+      </c>
+      <c r="N44" s="18"/>
+      <c r="O44" s="18"/>
+      <c r="P44" s="17"/>
+      <c r="Q44" s="17"/>
+      <c r="R44" s="17"/>
+      <c r="S44" s="17"/>
+      <c r="T44" s="17"/>
+      <c r="U44" s="18"/>
+      <c r="V44" s="18"/>
+      <c r="W44" s="17"/>
+      <c r="X44" s="17"/>
+      <c r="Y44" s="17"/>
+      <c r="Z44" s="17"/>
+      <c r="AA44" s="17"/>
       <c r="AB44" s="13" t="s">
         <v>20</v>
       </c>
@@ -15183,31 +15189,31 @@
       <c r="H45" s="10">
         <v>0.254</v>
       </c>
-      <c r="I45" s="12">
-        <v>1</v>
-      </c>
-      <c r="J45" s="12">
+      <c r="I45" s="17">
+        <v>1</v>
+      </c>
+      <c r="J45" s="17">
         <v>6</v>
       </c>
-      <c r="K45" s="12">
+      <c r="K45" s="17">
         <v>6</v>
       </c>
-      <c r="L45" s="12"/>
-      <c r="M45" s="12"/>
-      <c r="N45" s="13"/>
-      <c r="O45" s="13"/>
-      <c r="P45" s="12"/>
-      <c r="Q45" s="12"/>
-      <c r="R45" s="12"/>
-      <c r="S45" s="12"/>
-      <c r="T45" s="12"/>
-      <c r="U45" s="13"/>
-      <c r="V45" s="13"/>
-      <c r="W45" s="12"/>
-      <c r="X45" s="12"/>
-      <c r="Y45" s="12"/>
-      <c r="Z45" s="12"/>
-      <c r="AA45" s="12"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" s="18"/>
+      <c r="O45" s="18"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="17"/>
+      <c r="R45" s="17"/>
+      <c r="S45" s="17"/>
+      <c r="T45" s="17"/>
+      <c r="U45" s="18"/>
+      <c r="V45" s="18"/>
+      <c r="W45" s="17"/>
+      <c r="X45" s="17"/>
+      <c r="Y45" s="17"/>
+      <c r="Z45" s="17"/>
+      <c r="AA45" s="17"/>
       <c r="AB45" s="13" t="s">
         <v>20</v>
       </c>
@@ -15243,45 +15249,45 @@
       <c r="H46" s="10">
         <v>0.254</v>
       </c>
-      <c r="I46" s="12">
+      <c r="I46" s="17">
         <v>26</v>
       </c>
-      <c r="J46" s="12">
-        <v>2</v>
-      </c>
-      <c r="K46" s="12">
-        <v>8</v>
-      </c>
-      <c r="L46" s="12">
+      <c r="J46" s="17">
+        <v>2</v>
+      </c>
+      <c r="K46" s="17">
+        <v>8</v>
+      </c>
+      <c r="L46" s="17">
         <v>6</v>
       </c>
-      <c r="M46" s="12">
-        <v>7</v>
-      </c>
-      <c r="N46" s="10">
-        <v>1</v>
-      </c>
-      <c r="O46" s="10">
+      <c r="M46" s="17">
+        <v>7</v>
+      </c>
+      <c r="N46" s="18">
+        <v>1</v>
+      </c>
+      <c r="O46" s="18">
         <v>0.254</v>
       </c>
-      <c r="P46" s="12">
+      <c r="P46" s="17">
         <v>13</v>
       </c>
-      <c r="Q46" s="12">
+      <c r="Q46" s="17">
         <v>6</v>
       </c>
-      <c r="R46" s="12">
-        <v>8</v>
-      </c>
-      <c r="S46" s="12"/>
-      <c r="T46" s="12"/>
-      <c r="U46" s="13"/>
-      <c r="V46" s="13"/>
-      <c r="W46" s="12"/>
-      <c r="X46" s="12"/>
-      <c r="Y46" s="12"/>
-      <c r="Z46" s="12"/>
-      <c r="AA46" s="12"/>
+      <c r="R46" s="17">
+        <v>8</v>
+      </c>
+      <c r="S46" s="17"/>
+      <c r="T46" s="17"/>
+      <c r="U46" s="18"/>
+      <c r="V46" s="18"/>
+      <c r="W46" s="17"/>
+      <c r="X46" s="17"/>
+      <c r="Y46" s="17"/>
+      <c r="Z46" s="17"/>
+      <c r="AA46" s="17"/>
       <c r="AB46" s="13" t="s">
         <v>20</v>
       </c>
@@ -15317,45 +15323,45 @@
       <c r="H47" s="10">
         <v>0.254</v>
       </c>
-      <c r="I47" s="12">
+      <c r="I47" s="17">
         <v>5</v>
       </c>
-      <c r="J47" s="12">
+      <c r="J47" s="17">
         <v>5</v>
       </c>
-      <c r="K47" s="12">
-        <v>8</v>
-      </c>
-      <c r="L47" s="12"/>
-      <c r="M47" s="12"/>
-      <c r="N47" s="10">
-        <v>1</v>
-      </c>
-      <c r="O47" s="10">
+      <c r="K47" s="17">
+        <v>8</v>
+      </c>
+      <c r="L47" s="17"/>
+      <c r="M47" s="17"/>
+      <c r="N47" s="18">
+        <v>1</v>
+      </c>
+      <c r="O47" s="18">
         <v>0.254</v>
       </c>
-      <c r="P47" s="12">
+      <c r="P47" s="17">
         <v>5</v>
       </c>
-      <c r="Q47" s="12">
+      <c r="Q47" s="17">
         <v>3</v>
       </c>
-      <c r="R47" s="12">
+      <c r="R47" s="17">
         <v>6</v>
       </c>
-      <c r="S47" s="12">
-        <v>1</v>
-      </c>
-      <c r="T47" s="12">
-        <v>7</v>
-      </c>
-      <c r="U47" s="13"/>
-      <c r="V47" s="13"/>
-      <c r="W47" s="12"/>
-      <c r="X47" s="12"/>
-      <c r="Y47" s="12"/>
-      <c r="Z47" s="12"/>
-      <c r="AA47" s="12"/>
+      <c r="S47" s="17">
+        <v>1</v>
+      </c>
+      <c r="T47" s="17">
+        <v>7</v>
+      </c>
+      <c r="U47" s="18"/>
+      <c r="V47" s="18"/>
+      <c r="W47" s="17"/>
+      <c r="X47" s="17"/>
+      <c r="Y47" s="17"/>
+      <c r="Z47" s="17"/>
+      <c r="AA47" s="17"/>
       <c r="AB47" s="13" t="s">
         <v>20</v>
       </c>
@@ -15391,45 +15397,45 @@
       <c r="H48" s="10">
         <v>0.254</v>
       </c>
-      <c r="I48" s="12">
-        <v>1</v>
-      </c>
-      <c r="J48" s="12">
-        <v>7</v>
-      </c>
-      <c r="K48" s="12">
-        <v>7</v>
-      </c>
-      <c r="L48" s="12">
-        <v>1</v>
-      </c>
-      <c r="M48" s="12">
-        <v>8</v>
-      </c>
-      <c r="N48" s="10">
-        <v>1</v>
-      </c>
-      <c r="O48" s="10">
+      <c r="I48" s="17">
+        <v>1</v>
+      </c>
+      <c r="J48" s="17">
+        <v>7</v>
+      </c>
+      <c r="K48" s="17">
+        <v>7</v>
+      </c>
+      <c r="L48" s="17">
+        <v>1</v>
+      </c>
+      <c r="M48" s="17">
+        <v>8</v>
+      </c>
+      <c r="N48" s="18">
+        <v>1</v>
+      </c>
+      <c r="O48" s="18">
         <v>0.254</v>
       </c>
-      <c r="P48" s="12">
-        <v>1</v>
-      </c>
-      <c r="Q48" s="12">
+      <c r="P48" s="17">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="17">
         <v>6</v>
       </c>
-      <c r="R48" s="12">
+      <c r="R48" s="17">
         <v>6</v>
       </c>
-      <c r="S48" s="12"/>
-      <c r="T48" s="12"/>
-      <c r="U48" s="13"/>
-      <c r="V48" s="13"/>
-      <c r="W48" s="12"/>
-      <c r="X48" s="12"/>
-      <c r="Y48" s="12"/>
-      <c r="Z48" s="12"/>
-      <c r="AA48" s="12"/>
+      <c r="S48" s="17"/>
+      <c r="T48" s="17"/>
+      <c r="U48" s="18"/>
+      <c r="V48" s="18"/>
+      <c r="W48" s="17"/>
+      <c r="X48" s="17"/>
+      <c r="Y48" s="17"/>
+      <c r="Z48" s="17"/>
+      <c r="AA48" s="17"/>
       <c r="AB48" s="13" t="s">
         <v>20</v>
       </c>
@@ -15465,41 +15471,41 @@
       <c r="H49" s="10">
         <v>0.254</v>
       </c>
-      <c r="I49" s="12">
+      <c r="I49" s="17">
         <v>13</v>
       </c>
-      <c r="J49" s="12">
+      <c r="J49" s="17">
         <v>6</v>
       </c>
-      <c r="K49" s="12">
-        <v>8</v>
-      </c>
-      <c r="L49" s="12"/>
-      <c r="M49" s="12"/>
-      <c r="N49" s="10">
-        <v>1</v>
-      </c>
-      <c r="O49" s="10">
+      <c r="K49" s="17">
+        <v>8</v>
+      </c>
+      <c r="L49" s="17"/>
+      <c r="M49" s="17"/>
+      <c r="N49" s="18">
+        <v>1</v>
+      </c>
+      <c r="O49" s="18">
         <v>0.254</v>
       </c>
-      <c r="P49" s="12">
+      <c r="P49" s="17">
         <v>5</v>
       </c>
-      <c r="Q49" s="12">
+      <c r="Q49" s="17">
         <v>5</v>
       </c>
-      <c r="R49" s="12">
-        <v>8</v>
-      </c>
-      <c r="S49" s="12"/>
-      <c r="T49" s="12"/>
-      <c r="U49" s="13"/>
-      <c r="V49" s="13"/>
-      <c r="W49" s="12"/>
-      <c r="X49" s="12"/>
-      <c r="Y49" s="12"/>
-      <c r="Z49" s="12"/>
-      <c r="AA49" s="12"/>
+      <c r="R49" s="17">
+        <v>8</v>
+      </c>
+      <c r="S49" s="17"/>
+      <c r="T49" s="17"/>
+      <c r="U49" s="18"/>
+      <c r="V49" s="18"/>
+      <c r="W49" s="17"/>
+      <c r="X49" s="17"/>
+      <c r="Y49" s="17"/>
+      <c r="Z49" s="17"/>
+      <c r="AA49" s="17"/>
       <c r="AB49" s="13" t="s">
         <v>20</v>
       </c>
@@ -15535,45 +15541,45 @@
       <c r="H50" s="10">
         <v>0.254</v>
       </c>
-      <c r="I50" s="12">
+      <c r="I50" s="17">
         <v>21</v>
       </c>
-      <c r="J50" s="12">
-        <v>7</v>
-      </c>
-      <c r="K50" s="12">
-        <v>8</v>
-      </c>
-      <c r="L50" s="12"/>
-      <c r="M50" s="12"/>
-      <c r="N50" s="10">
-        <v>1</v>
-      </c>
-      <c r="O50" s="10">
+      <c r="J50" s="17">
+        <v>7</v>
+      </c>
+      <c r="K50" s="17">
+        <v>8</v>
+      </c>
+      <c r="L50" s="17"/>
+      <c r="M50" s="17"/>
+      <c r="N50" s="18">
+        <v>1</v>
+      </c>
+      <c r="O50" s="18">
         <v>0.254</v>
       </c>
-      <c r="P50" s="12">
-        <v>7</v>
-      </c>
-      <c r="Q50" s="12">
+      <c r="P50" s="17">
+        <v>7</v>
+      </c>
+      <c r="Q50" s="17">
         <v>6</v>
       </c>
-      <c r="R50" s="12">
-        <v>8</v>
-      </c>
-      <c r="S50" s="12">
-        <v>2</v>
-      </c>
-      <c r="T50" s="12">
-        <v>7</v>
-      </c>
-      <c r="U50" s="13"/>
-      <c r="V50" s="13"/>
-      <c r="W50" s="12"/>
-      <c r="X50" s="12"/>
-      <c r="Y50" s="12"/>
-      <c r="Z50" s="12"/>
-      <c r="AA50" s="12"/>
+      <c r="R50" s="17">
+        <v>8</v>
+      </c>
+      <c r="S50" s="17">
+        <v>2</v>
+      </c>
+      <c r="T50" s="17">
+        <v>7</v>
+      </c>
+      <c r="U50" s="18"/>
+      <c r="V50" s="18"/>
+      <c r="W50" s="17"/>
+      <c r="X50" s="17"/>
+      <c r="Y50" s="17"/>
+      <c r="Z50" s="17"/>
+      <c r="AA50" s="17"/>
       <c r="AB50" s="13" t="s">
         <v>20</v>
       </c>
@@ -15609,41 +15615,41 @@
       <c r="H51" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I51" s="12">
+      <c r="I51" s="17">
         <v>9</v>
       </c>
-      <c r="J51" s="12">
-        <v>7</v>
-      </c>
-      <c r="K51" s="12">
-        <v>8</v>
-      </c>
-      <c r="L51" s="12"/>
-      <c r="M51" s="12"/>
-      <c r="N51" s="10">
-        <v>1</v>
-      </c>
-      <c r="O51" s="10">
+      <c r="J51" s="17">
+        <v>7</v>
+      </c>
+      <c r="K51" s="17">
+        <v>8</v>
+      </c>
+      <c r="L51" s="17"/>
+      <c r="M51" s="17"/>
+      <c r="N51" s="18">
+        <v>1</v>
+      </c>
+      <c r="O51" s="18">
         <v>0.44</v>
       </c>
-      <c r="P51" s="12">
+      <c r="P51" s="17">
         <v>13</v>
       </c>
-      <c r="Q51" s="12">
+      <c r="Q51" s="17">
         <v>3</v>
       </c>
-      <c r="R51" s="12">
-        <v>8</v>
-      </c>
-      <c r="S51" s="12"/>
-      <c r="T51" s="12"/>
-      <c r="U51" s="13"/>
-      <c r="V51" s="13"/>
-      <c r="W51" s="12"/>
-      <c r="X51" s="12"/>
-      <c r="Y51" s="12"/>
-      <c r="Z51" s="12"/>
-      <c r="AA51" s="12"/>
+      <c r="R51" s="17">
+        <v>8</v>
+      </c>
+      <c r="S51" s="17"/>
+      <c r="T51" s="17"/>
+      <c r="U51" s="18"/>
+      <c r="V51" s="18"/>
+      <c r="W51" s="17"/>
+      <c r="X51" s="17"/>
+      <c r="Y51" s="17"/>
+      <c r="Z51" s="17"/>
+      <c r="AA51" s="17"/>
       <c r="AB51" s="13" t="s">
         <v>20</v>
       </c>
@@ -15679,31 +15685,31 @@
       <c r="H52" s="10">
         <v>0.254</v>
       </c>
-      <c r="I52" s="12">
-        <v>1</v>
-      </c>
-      <c r="J52" s="12">
+      <c r="I52" s="17">
+        <v>1</v>
+      </c>
+      <c r="J52" s="17">
         <v>6</v>
       </c>
-      <c r="K52" s="12">
+      <c r="K52" s="17">
         <v>6</v>
       </c>
-      <c r="L52" s="12"/>
-      <c r="M52" s="12"/>
-      <c r="N52" s="13"/>
-      <c r="O52" s="13"/>
-      <c r="P52" s="12"/>
-      <c r="Q52" s="12"/>
-      <c r="R52" s="12"/>
-      <c r="S52" s="12"/>
-      <c r="T52" s="12"/>
-      <c r="U52" s="13"/>
-      <c r="V52" s="13"/>
-      <c r="W52" s="12"/>
-      <c r="X52" s="12"/>
-      <c r="Y52" s="12"/>
-      <c r="Z52" s="12"/>
-      <c r="AA52" s="12"/>
+      <c r="L52" s="17"/>
+      <c r="M52" s="17"/>
+      <c r="N52" s="18"/>
+      <c r="O52" s="18"/>
+      <c r="P52" s="17"/>
+      <c r="Q52" s="17"/>
+      <c r="R52" s="17"/>
+      <c r="S52" s="17"/>
+      <c r="T52" s="17"/>
+      <c r="U52" s="18"/>
+      <c r="V52" s="18"/>
+      <c r="W52" s="17"/>
+      <c r="X52" s="17"/>
+      <c r="Y52" s="17"/>
+      <c r="Z52" s="17"/>
+      <c r="AA52" s="17"/>
       <c r="AB52" s="13" t="s">
         <v>20</v>
       </c>
@@ -15739,35 +15745,35 @@
       <c r="H53" s="10">
         <v>0.254</v>
       </c>
-      <c r="I53" s="12">
-        <v>1</v>
-      </c>
-      <c r="J53" s="12">
-        <v>7</v>
-      </c>
-      <c r="K53" s="12">
-        <v>7</v>
-      </c>
-      <c r="L53" s="12">
-        <v>1</v>
-      </c>
-      <c r="M53" s="12">
-        <v>8</v>
-      </c>
-      <c r="N53" s="13"/>
-      <c r="O53" s="13"/>
-      <c r="P53" s="12"/>
-      <c r="Q53" s="12"/>
-      <c r="R53" s="12"/>
-      <c r="S53" s="12"/>
-      <c r="T53" s="12"/>
-      <c r="U53" s="13"/>
-      <c r="V53" s="13"/>
-      <c r="W53" s="12"/>
-      <c r="X53" s="12"/>
-      <c r="Y53" s="12"/>
-      <c r="Z53" s="12"/>
-      <c r="AA53" s="12"/>
+      <c r="I53" s="17">
+        <v>1</v>
+      </c>
+      <c r="J53" s="17">
+        <v>7</v>
+      </c>
+      <c r="K53" s="17">
+        <v>7</v>
+      </c>
+      <c r="L53" s="17">
+        <v>1</v>
+      </c>
+      <c r="M53" s="17">
+        <v>8</v>
+      </c>
+      <c r="N53" s="18"/>
+      <c r="O53" s="18"/>
+      <c r="P53" s="17"/>
+      <c r="Q53" s="17"/>
+      <c r="R53" s="17"/>
+      <c r="S53" s="17"/>
+      <c r="T53" s="17"/>
+      <c r="U53" s="18"/>
+      <c r="V53" s="18"/>
+      <c r="W53" s="17"/>
+      <c r="X53" s="17"/>
+      <c r="Y53" s="17"/>
+      <c r="Z53" s="17"/>
+      <c r="AA53" s="17"/>
       <c r="AB53" s="13" t="s">
         <v>20</v>
       </c>
@@ -15803,31 +15809,31 @@
       <c r="H54" s="10">
         <v>0.254</v>
       </c>
-      <c r="I54" s="12">
+      <c r="I54" s="17">
         <v>13</v>
       </c>
-      <c r="J54" s="12">
+      <c r="J54" s="17">
         <v>6</v>
       </c>
-      <c r="K54" s="12">
-        <v>8</v>
-      </c>
-      <c r="L54" s="12"/>
-      <c r="M54" s="12"/>
-      <c r="N54" s="13"/>
-      <c r="O54" s="13"/>
-      <c r="P54" s="12"/>
-      <c r="Q54" s="12"/>
-      <c r="R54" s="12"/>
-      <c r="S54" s="12"/>
-      <c r="T54" s="12"/>
-      <c r="U54" s="13"/>
-      <c r="V54" s="13"/>
-      <c r="W54" s="12"/>
-      <c r="X54" s="12"/>
-      <c r="Y54" s="12"/>
-      <c r="Z54" s="12"/>
-      <c r="AA54" s="12"/>
+      <c r="K54" s="17">
+        <v>8</v>
+      </c>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="18"/>
+      <c r="O54" s="18"/>
+      <c r="P54" s="17"/>
+      <c r="Q54" s="17"/>
+      <c r="R54" s="17"/>
+      <c r="S54" s="17"/>
+      <c r="T54" s="17"/>
+      <c r="U54" s="18"/>
+      <c r="V54" s="18"/>
+      <c r="W54" s="17"/>
+      <c r="X54" s="17"/>
+      <c r="Y54" s="17"/>
+      <c r="Z54" s="17"/>
+      <c r="AA54" s="17"/>
       <c r="AB54" s="13" t="s">
         <v>20</v>
       </c>
@@ -15863,35 +15869,35 @@
       <c r="H55" s="10">
         <v>0.254</v>
       </c>
-      <c r="I55" s="12">
-        <v>1</v>
-      </c>
-      <c r="J55" s="12">
-        <v>2</v>
-      </c>
-      <c r="K55" s="12">
-        <v>7</v>
-      </c>
-      <c r="L55" s="12">
-        <v>2</v>
-      </c>
-      <c r="M55" s="12">
+      <c r="I55" s="17">
+        <v>1</v>
+      </c>
+      <c r="J55" s="17">
+        <v>2</v>
+      </c>
+      <c r="K55" s="17">
+        <v>7</v>
+      </c>
+      <c r="L55" s="17">
+        <v>2</v>
+      </c>
+      <c r="M55" s="17">
         <v>6</v>
       </c>
-      <c r="N55" s="13"/>
-      <c r="O55" s="13"/>
-      <c r="P55" s="12"/>
-      <c r="Q55" s="12"/>
-      <c r="R55" s="12"/>
-      <c r="S55" s="12"/>
-      <c r="T55" s="12"/>
-      <c r="U55" s="13"/>
-      <c r="V55" s="13"/>
-      <c r="W55" s="12"/>
-      <c r="X55" s="12"/>
-      <c r="Y55" s="12"/>
-      <c r="Z55" s="12"/>
-      <c r="AA55" s="12"/>
+      <c r="N55" s="18"/>
+      <c r="O55" s="18"/>
+      <c r="P55" s="17"/>
+      <c r="Q55" s="17"/>
+      <c r="R55" s="17"/>
+      <c r="S55" s="17"/>
+      <c r="T55" s="17"/>
+      <c r="U55" s="18"/>
+      <c r="V55" s="18"/>
+      <c r="W55" s="17"/>
+      <c r="X55" s="17"/>
+      <c r="Y55" s="17"/>
+      <c r="Z55" s="17"/>
+      <c r="AA55" s="17"/>
       <c r="AB55" s="13" t="s">
         <v>20</v>
       </c>
@@ -15927,35 +15933,35 @@
       <c r="H56" s="10">
         <v>0.254</v>
       </c>
-      <c r="I56" s="12">
-        <v>1</v>
-      </c>
-      <c r="J56" s="12">
-        <v>2</v>
-      </c>
-      <c r="K56" s="12">
-        <v>8</v>
-      </c>
-      <c r="L56" s="12">
-        <v>1</v>
-      </c>
-      <c r="M56" s="12">
-        <v>7</v>
-      </c>
-      <c r="N56" s="13"/>
-      <c r="O56" s="13"/>
-      <c r="P56" s="12"/>
-      <c r="Q56" s="12"/>
-      <c r="R56" s="12"/>
-      <c r="S56" s="12"/>
-      <c r="T56" s="12"/>
-      <c r="U56" s="13"/>
-      <c r="V56" s="13"/>
-      <c r="W56" s="12"/>
-      <c r="X56" s="12"/>
-      <c r="Y56" s="12"/>
-      <c r="Z56" s="12"/>
-      <c r="AA56" s="12"/>
+      <c r="I56" s="17">
+        <v>1</v>
+      </c>
+      <c r="J56" s="17">
+        <v>2</v>
+      </c>
+      <c r="K56" s="17">
+        <v>8</v>
+      </c>
+      <c r="L56" s="17">
+        <v>1</v>
+      </c>
+      <c r="M56" s="17">
+        <v>7</v>
+      </c>
+      <c r="N56" s="18"/>
+      <c r="O56" s="18"/>
+      <c r="P56" s="17"/>
+      <c r="Q56" s="17"/>
+      <c r="R56" s="17"/>
+      <c r="S56" s="17"/>
+      <c r="T56" s="17"/>
+      <c r="U56" s="18"/>
+      <c r="V56" s="18"/>
+      <c r="W56" s="17"/>
+      <c r="X56" s="17"/>
+      <c r="Y56" s="17"/>
+      <c r="Z56" s="17"/>
+      <c r="AA56" s="17"/>
       <c r="AB56" s="13" t="s">
         <v>20</v>
       </c>
@@ -15991,35 +15997,35 @@
       <c r="H57" s="10">
         <v>0.254</v>
       </c>
-      <c r="I57" s="12">
-        <v>1</v>
-      </c>
-      <c r="J57" s="12">
-        <v>2</v>
-      </c>
-      <c r="K57" s="12">
-        <v>7</v>
-      </c>
-      <c r="L57" s="12">
-        <v>2</v>
-      </c>
-      <c r="M57" s="12">
+      <c r="I57" s="17">
+        <v>1</v>
+      </c>
+      <c r="J57" s="17">
+        <v>2</v>
+      </c>
+      <c r="K57" s="17">
+        <v>7</v>
+      </c>
+      <c r="L57" s="17">
+        <v>2</v>
+      </c>
+      <c r="M57" s="17">
         <v>6</v>
       </c>
-      <c r="N57" s="13"/>
-      <c r="O57" s="13"/>
-      <c r="P57" s="12"/>
-      <c r="Q57" s="12"/>
-      <c r="R57" s="12"/>
-      <c r="S57" s="12"/>
-      <c r="T57" s="12"/>
-      <c r="U57" s="13"/>
-      <c r="V57" s="13"/>
-      <c r="W57" s="12"/>
-      <c r="X57" s="12"/>
-      <c r="Y57" s="12"/>
-      <c r="Z57" s="12"/>
-      <c r="AA57" s="12"/>
+      <c r="N57" s="18"/>
+      <c r="O57" s="18"/>
+      <c r="P57" s="17"/>
+      <c r="Q57" s="17"/>
+      <c r="R57" s="17"/>
+      <c r="S57" s="17"/>
+      <c r="T57" s="17"/>
+      <c r="U57" s="18"/>
+      <c r="V57" s="18"/>
+      <c r="W57" s="17"/>
+      <c r="X57" s="17"/>
+      <c r="Y57" s="17"/>
+      <c r="Z57" s="17"/>
+      <c r="AA57" s="17"/>
       <c r="AB57" s="13" t="s">
         <v>20</v>
       </c>
@@ -16055,35 +16061,35 @@
       <c r="H58" s="10">
         <v>0.254</v>
       </c>
-      <c r="I58" s="12">
-        <v>1</v>
-      </c>
-      <c r="J58" s="12">
-        <v>2</v>
-      </c>
-      <c r="K58" s="12">
-        <v>8</v>
-      </c>
-      <c r="L58" s="12">
-        <v>1</v>
-      </c>
-      <c r="M58" s="12">
-        <v>7</v>
-      </c>
-      <c r="N58" s="13"/>
-      <c r="O58" s="13"/>
-      <c r="P58" s="12"/>
-      <c r="Q58" s="12"/>
-      <c r="R58" s="12"/>
-      <c r="S58" s="12"/>
-      <c r="T58" s="12"/>
-      <c r="U58" s="13"/>
-      <c r="V58" s="13"/>
-      <c r="W58" s="12"/>
-      <c r="X58" s="12"/>
-      <c r="Y58" s="12"/>
-      <c r="Z58" s="12"/>
-      <c r="AA58" s="12"/>
+      <c r="I58" s="17">
+        <v>1</v>
+      </c>
+      <c r="J58" s="17">
+        <v>2</v>
+      </c>
+      <c r="K58" s="17">
+        <v>8</v>
+      </c>
+      <c r="L58" s="17">
+        <v>1</v>
+      </c>
+      <c r="M58" s="17">
+        <v>7</v>
+      </c>
+      <c r="N58" s="18"/>
+      <c r="O58" s="18"/>
+      <c r="P58" s="17"/>
+      <c r="Q58" s="17"/>
+      <c r="R58" s="17"/>
+      <c r="S58" s="17"/>
+      <c r="T58" s="17"/>
+      <c r="U58" s="18"/>
+      <c r="V58" s="18"/>
+      <c r="W58" s="17"/>
+      <c r="X58" s="17"/>
+      <c r="Y58" s="17"/>
+      <c r="Z58" s="17"/>
+      <c r="AA58" s="17"/>
       <c r="AB58" s="13" t="s">
         <v>20</v>
       </c>
@@ -16119,35 +16125,35 @@
       <c r="H59" s="10">
         <v>0.254</v>
       </c>
-      <c r="I59" s="12">
-        <v>1</v>
-      </c>
-      <c r="J59" s="12">
-        <v>2</v>
-      </c>
-      <c r="K59" s="12">
-        <v>8</v>
-      </c>
-      <c r="L59" s="12">
-        <v>1</v>
-      </c>
-      <c r="M59" s="12">
-        <v>7</v>
-      </c>
-      <c r="N59" s="13"/>
-      <c r="O59" s="13"/>
-      <c r="P59" s="12"/>
-      <c r="Q59" s="12"/>
-      <c r="R59" s="12"/>
-      <c r="S59" s="12"/>
-      <c r="T59" s="12"/>
-      <c r="U59" s="13"/>
-      <c r="V59" s="13"/>
-      <c r="W59" s="12"/>
-      <c r="X59" s="12"/>
-      <c r="Y59" s="12"/>
-      <c r="Z59" s="12"/>
-      <c r="AA59" s="12"/>
+      <c r="I59" s="17">
+        <v>1</v>
+      </c>
+      <c r="J59" s="17">
+        <v>2</v>
+      </c>
+      <c r="K59" s="17">
+        <v>8</v>
+      </c>
+      <c r="L59" s="17">
+        <v>1</v>
+      </c>
+      <c r="M59" s="17">
+        <v>7</v>
+      </c>
+      <c r="N59" s="18"/>
+      <c r="O59" s="18"/>
+      <c r="P59" s="17"/>
+      <c r="Q59" s="17"/>
+      <c r="R59" s="17"/>
+      <c r="S59" s="17"/>
+      <c r="T59" s="17"/>
+      <c r="U59" s="18"/>
+      <c r="V59" s="18"/>
+      <c r="W59" s="17"/>
+      <c r="X59" s="17"/>
+      <c r="Y59" s="17"/>
+      <c r="Z59" s="17"/>
+      <c r="AA59" s="17"/>
       <c r="AB59" s="13" t="s">
         <v>20</v>
       </c>
@@ -16183,35 +16189,35 @@
       <c r="H60" s="10">
         <v>0.254</v>
       </c>
-      <c r="I60" s="12">
-        <v>1</v>
-      </c>
-      <c r="J60" s="12">
-        <v>2</v>
-      </c>
-      <c r="K60" s="12">
-        <v>8</v>
-      </c>
-      <c r="L60" s="12">
-        <v>1</v>
-      </c>
-      <c r="M60" s="12">
-        <v>7</v>
-      </c>
-      <c r="N60" s="13"/>
-      <c r="O60" s="13"/>
-      <c r="P60" s="12"/>
-      <c r="Q60" s="12"/>
-      <c r="R60" s="12"/>
-      <c r="S60" s="12"/>
-      <c r="T60" s="12"/>
-      <c r="U60" s="13"/>
-      <c r="V60" s="13"/>
-      <c r="W60" s="12"/>
-      <c r="X60" s="12"/>
-      <c r="Y60" s="12"/>
-      <c r="Z60" s="12"/>
-      <c r="AA60" s="12"/>
+      <c r="I60" s="17">
+        <v>1</v>
+      </c>
+      <c r="J60" s="17">
+        <v>2</v>
+      </c>
+      <c r="K60" s="17">
+        <v>8</v>
+      </c>
+      <c r="L60" s="17">
+        <v>1</v>
+      </c>
+      <c r="M60" s="17">
+        <v>7</v>
+      </c>
+      <c r="N60" s="18"/>
+      <c r="O60" s="18"/>
+      <c r="P60" s="17"/>
+      <c r="Q60" s="17"/>
+      <c r="R60" s="17"/>
+      <c r="S60" s="17"/>
+      <c r="T60" s="17"/>
+      <c r="U60" s="18"/>
+      <c r="V60" s="18"/>
+      <c r="W60" s="17"/>
+      <c r="X60" s="17"/>
+      <c r="Y60" s="17"/>
+      <c r="Z60" s="17"/>
+      <c r="AA60" s="17"/>
       <c r="AB60" s="13" t="s">
         <v>20</v>
       </c>
@@ -16247,35 +16253,35 @@
       <c r="H61" s="10">
         <v>0.254</v>
       </c>
-      <c r="I61" s="12">
-        <v>1</v>
-      </c>
-      <c r="J61" s="12">
-        <v>2</v>
-      </c>
-      <c r="K61" s="12">
-        <v>8</v>
-      </c>
-      <c r="L61" s="12">
-        <v>1</v>
-      </c>
-      <c r="M61" s="12">
-        <v>7</v>
-      </c>
-      <c r="N61" s="13"/>
-      <c r="O61" s="13"/>
-      <c r="P61" s="12"/>
-      <c r="Q61" s="12"/>
-      <c r="R61" s="12"/>
-      <c r="S61" s="12"/>
-      <c r="T61" s="12"/>
-      <c r="U61" s="13"/>
-      <c r="V61" s="13"/>
-      <c r="W61" s="12"/>
-      <c r="X61" s="12"/>
-      <c r="Y61" s="12"/>
-      <c r="Z61" s="12"/>
-      <c r="AA61" s="12"/>
+      <c r="I61" s="17">
+        <v>1</v>
+      </c>
+      <c r="J61" s="17">
+        <v>2</v>
+      </c>
+      <c r="K61" s="17">
+        <v>8</v>
+      </c>
+      <c r="L61" s="17">
+        <v>1</v>
+      </c>
+      <c r="M61" s="17">
+        <v>7</v>
+      </c>
+      <c r="N61" s="18"/>
+      <c r="O61" s="18"/>
+      <c r="P61" s="17"/>
+      <c r="Q61" s="17"/>
+      <c r="R61" s="17"/>
+      <c r="S61" s="17"/>
+      <c r="T61" s="17"/>
+      <c r="U61" s="18"/>
+      <c r="V61" s="18"/>
+      <c r="W61" s="17"/>
+      <c r="X61" s="17"/>
+      <c r="Y61" s="17"/>
+      <c r="Z61" s="17"/>
+      <c r="AA61" s="17"/>
       <c r="AB61" s="13" t="s">
         <v>20</v>
       </c>
@@ -16311,35 +16317,35 @@
       <c r="H62" s="10">
         <v>0.254</v>
       </c>
-      <c r="I62" s="12">
-        <v>1</v>
-      </c>
-      <c r="J62" s="12">
-        <v>2</v>
-      </c>
-      <c r="K62" s="12">
-        <v>7</v>
-      </c>
-      <c r="L62" s="12">
-        <v>2</v>
-      </c>
-      <c r="M62" s="12">
+      <c r="I62" s="17">
+        <v>1</v>
+      </c>
+      <c r="J62" s="17">
+        <v>2</v>
+      </c>
+      <c r="K62" s="17">
+        <v>7</v>
+      </c>
+      <c r="L62" s="17">
+        <v>2</v>
+      </c>
+      <c r="M62" s="17">
         <v>6</v>
       </c>
-      <c r="N62" s="13"/>
-      <c r="O62" s="13"/>
-      <c r="P62" s="12"/>
-      <c r="Q62" s="12"/>
-      <c r="R62" s="12"/>
-      <c r="S62" s="12"/>
-      <c r="T62" s="12"/>
-      <c r="U62" s="13"/>
-      <c r="V62" s="13"/>
-      <c r="W62" s="12"/>
-      <c r="X62" s="12"/>
-      <c r="Y62" s="12"/>
-      <c r="Z62" s="12"/>
-      <c r="AA62" s="12"/>
+      <c r="N62" s="18"/>
+      <c r="O62" s="18"/>
+      <c r="P62" s="17"/>
+      <c r="Q62" s="17"/>
+      <c r="R62" s="17"/>
+      <c r="S62" s="17"/>
+      <c r="T62" s="17"/>
+      <c r="U62" s="18"/>
+      <c r="V62" s="18"/>
+      <c r="W62" s="17"/>
+      <c r="X62" s="17"/>
+      <c r="Y62" s="17"/>
+      <c r="Z62" s="17"/>
+      <c r="AA62" s="17"/>
       <c r="AB62" s="13" t="s">
         <v>20</v>
       </c>
@@ -16375,35 +16381,35 @@
       <c r="H63" s="10">
         <v>0.254</v>
       </c>
-      <c r="I63" s="12">
-        <v>1</v>
-      </c>
-      <c r="J63" s="12">
+      <c r="I63" s="17">
+        <v>1</v>
+      </c>
+      <c r="J63" s="17">
         <v>3</v>
       </c>
-      <c r="K63" s="12">
-        <v>8</v>
-      </c>
-      <c r="L63" s="12">
-        <v>2</v>
-      </c>
-      <c r="M63" s="12">
-        <v>7</v>
-      </c>
-      <c r="N63" s="13"/>
-      <c r="O63" s="13"/>
-      <c r="P63" s="12"/>
-      <c r="Q63" s="12"/>
-      <c r="R63" s="12"/>
-      <c r="S63" s="12"/>
-      <c r="T63" s="12"/>
-      <c r="U63" s="13"/>
-      <c r="V63" s="13"/>
-      <c r="W63" s="12"/>
-      <c r="X63" s="12"/>
-      <c r="Y63" s="12"/>
-      <c r="Z63" s="12"/>
-      <c r="AA63" s="12"/>
+      <c r="K63" s="17">
+        <v>8</v>
+      </c>
+      <c r="L63" s="17">
+        <v>2</v>
+      </c>
+      <c r="M63" s="17">
+        <v>7</v>
+      </c>
+      <c r="N63" s="18"/>
+      <c r="O63" s="18"/>
+      <c r="P63" s="17"/>
+      <c r="Q63" s="17"/>
+      <c r="R63" s="17"/>
+      <c r="S63" s="17"/>
+      <c r="T63" s="17"/>
+      <c r="U63" s="18"/>
+      <c r="V63" s="18"/>
+      <c r="W63" s="17"/>
+      <c r="X63" s="17"/>
+      <c r="Y63" s="17"/>
+      <c r="Z63" s="17"/>
+      <c r="AA63" s="17"/>
       <c r="AB63" s="13" t="s">
         <v>20</v>
       </c>
@@ -16439,35 +16445,35 @@
       <c r="H64" s="10">
         <v>0.254</v>
       </c>
-      <c r="I64" s="12">
-        <v>1</v>
-      </c>
-      <c r="J64" s="12">
+      <c r="I64" s="17">
+        <v>1</v>
+      </c>
+      <c r="J64" s="17">
         <v>3</v>
       </c>
-      <c r="K64" s="12">
-        <v>8</v>
-      </c>
-      <c r="L64" s="12">
-        <v>2</v>
-      </c>
-      <c r="M64" s="12">
-        <v>7</v>
-      </c>
-      <c r="N64" s="13"/>
-      <c r="O64" s="13"/>
-      <c r="P64" s="12"/>
-      <c r="Q64" s="12"/>
-      <c r="R64" s="12"/>
-      <c r="S64" s="12"/>
-      <c r="T64" s="12"/>
-      <c r="U64" s="13"/>
-      <c r="V64" s="13"/>
-      <c r="W64" s="12"/>
-      <c r="X64" s="12"/>
-      <c r="Y64" s="12"/>
-      <c r="Z64" s="12"/>
-      <c r="AA64" s="12"/>
+      <c r="K64" s="17">
+        <v>8</v>
+      </c>
+      <c r="L64" s="17">
+        <v>2</v>
+      </c>
+      <c r="M64" s="17">
+        <v>7</v>
+      </c>
+      <c r="N64" s="18"/>
+      <c r="O64" s="18"/>
+      <c r="P64" s="17"/>
+      <c r="Q64" s="17"/>
+      <c r="R64" s="17"/>
+      <c r="S64" s="17"/>
+      <c r="T64" s="17"/>
+      <c r="U64" s="18"/>
+      <c r="V64" s="18"/>
+      <c r="W64" s="17"/>
+      <c r="X64" s="17"/>
+      <c r="Y64" s="17"/>
+      <c r="Z64" s="17"/>
+      <c r="AA64" s="17"/>
       <c r="AB64" s="13" t="s">
         <v>20</v>
       </c>
@@ -16503,35 +16509,35 @@
       <c r="H65" s="10">
         <v>0.254</v>
       </c>
-      <c r="I65" s="12">
-        <v>1</v>
-      </c>
-      <c r="J65" s="12">
+      <c r="I65" s="17">
+        <v>1</v>
+      </c>
+      <c r="J65" s="17">
         <v>3</v>
       </c>
-      <c r="K65" s="12">
-        <v>8</v>
-      </c>
-      <c r="L65" s="12">
-        <v>2</v>
-      </c>
-      <c r="M65" s="12">
-        <v>7</v>
-      </c>
-      <c r="N65" s="13"/>
-      <c r="O65" s="13"/>
-      <c r="P65" s="12"/>
-      <c r="Q65" s="12"/>
-      <c r="R65" s="12"/>
-      <c r="S65" s="12"/>
-      <c r="T65" s="12"/>
-      <c r="U65" s="13"/>
-      <c r="V65" s="13"/>
-      <c r="W65" s="12"/>
-      <c r="X65" s="12"/>
-      <c r="Y65" s="12"/>
-      <c r="Z65" s="12"/>
-      <c r="AA65" s="12"/>
+      <c r="K65" s="17">
+        <v>8</v>
+      </c>
+      <c r="L65" s="17">
+        <v>2</v>
+      </c>
+      <c r="M65" s="17">
+        <v>7</v>
+      </c>
+      <c r="N65" s="18"/>
+      <c r="O65" s="18"/>
+      <c r="P65" s="17"/>
+      <c r="Q65" s="17"/>
+      <c r="R65" s="17"/>
+      <c r="S65" s="17"/>
+      <c r="T65" s="17"/>
+      <c r="U65" s="18"/>
+      <c r="V65" s="18"/>
+      <c r="W65" s="17"/>
+      <c r="X65" s="17"/>
+      <c r="Y65" s="17"/>
+      <c r="Z65" s="17"/>
+      <c r="AA65" s="17"/>
       <c r="AB65" s="13" t="s">
         <v>20</v>
       </c>
@@ -16567,35 +16573,35 @@
       <c r="H66" s="10">
         <v>0.254</v>
       </c>
-      <c r="I66" s="12">
-        <v>1</v>
-      </c>
-      <c r="J66" s="12">
+      <c r="I66" s="17">
+        <v>1</v>
+      </c>
+      <c r="J66" s="17">
         <v>3</v>
       </c>
-      <c r="K66" s="12">
-        <v>8</v>
-      </c>
-      <c r="L66" s="12">
-        <v>2</v>
-      </c>
-      <c r="M66" s="12">
-        <v>7</v>
-      </c>
-      <c r="N66" s="13"/>
-      <c r="O66" s="13"/>
-      <c r="P66" s="12"/>
-      <c r="Q66" s="12"/>
-      <c r="R66" s="12"/>
-      <c r="S66" s="12"/>
-      <c r="T66" s="12"/>
-      <c r="U66" s="13"/>
-      <c r="V66" s="13"/>
-      <c r="W66" s="12"/>
-      <c r="X66" s="12"/>
-      <c r="Y66" s="12"/>
-      <c r="Z66" s="12"/>
-      <c r="AA66" s="12"/>
+      <c r="K66" s="17">
+        <v>8</v>
+      </c>
+      <c r="L66" s="17">
+        <v>2</v>
+      </c>
+      <c r="M66" s="17">
+        <v>7</v>
+      </c>
+      <c r="N66" s="18"/>
+      <c r="O66" s="18"/>
+      <c r="P66" s="17"/>
+      <c r="Q66" s="17"/>
+      <c r="R66" s="17"/>
+      <c r="S66" s="17"/>
+      <c r="T66" s="17"/>
+      <c r="U66" s="18"/>
+      <c r="V66" s="18"/>
+      <c r="W66" s="17"/>
+      <c r="X66" s="17"/>
+      <c r="Y66" s="17"/>
+      <c r="Z66" s="17"/>
+      <c r="AA66" s="17"/>
       <c r="AB66" s="13" t="s">
         <v>20</v>
       </c>
@@ -16631,35 +16637,35 @@
       <c r="H67" s="10">
         <v>0.254</v>
       </c>
-      <c r="I67" s="12">
-        <v>1</v>
-      </c>
-      <c r="J67" s="12">
+      <c r="I67" s="17">
+        <v>1</v>
+      </c>
+      <c r="J67" s="17">
         <v>3</v>
       </c>
-      <c r="K67" s="12">
-        <v>8</v>
-      </c>
-      <c r="L67" s="12">
-        <v>2</v>
-      </c>
-      <c r="M67" s="12">
-        <v>7</v>
-      </c>
-      <c r="N67" s="13"/>
-      <c r="O67" s="13"/>
-      <c r="P67" s="12"/>
-      <c r="Q67" s="12"/>
-      <c r="R67" s="12"/>
-      <c r="S67" s="12"/>
-      <c r="T67" s="12"/>
-      <c r="U67" s="13"/>
-      <c r="V67" s="13"/>
-      <c r="W67" s="12"/>
-      <c r="X67" s="12"/>
-      <c r="Y67" s="12"/>
-      <c r="Z67" s="12"/>
-      <c r="AA67" s="12"/>
+      <c r="K67" s="17">
+        <v>8</v>
+      </c>
+      <c r="L67" s="17">
+        <v>2</v>
+      </c>
+      <c r="M67" s="17">
+        <v>7</v>
+      </c>
+      <c r="N67" s="18"/>
+      <c r="O67" s="18"/>
+      <c r="P67" s="17"/>
+      <c r="Q67" s="17"/>
+      <c r="R67" s="17"/>
+      <c r="S67" s="17"/>
+      <c r="T67" s="17"/>
+      <c r="U67" s="18"/>
+      <c r="V67" s="18"/>
+      <c r="W67" s="17"/>
+      <c r="X67" s="17"/>
+      <c r="Y67" s="17"/>
+      <c r="Z67" s="17"/>
+      <c r="AA67" s="17"/>
       <c r="AB67" s="13" t="s">
         <v>20</v>
       </c>
@@ -16695,35 +16701,35 @@
       <c r="H68" s="10">
         <v>0.254</v>
       </c>
-      <c r="I68" s="12">
-        <v>1</v>
-      </c>
-      <c r="J68" s="12">
+      <c r="I68" s="17">
+        <v>1</v>
+      </c>
+      <c r="J68" s="17">
         <v>3</v>
       </c>
-      <c r="K68" s="12">
-        <v>8</v>
-      </c>
-      <c r="L68" s="12">
-        <v>2</v>
-      </c>
-      <c r="M68" s="12">
-        <v>7</v>
-      </c>
-      <c r="N68" s="13"/>
-      <c r="O68" s="13"/>
-      <c r="P68" s="12"/>
-      <c r="Q68" s="12"/>
-      <c r="R68" s="12"/>
-      <c r="S68" s="12"/>
-      <c r="T68" s="12"/>
-      <c r="U68" s="13"/>
-      <c r="V68" s="13"/>
-      <c r="W68" s="12"/>
-      <c r="X68" s="12"/>
-      <c r="Y68" s="12"/>
-      <c r="Z68" s="12"/>
-      <c r="AA68" s="12"/>
+      <c r="K68" s="17">
+        <v>8</v>
+      </c>
+      <c r="L68" s="17">
+        <v>2</v>
+      </c>
+      <c r="M68" s="17">
+        <v>7</v>
+      </c>
+      <c r="N68" s="18"/>
+      <c r="O68" s="18"/>
+      <c r="P68" s="17"/>
+      <c r="Q68" s="17"/>
+      <c r="R68" s="17"/>
+      <c r="S68" s="17"/>
+      <c r="T68" s="17"/>
+      <c r="U68" s="18"/>
+      <c r="V68" s="18"/>
+      <c r="W68" s="17"/>
+      <c r="X68" s="17"/>
+      <c r="Y68" s="17"/>
+      <c r="Z68" s="17"/>
+      <c r="AA68" s="17"/>
       <c r="AB68" s="13" t="s">
         <v>20</v>
       </c>
@@ -16759,35 +16765,35 @@
       <c r="H69" s="10">
         <v>0.254</v>
       </c>
-      <c r="I69" s="12">
-        <v>1</v>
-      </c>
-      <c r="J69" s="12">
+      <c r="I69" s="17">
+        <v>1</v>
+      </c>
+      <c r="J69" s="17">
         <v>3</v>
       </c>
-      <c r="K69" s="12">
-        <v>8</v>
-      </c>
-      <c r="L69" s="12">
-        <v>2</v>
-      </c>
-      <c r="M69" s="12">
-        <v>7</v>
-      </c>
-      <c r="N69" s="13"/>
-      <c r="O69" s="13"/>
-      <c r="P69" s="12"/>
-      <c r="Q69" s="12"/>
-      <c r="R69" s="12"/>
-      <c r="S69" s="12"/>
-      <c r="T69" s="12"/>
-      <c r="U69" s="13"/>
-      <c r="V69" s="13"/>
-      <c r="W69" s="12"/>
-      <c r="X69" s="12"/>
-      <c r="Y69" s="12"/>
-      <c r="Z69" s="12"/>
-      <c r="AA69" s="12"/>
+      <c r="K69" s="17">
+        <v>8</v>
+      </c>
+      <c r="L69" s="17">
+        <v>2</v>
+      </c>
+      <c r="M69" s="17">
+        <v>7</v>
+      </c>
+      <c r="N69" s="18"/>
+      <c r="O69" s="18"/>
+      <c r="P69" s="17"/>
+      <c r="Q69" s="17"/>
+      <c r="R69" s="17"/>
+      <c r="S69" s="17"/>
+      <c r="T69" s="17"/>
+      <c r="U69" s="18"/>
+      <c r="V69" s="18"/>
+      <c r="W69" s="17"/>
+      <c r="X69" s="17"/>
+      <c r="Y69" s="17"/>
+      <c r="Z69" s="17"/>
+      <c r="AA69" s="17"/>
       <c r="AB69" s="13" t="s">
         <v>20</v>
       </c>
@@ -16823,35 +16829,35 @@
       <c r="H70" s="10">
         <v>0.254</v>
       </c>
-      <c r="I70" s="12">
-        <v>1</v>
-      </c>
-      <c r="J70" s="12">
-        <v>2</v>
-      </c>
-      <c r="K70" s="12">
-        <v>8</v>
-      </c>
-      <c r="L70" s="12">
+      <c r="I70" s="17">
+        <v>1</v>
+      </c>
+      <c r="J70" s="17">
+        <v>2</v>
+      </c>
+      <c r="K70" s="17">
+        <v>8</v>
+      </c>
+      <c r="L70" s="17">
         <v>4</v>
       </c>
-      <c r="M70" s="12">
-        <v>7</v>
-      </c>
-      <c r="N70" s="13"/>
-      <c r="O70" s="13"/>
-      <c r="P70" s="12"/>
-      <c r="Q70" s="12"/>
-      <c r="R70" s="12"/>
-      <c r="S70" s="12"/>
-      <c r="T70" s="12"/>
-      <c r="U70" s="13"/>
-      <c r="V70" s="13"/>
-      <c r="W70" s="12"/>
-      <c r="X70" s="12"/>
-      <c r="Y70" s="12"/>
-      <c r="Z70" s="12"/>
-      <c r="AA70" s="12"/>
+      <c r="M70" s="17">
+        <v>7</v>
+      </c>
+      <c r="N70" s="18"/>
+      <c r="O70" s="18"/>
+      <c r="P70" s="17"/>
+      <c r="Q70" s="17"/>
+      <c r="R70" s="17"/>
+      <c r="S70" s="17"/>
+      <c r="T70" s="17"/>
+      <c r="U70" s="18"/>
+      <c r="V70" s="18"/>
+      <c r="W70" s="17"/>
+      <c r="X70" s="17"/>
+      <c r="Y70" s="17"/>
+      <c r="Z70" s="17"/>
+      <c r="AA70" s="17"/>
       <c r="AB70" s="13" t="s">
         <v>20</v>
       </c>
@@ -16887,35 +16893,35 @@
       <c r="H71" s="10">
         <v>0.30399999999999999</v>
       </c>
-      <c r="I71" s="12">
-        <v>1</v>
-      </c>
-      <c r="J71" s="12">
+      <c r="I71" s="17">
+        <v>1</v>
+      </c>
+      <c r="J71" s="17">
         <v>3</v>
       </c>
-      <c r="K71" s="12">
-        <v>8</v>
-      </c>
-      <c r="L71" s="12">
+      <c r="K71" s="17">
+        <v>8</v>
+      </c>
+      <c r="L71" s="17">
         <v>4</v>
       </c>
-      <c r="M71" s="12">
-        <v>7</v>
-      </c>
-      <c r="N71" s="13"/>
-      <c r="O71" s="13"/>
-      <c r="P71" s="12"/>
-      <c r="Q71" s="12"/>
-      <c r="R71" s="12"/>
-      <c r="S71" s="12"/>
-      <c r="T71" s="12"/>
-      <c r="U71" s="13"/>
-      <c r="V71" s="13"/>
-      <c r="W71" s="12"/>
-      <c r="X71" s="12"/>
-      <c r="Y71" s="12"/>
-      <c r="Z71" s="12"/>
-      <c r="AA71" s="12"/>
+      <c r="M71" s="17">
+        <v>7</v>
+      </c>
+      <c r="N71" s="18"/>
+      <c r="O71" s="18"/>
+      <c r="P71" s="17"/>
+      <c r="Q71" s="17"/>
+      <c r="R71" s="17"/>
+      <c r="S71" s="17"/>
+      <c r="T71" s="17"/>
+      <c r="U71" s="18"/>
+      <c r="V71" s="18"/>
+      <c r="W71" s="17"/>
+      <c r="X71" s="17"/>
+      <c r="Y71" s="17"/>
+      <c r="Z71" s="17"/>
+      <c r="AA71" s="17"/>
       <c r="AB71" s="13" t="s">
         <v>20</v>
       </c>
@@ -16951,35 +16957,35 @@
       <c r="H72" s="10">
         <v>0.30399999999999999</v>
       </c>
-      <c r="I72" s="12">
-        <v>1</v>
-      </c>
-      <c r="J72" s="12">
+      <c r="I72" s="17">
+        <v>1</v>
+      </c>
+      <c r="J72" s="17">
         <v>3</v>
       </c>
-      <c r="K72" s="12">
-        <v>8</v>
-      </c>
-      <c r="L72" s="12">
+      <c r="K72" s="17">
+        <v>8</v>
+      </c>
+      <c r="L72" s="17">
         <v>4</v>
       </c>
-      <c r="M72" s="12">
-        <v>7</v>
-      </c>
-      <c r="N72" s="13"/>
-      <c r="O72" s="13"/>
-      <c r="P72" s="12"/>
-      <c r="Q72" s="12"/>
-      <c r="R72" s="12"/>
-      <c r="S72" s="12"/>
-      <c r="T72" s="12"/>
-      <c r="U72" s="13"/>
-      <c r="V72" s="13"/>
-      <c r="W72" s="12"/>
-      <c r="X72" s="12"/>
-      <c r="Y72" s="12"/>
-      <c r="Z72" s="12"/>
-      <c r="AA72" s="12"/>
+      <c r="M72" s="17">
+        <v>7</v>
+      </c>
+      <c r="N72" s="18"/>
+      <c r="O72" s="18"/>
+      <c r="P72" s="17"/>
+      <c r="Q72" s="17"/>
+      <c r="R72" s="17"/>
+      <c r="S72" s="17"/>
+      <c r="T72" s="17"/>
+      <c r="U72" s="18"/>
+      <c r="V72" s="18"/>
+      <c r="W72" s="17"/>
+      <c r="X72" s="17"/>
+      <c r="Y72" s="17"/>
+      <c r="Z72" s="17"/>
+      <c r="AA72" s="17"/>
       <c r="AB72" s="13" t="s">
         <v>20</v>
       </c>
@@ -17015,31 +17021,31 @@
       <c r="H73" s="10">
         <v>0.254</v>
       </c>
-      <c r="I73" s="12">
-        <v>7</v>
-      </c>
-      <c r="J73" s="12">
-        <v>2</v>
-      </c>
-      <c r="K73" s="12">
-        <v>8</v>
-      </c>
-      <c r="L73" s="12"/>
-      <c r="M73" s="12"/>
-      <c r="N73" s="13"/>
-      <c r="O73" s="13"/>
-      <c r="P73" s="12"/>
-      <c r="Q73" s="12"/>
-      <c r="R73" s="12"/>
-      <c r="S73" s="12"/>
-      <c r="T73" s="12"/>
-      <c r="U73" s="13"/>
-      <c r="V73" s="13"/>
-      <c r="W73" s="12"/>
-      <c r="X73" s="12"/>
-      <c r="Y73" s="12"/>
-      <c r="Z73" s="12"/>
-      <c r="AA73" s="12"/>
+      <c r="I73" s="17">
+        <v>7</v>
+      </c>
+      <c r="J73" s="17">
+        <v>2</v>
+      </c>
+      <c r="K73" s="17">
+        <v>8</v>
+      </c>
+      <c r="L73" s="17"/>
+      <c r="M73" s="17"/>
+      <c r="N73" s="18"/>
+      <c r="O73" s="18"/>
+      <c r="P73" s="17"/>
+      <c r="Q73" s="17"/>
+      <c r="R73" s="17"/>
+      <c r="S73" s="17"/>
+      <c r="T73" s="17"/>
+      <c r="U73" s="18"/>
+      <c r="V73" s="18"/>
+      <c r="W73" s="17"/>
+      <c r="X73" s="17"/>
+      <c r="Y73" s="17"/>
+      <c r="Z73" s="17"/>
+      <c r="AA73" s="17"/>
       <c r="AB73" s="13" t="s">
         <v>20</v>
       </c>
@@ -17075,31 +17081,31 @@
       <c r="H74" s="10">
         <v>0.254</v>
       </c>
-      <c r="I74" s="12">
-        <v>7</v>
-      </c>
-      <c r="J74" s="12">
-        <v>2</v>
-      </c>
-      <c r="K74" s="12">
-        <v>8</v>
-      </c>
-      <c r="L74" s="12"/>
-      <c r="M74" s="12"/>
-      <c r="N74" s="13"/>
-      <c r="O74" s="13"/>
-      <c r="P74" s="12"/>
-      <c r="Q74" s="12"/>
-      <c r="R74" s="12"/>
-      <c r="S74" s="12"/>
-      <c r="T74" s="12"/>
-      <c r="U74" s="13"/>
-      <c r="V74" s="13"/>
-      <c r="W74" s="12"/>
-      <c r="X74" s="12"/>
-      <c r="Y74" s="12"/>
-      <c r="Z74" s="12"/>
-      <c r="AA74" s="12"/>
+      <c r="I74" s="17">
+        <v>7</v>
+      </c>
+      <c r="J74" s="17">
+        <v>2</v>
+      </c>
+      <c r="K74" s="17">
+        <v>8</v>
+      </c>
+      <c r="L74" s="17"/>
+      <c r="M74" s="17"/>
+      <c r="N74" s="18"/>
+      <c r="O74" s="18"/>
+      <c r="P74" s="17"/>
+      <c r="Q74" s="17"/>
+      <c r="R74" s="17"/>
+      <c r="S74" s="17"/>
+      <c r="T74" s="17"/>
+      <c r="U74" s="18"/>
+      <c r="V74" s="18"/>
+      <c r="W74" s="17"/>
+      <c r="X74" s="17"/>
+      <c r="Y74" s="17"/>
+      <c r="Z74" s="17"/>
+      <c r="AA74" s="17"/>
       <c r="AB74" s="13" t="s">
         <v>20</v>
       </c>
@@ -17135,31 +17141,31 @@
       <c r="H75" s="10">
         <v>0.254</v>
       </c>
-      <c r="I75" s="12">
-        <v>1</v>
-      </c>
-      <c r="J75" s="12">
+      <c r="I75" s="17">
+        <v>1</v>
+      </c>
+      <c r="J75" s="17">
         <v>4</v>
       </c>
-      <c r="K75" s="12">
-        <v>7</v>
-      </c>
-      <c r="L75" s="12"/>
-      <c r="M75" s="12"/>
-      <c r="N75" s="13"/>
-      <c r="O75" s="13"/>
-      <c r="P75" s="12"/>
-      <c r="Q75" s="12"/>
-      <c r="R75" s="12"/>
-      <c r="S75" s="12"/>
-      <c r="T75" s="12"/>
-      <c r="U75" s="13"/>
-      <c r="V75" s="13"/>
-      <c r="W75" s="12"/>
-      <c r="X75" s="12"/>
-      <c r="Y75" s="12"/>
-      <c r="Z75" s="12"/>
-      <c r="AA75" s="12"/>
+      <c r="K75" s="17">
+        <v>7</v>
+      </c>
+      <c r="L75" s="17"/>
+      <c r="M75" s="17"/>
+      <c r="N75" s="18"/>
+      <c r="O75" s="18"/>
+      <c r="P75" s="17"/>
+      <c r="Q75" s="17"/>
+      <c r="R75" s="17"/>
+      <c r="S75" s="17"/>
+      <c r="T75" s="17"/>
+      <c r="U75" s="18"/>
+      <c r="V75" s="18"/>
+      <c r="W75" s="17"/>
+      <c r="X75" s="17"/>
+      <c r="Y75" s="17"/>
+      <c r="Z75" s="17"/>
+      <c r="AA75" s="17"/>
       <c r="AB75" s="13" t="s">
         <v>20</v>
       </c>
@@ -17195,35 +17201,35 @@
       <c r="H76" s="10">
         <v>0.254</v>
       </c>
-      <c r="I76" s="12">
-        <v>1</v>
-      </c>
-      <c r="J76" s="12">
-        <v>2</v>
-      </c>
-      <c r="K76" s="12">
-        <v>8</v>
-      </c>
-      <c r="L76" s="12">
-        <v>1</v>
-      </c>
-      <c r="M76" s="12">
-        <v>7</v>
-      </c>
-      <c r="N76" s="13"/>
-      <c r="O76" s="13"/>
-      <c r="P76" s="12"/>
-      <c r="Q76" s="12"/>
-      <c r="R76" s="12"/>
-      <c r="S76" s="12"/>
-      <c r="T76" s="12"/>
-      <c r="U76" s="13"/>
-      <c r="V76" s="13"/>
-      <c r="W76" s="12"/>
-      <c r="X76" s="12"/>
-      <c r="Y76" s="12"/>
-      <c r="Z76" s="12"/>
-      <c r="AA76" s="12"/>
+      <c r="I76" s="17">
+        <v>1</v>
+      </c>
+      <c r="J76" s="17">
+        <v>2</v>
+      </c>
+      <c r="K76" s="17">
+        <v>8</v>
+      </c>
+      <c r="L76" s="17">
+        <v>1</v>
+      </c>
+      <c r="M76" s="17">
+        <v>7</v>
+      </c>
+      <c r="N76" s="18"/>
+      <c r="O76" s="18"/>
+      <c r="P76" s="17"/>
+      <c r="Q76" s="17"/>
+      <c r="R76" s="17"/>
+      <c r="S76" s="17"/>
+      <c r="T76" s="17"/>
+      <c r="U76" s="18"/>
+      <c r="V76" s="18"/>
+      <c r="W76" s="17"/>
+      <c r="X76" s="17"/>
+      <c r="Y76" s="17"/>
+      <c r="Z76" s="17"/>
+      <c r="AA76" s="17"/>
       <c r="AB76" s="13" t="s">
         <v>20</v>
       </c>
@@ -17259,31 +17265,31 @@
       <c r="H77" s="10">
         <v>0.254</v>
       </c>
-      <c r="I77" s="12">
-        <v>1</v>
-      </c>
-      <c r="J77" s="12">
+      <c r="I77" s="17">
+        <v>1</v>
+      </c>
+      <c r="J77" s="17">
         <v>4</v>
       </c>
-      <c r="K77" s="12">
-        <v>7</v>
-      </c>
-      <c r="L77" s="12"/>
-      <c r="M77" s="12"/>
-      <c r="N77" s="13"/>
-      <c r="O77" s="13"/>
-      <c r="P77" s="12"/>
-      <c r="Q77" s="12"/>
-      <c r="R77" s="12"/>
-      <c r="S77" s="12"/>
-      <c r="T77" s="12"/>
-      <c r="U77" s="13"/>
-      <c r="V77" s="13"/>
-      <c r="W77" s="12"/>
-      <c r="X77" s="12"/>
-      <c r="Y77" s="12"/>
-      <c r="Z77" s="12"/>
-      <c r="AA77" s="12"/>
+      <c r="K77" s="17">
+        <v>7</v>
+      </c>
+      <c r="L77" s="17"/>
+      <c r="M77" s="17"/>
+      <c r="N77" s="18"/>
+      <c r="O77" s="18"/>
+      <c r="P77" s="17"/>
+      <c r="Q77" s="17"/>
+      <c r="R77" s="17"/>
+      <c r="S77" s="17"/>
+      <c r="T77" s="17"/>
+      <c r="U77" s="18"/>
+      <c r="V77" s="18"/>
+      <c r="W77" s="17"/>
+      <c r="X77" s="17"/>
+      <c r="Y77" s="17"/>
+      <c r="Z77" s="17"/>
+      <c r="AA77" s="17"/>
       <c r="AB77" s="13" t="s">
         <v>20</v>
       </c>
@@ -17319,35 +17325,35 @@
       <c r="H78" s="10">
         <v>0.254</v>
       </c>
-      <c r="I78" s="12">
-        <v>1</v>
-      </c>
-      <c r="J78" s="12">
-        <v>2</v>
-      </c>
-      <c r="K78" s="12">
-        <v>8</v>
-      </c>
-      <c r="L78" s="12">
-        <v>1</v>
-      </c>
-      <c r="M78" s="12">
-        <v>7</v>
-      </c>
-      <c r="N78" s="13"/>
-      <c r="O78" s="13"/>
-      <c r="P78" s="12"/>
-      <c r="Q78" s="12"/>
-      <c r="R78" s="12"/>
-      <c r="S78" s="12"/>
-      <c r="T78" s="12"/>
-      <c r="U78" s="13"/>
-      <c r="V78" s="13"/>
-      <c r="W78" s="12"/>
-      <c r="X78" s="12"/>
-      <c r="Y78" s="12"/>
-      <c r="Z78" s="12"/>
-      <c r="AA78" s="12"/>
+      <c r="I78" s="17">
+        <v>1</v>
+      </c>
+      <c r="J78" s="17">
+        <v>2</v>
+      </c>
+      <c r="K78" s="17">
+        <v>8</v>
+      </c>
+      <c r="L78" s="17">
+        <v>1</v>
+      </c>
+      <c r="M78" s="17">
+        <v>7</v>
+      </c>
+      <c r="N78" s="18"/>
+      <c r="O78" s="18"/>
+      <c r="P78" s="17"/>
+      <c r="Q78" s="17"/>
+      <c r="R78" s="17"/>
+      <c r="S78" s="17"/>
+      <c r="T78" s="17"/>
+      <c r="U78" s="18"/>
+      <c r="V78" s="18"/>
+      <c r="W78" s="17"/>
+      <c r="X78" s="17"/>
+      <c r="Y78" s="17"/>
+      <c r="Z78" s="17"/>
+      <c r="AA78" s="17"/>
       <c r="AB78" s="13" t="s">
         <v>20</v>
       </c>
@@ -17383,35 +17389,35 @@
       <c r="H79" s="10">
         <v>0.254</v>
       </c>
-      <c r="I79" s="12">
-        <v>1</v>
-      </c>
-      <c r="J79" s="12">
-        <v>2</v>
-      </c>
-      <c r="K79" s="12">
-        <v>8</v>
-      </c>
-      <c r="L79" s="12">
-        <v>1</v>
-      </c>
-      <c r="M79" s="12">
-        <v>7</v>
-      </c>
-      <c r="N79" s="13"/>
-      <c r="O79" s="13"/>
-      <c r="P79" s="12"/>
-      <c r="Q79" s="12"/>
-      <c r="R79" s="12"/>
-      <c r="S79" s="12"/>
-      <c r="T79" s="12"/>
-      <c r="U79" s="13"/>
-      <c r="V79" s="13"/>
-      <c r="W79" s="12"/>
-      <c r="X79" s="12"/>
-      <c r="Y79" s="12"/>
-      <c r="Z79" s="12"/>
-      <c r="AA79" s="12"/>
+      <c r="I79" s="17">
+        <v>1</v>
+      </c>
+      <c r="J79" s="17">
+        <v>2</v>
+      </c>
+      <c r="K79" s="17">
+        <v>8</v>
+      </c>
+      <c r="L79" s="17">
+        <v>1</v>
+      </c>
+      <c r="M79" s="17">
+        <v>7</v>
+      </c>
+      <c r="N79" s="18"/>
+      <c r="O79" s="18"/>
+      <c r="P79" s="17"/>
+      <c r="Q79" s="17"/>
+      <c r="R79" s="17"/>
+      <c r="S79" s="17"/>
+      <c r="T79" s="17"/>
+      <c r="U79" s="18"/>
+      <c r="V79" s="18"/>
+      <c r="W79" s="17"/>
+      <c r="X79" s="17"/>
+      <c r="Y79" s="17"/>
+      <c r="Z79" s="17"/>
+      <c r="AA79" s="17"/>
       <c r="AB79" s="13" t="s">
         <v>20</v>
       </c>
@@ -17447,35 +17453,35 @@
       <c r="H80" s="10">
         <v>0.254</v>
       </c>
-      <c r="I80" s="12">
-        <v>1</v>
-      </c>
-      <c r="J80" s="12">
-        <v>2</v>
-      </c>
-      <c r="K80" s="12">
-        <v>8</v>
-      </c>
-      <c r="L80" s="12">
-        <v>1</v>
-      </c>
-      <c r="M80" s="12">
-        <v>7</v>
-      </c>
-      <c r="N80" s="13"/>
-      <c r="O80" s="13"/>
-      <c r="P80" s="12"/>
-      <c r="Q80" s="12"/>
-      <c r="R80" s="12"/>
-      <c r="S80" s="12"/>
-      <c r="T80" s="12"/>
-      <c r="U80" s="13"/>
-      <c r="V80" s="13"/>
-      <c r="W80" s="12"/>
-      <c r="X80" s="12"/>
-      <c r="Y80" s="12"/>
-      <c r="Z80" s="12"/>
-      <c r="AA80" s="12"/>
+      <c r="I80" s="17">
+        <v>1</v>
+      </c>
+      <c r="J80" s="17">
+        <v>2</v>
+      </c>
+      <c r="K80" s="17">
+        <v>8</v>
+      </c>
+      <c r="L80" s="17">
+        <v>1</v>
+      </c>
+      <c r="M80" s="17">
+        <v>7</v>
+      </c>
+      <c r="N80" s="18"/>
+      <c r="O80" s="18"/>
+      <c r="P80" s="17"/>
+      <c r="Q80" s="17"/>
+      <c r="R80" s="17"/>
+      <c r="S80" s="17"/>
+      <c r="T80" s="17"/>
+      <c r="U80" s="18"/>
+      <c r="V80" s="18"/>
+      <c r="W80" s="17"/>
+      <c r="X80" s="17"/>
+      <c r="Y80" s="17"/>
+      <c r="Z80" s="17"/>
+      <c r="AA80" s="17"/>
       <c r="AB80" s="13" t="s">
         <v>20</v>
       </c>
@@ -17511,35 +17517,35 @@
       <c r="H81" s="10">
         <v>0.254</v>
       </c>
-      <c r="I81" s="12">
-        <v>1</v>
-      </c>
-      <c r="J81" s="12">
-        <v>2</v>
-      </c>
-      <c r="K81" s="12">
-        <v>7</v>
-      </c>
-      <c r="L81" s="12">
-        <v>2</v>
-      </c>
-      <c r="M81" s="12">
+      <c r="I81" s="17">
+        <v>1</v>
+      </c>
+      <c r="J81" s="17">
+        <v>2</v>
+      </c>
+      <c r="K81" s="17">
+        <v>7</v>
+      </c>
+      <c r="L81" s="17">
+        <v>2</v>
+      </c>
+      <c r="M81" s="17">
         <v>6</v>
       </c>
-      <c r="N81" s="13"/>
-      <c r="O81" s="13"/>
-      <c r="P81" s="12"/>
-      <c r="Q81" s="12"/>
-      <c r="R81" s="12"/>
-      <c r="S81" s="12"/>
-      <c r="T81" s="12"/>
-      <c r="U81" s="13"/>
-      <c r="V81" s="13"/>
-      <c r="W81" s="12"/>
-      <c r="X81" s="12"/>
-      <c r="Y81" s="12"/>
-      <c r="Z81" s="12"/>
-      <c r="AA81" s="12"/>
+      <c r="N81" s="18"/>
+      <c r="O81" s="18"/>
+      <c r="P81" s="17"/>
+      <c r="Q81" s="17"/>
+      <c r="R81" s="17"/>
+      <c r="S81" s="17"/>
+      <c r="T81" s="17"/>
+      <c r="U81" s="18"/>
+      <c r="V81" s="18"/>
+      <c r="W81" s="17"/>
+      <c r="X81" s="17"/>
+      <c r="Y81" s="17"/>
+      <c r="Z81" s="17"/>
+      <c r="AA81" s="17"/>
       <c r="AB81" s="13" t="s">
         <v>20</v>
       </c>
@@ -17575,35 +17581,35 @@
       <c r="H82" s="10">
         <v>0.254</v>
       </c>
-      <c r="I82" s="12">
-        <v>1</v>
-      </c>
-      <c r="J82" s="12">
+      <c r="I82" s="17">
+        <v>1</v>
+      </c>
+      <c r="J82" s="17">
         <v>5</v>
       </c>
-      <c r="K82" s="12">
-        <v>8</v>
-      </c>
-      <c r="L82" s="12">
-        <v>1</v>
-      </c>
-      <c r="M82" s="12">
-        <v>7</v>
-      </c>
-      <c r="N82" s="13"/>
-      <c r="O82" s="13"/>
-      <c r="P82" s="12"/>
-      <c r="Q82" s="12"/>
-      <c r="R82" s="12"/>
-      <c r="S82" s="12"/>
-      <c r="T82" s="12"/>
-      <c r="U82" s="13"/>
-      <c r="V82" s="13"/>
-      <c r="W82" s="12"/>
-      <c r="X82" s="12"/>
-      <c r="Y82" s="12"/>
-      <c r="Z82" s="12"/>
-      <c r="AA82" s="12"/>
+      <c r="K82" s="17">
+        <v>8</v>
+      </c>
+      <c r="L82" s="17">
+        <v>1</v>
+      </c>
+      <c r="M82" s="17">
+        <v>7</v>
+      </c>
+      <c r="N82" s="18"/>
+      <c r="O82" s="18"/>
+      <c r="P82" s="17"/>
+      <c r="Q82" s="17"/>
+      <c r="R82" s="17"/>
+      <c r="S82" s="17"/>
+      <c r="T82" s="17"/>
+      <c r="U82" s="18"/>
+      <c r="V82" s="18"/>
+      <c r="W82" s="17"/>
+      <c r="X82" s="17"/>
+      <c r="Y82" s="17"/>
+      <c r="Z82" s="17"/>
+      <c r="AA82" s="17"/>
       <c r="AB82" s="13" t="s">
         <v>20</v>
       </c>
@@ -17639,35 +17645,35 @@
       <c r="H83" s="10">
         <v>0.254</v>
       </c>
-      <c r="I83" s="12">
-        <v>1</v>
-      </c>
-      <c r="J83" s="12">
+      <c r="I83" s="17">
+        <v>1</v>
+      </c>
+      <c r="J83" s="17">
         <v>3</v>
       </c>
-      <c r="K83" s="12">
-        <v>8</v>
-      </c>
-      <c r="L83" s="12">
-        <v>2</v>
-      </c>
-      <c r="M83" s="12">
-        <v>7</v>
-      </c>
-      <c r="N83" s="13"/>
-      <c r="O83" s="13"/>
-      <c r="P83" s="12"/>
-      <c r="Q83" s="12"/>
-      <c r="R83" s="12"/>
-      <c r="S83" s="12"/>
-      <c r="T83" s="12"/>
-      <c r="U83" s="13"/>
-      <c r="V83" s="13"/>
-      <c r="W83" s="12"/>
-      <c r="X83" s="12"/>
-      <c r="Y83" s="12"/>
-      <c r="Z83" s="12"/>
-      <c r="AA83" s="12"/>
+      <c r="K83" s="17">
+        <v>8</v>
+      </c>
+      <c r="L83" s="17">
+        <v>2</v>
+      </c>
+      <c r="M83" s="17">
+        <v>7</v>
+      </c>
+      <c r="N83" s="18"/>
+      <c r="O83" s="18"/>
+      <c r="P83" s="17"/>
+      <c r="Q83" s="17"/>
+      <c r="R83" s="17"/>
+      <c r="S83" s="17"/>
+      <c r="T83" s="17"/>
+      <c r="U83" s="18"/>
+      <c r="V83" s="18"/>
+      <c r="W83" s="17"/>
+      <c r="X83" s="17"/>
+      <c r="Y83" s="17"/>
+      <c r="Z83" s="17"/>
+      <c r="AA83" s="17"/>
       <c r="AB83" s="13" t="s">
         <v>20</v>
       </c>
@@ -17703,35 +17709,35 @@
       <c r="H84" s="10">
         <v>0.254</v>
       </c>
-      <c r="I84" s="12">
-        <v>1</v>
-      </c>
-      <c r="J84" s="12">
+      <c r="I84" s="17">
+        <v>1</v>
+      </c>
+      <c r="J84" s="17">
         <v>5</v>
       </c>
-      <c r="K84" s="12">
-        <v>8</v>
-      </c>
-      <c r="L84" s="12">
-        <v>1</v>
-      </c>
-      <c r="M84" s="12">
-        <v>7</v>
-      </c>
-      <c r="N84" s="13"/>
-      <c r="O84" s="13"/>
-      <c r="P84" s="12"/>
-      <c r="Q84" s="12"/>
-      <c r="R84" s="12"/>
-      <c r="S84" s="12"/>
-      <c r="T84" s="12"/>
-      <c r="U84" s="13"/>
-      <c r="V84" s="13"/>
-      <c r="W84" s="12"/>
-      <c r="X84" s="12"/>
-      <c r="Y84" s="12"/>
-      <c r="Z84" s="12"/>
-      <c r="AA84" s="12"/>
+      <c r="K84" s="17">
+        <v>8</v>
+      </c>
+      <c r="L84" s="17">
+        <v>1</v>
+      </c>
+      <c r="M84" s="17">
+        <v>7</v>
+      </c>
+      <c r="N84" s="18"/>
+      <c r="O84" s="18"/>
+      <c r="P84" s="17"/>
+      <c r="Q84" s="17"/>
+      <c r="R84" s="17"/>
+      <c r="S84" s="17"/>
+      <c r="T84" s="17"/>
+      <c r="U84" s="18"/>
+      <c r="V84" s="18"/>
+      <c r="W84" s="17"/>
+      <c r="X84" s="17"/>
+      <c r="Y84" s="17"/>
+      <c r="Z84" s="17"/>
+      <c r="AA84" s="17"/>
       <c r="AB84" s="13" t="s">
         <v>20</v>
       </c>
@@ -17767,35 +17773,35 @@
       <c r="H85" s="10">
         <v>0.254</v>
       </c>
-      <c r="I85" s="12">
-        <v>1</v>
-      </c>
-      <c r="J85" s="12">
+      <c r="I85" s="17">
+        <v>1</v>
+      </c>
+      <c r="J85" s="17">
         <v>3</v>
       </c>
-      <c r="K85" s="12">
-        <v>8</v>
-      </c>
-      <c r="L85" s="12">
-        <v>2</v>
-      </c>
-      <c r="M85" s="12">
-        <v>7</v>
-      </c>
-      <c r="N85" s="13"/>
-      <c r="O85" s="13"/>
-      <c r="P85" s="12"/>
-      <c r="Q85" s="12"/>
-      <c r="R85" s="12"/>
-      <c r="S85" s="12"/>
-      <c r="T85" s="12"/>
-      <c r="U85" s="13"/>
-      <c r="V85" s="13"/>
-      <c r="W85" s="12"/>
-      <c r="X85" s="12"/>
-      <c r="Y85" s="12"/>
-      <c r="Z85" s="12"/>
-      <c r="AA85" s="12"/>
+      <c r="K85" s="17">
+        <v>8</v>
+      </c>
+      <c r="L85" s="17">
+        <v>2</v>
+      </c>
+      <c r="M85" s="17">
+        <v>7</v>
+      </c>
+      <c r="N85" s="18"/>
+      <c r="O85" s="18"/>
+      <c r="P85" s="17"/>
+      <c r="Q85" s="17"/>
+      <c r="R85" s="17"/>
+      <c r="S85" s="17"/>
+      <c r="T85" s="17"/>
+      <c r="U85" s="18"/>
+      <c r="V85" s="18"/>
+      <c r="W85" s="17"/>
+      <c r="X85" s="17"/>
+      <c r="Y85" s="17"/>
+      <c r="Z85" s="17"/>
+      <c r="AA85" s="17"/>
       <c r="AB85" s="13" t="s">
         <v>20</v>
       </c>
@@ -17831,35 +17837,35 @@
       <c r="H86" s="10">
         <v>0.254</v>
       </c>
-      <c r="I86" s="12">
-        <v>1</v>
-      </c>
-      <c r="J86" s="12">
+      <c r="I86" s="17">
+        <v>1</v>
+      </c>
+      <c r="J86" s="17">
         <v>3</v>
       </c>
-      <c r="K86" s="12">
-        <v>8</v>
-      </c>
-      <c r="L86" s="12">
-        <v>2</v>
-      </c>
-      <c r="M86" s="12">
-        <v>7</v>
-      </c>
-      <c r="N86" s="13"/>
-      <c r="O86" s="13"/>
-      <c r="P86" s="12"/>
-      <c r="Q86" s="12"/>
-      <c r="R86" s="12"/>
-      <c r="S86" s="12"/>
-      <c r="T86" s="12"/>
-      <c r="U86" s="13"/>
-      <c r="V86" s="13"/>
-      <c r="W86" s="12"/>
-      <c r="X86" s="12"/>
-      <c r="Y86" s="12"/>
-      <c r="Z86" s="12"/>
-      <c r="AA86" s="12"/>
+      <c r="K86" s="17">
+        <v>8</v>
+      </c>
+      <c r="L86" s="17">
+        <v>2</v>
+      </c>
+      <c r="M86" s="17">
+        <v>7</v>
+      </c>
+      <c r="N86" s="18"/>
+      <c r="O86" s="18"/>
+      <c r="P86" s="17"/>
+      <c r="Q86" s="17"/>
+      <c r="R86" s="17"/>
+      <c r="S86" s="17"/>
+      <c r="T86" s="17"/>
+      <c r="U86" s="18"/>
+      <c r="V86" s="18"/>
+      <c r="W86" s="17"/>
+      <c r="X86" s="17"/>
+      <c r="Y86" s="17"/>
+      <c r="Z86" s="17"/>
+      <c r="AA86" s="17"/>
       <c r="AB86" s="13" t="s">
         <v>20</v>
       </c>
@@ -17895,35 +17901,35 @@
       <c r="H87" s="10">
         <v>0.254</v>
       </c>
-      <c r="I87" s="12">
-        <v>1</v>
-      </c>
-      <c r="J87" s="12">
-        <v>2</v>
-      </c>
-      <c r="K87" s="12">
-        <v>8</v>
-      </c>
-      <c r="L87" s="12">
+      <c r="I87" s="17">
+        <v>1</v>
+      </c>
+      <c r="J87" s="17">
+        <v>2</v>
+      </c>
+      <c r="K87" s="17">
+        <v>8</v>
+      </c>
+      <c r="L87" s="17">
         <v>4</v>
       </c>
-      <c r="M87" s="12">
-        <v>7</v>
-      </c>
-      <c r="N87" s="13"/>
-      <c r="O87" s="13"/>
-      <c r="P87" s="12"/>
-      <c r="Q87" s="12"/>
-      <c r="R87" s="12"/>
-      <c r="S87" s="12"/>
-      <c r="T87" s="12"/>
-      <c r="U87" s="13"/>
-      <c r="V87" s="13"/>
-      <c r="W87" s="12"/>
-      <c r="X87" s="12"/>
-      <c r="Y87" s="12"/>
-      <c r="Z87" s="12"/>
-      <c r="AA87" s="12"/>
+      <c r="M87" s="17">
+        <v>7</v>
+      </c>
+      <c r="N87" s="18"/>
+      <c r="O87" s="18"/>
+      <c r="P87" s="17"/>
+      <c r="Q87" s="17"/>
+      <c r="R87" s="17"/>
+      <c r="S87" s="17"/>
+      <c r="T87" s="17"/>
+      <c r="U87" s="18"/>
+      <c r="V87" s="18"/>
+      <c r="W87" s="17"/>
+      <c r="X87" s="17"/>
+      <c r="Y87" s="17"/>
+      <c r="Z87" s="17"/>
+      <c r="AA87" s="17"/>
       <c r="AB87" s="13" t="s">
         <v>20</v>
       </c>
@@ -17959,35 +17965,35 @@
       <c r="H88" s="10">
         <v>0.30399999999999999</v>
       </c>
-      <c r="I88" s="12">
-        <v>1</v>
-      </c>
-      <c r="J88" s="12">
+      <c r="I88" s="17">
+        <v>1</v>
+      </c>
+      <c r="J88" s="17">
         <v>3</v>
       </c>
-      <c r="K88" s="12">
-        <v>8</v>
-      </c>
-      <c r="L88" s="12">
+      <c r="K88" s="17">
+        <v>8</v>
+      </c>
+      <c r="L88" s="17">
         <v>4</v>
       </c>
-      <c r="M88" s="12">
-        <v>7</v>
-      </c>
-      <c r="N88" s="13"/>
-      <c r="O88" s="13"/>
-      <c r="P88" s="12"/>
-      <c r="Q88" s="12"/>
-      <c r="R88" s="12"/>
-      <c r="S88" s="12"/>
-      <c r="T88" s="12"/>
-      <c r="U88" s="13"/>
-      <c r="V88" s="13"/>
-      <c r="W88" s="12"/>
-      <c r="X88" s="12"/>
-      <c r="Y88" s="12"/>
-      <c r="Z88" s="12"/>
-      <c r="AA88" s="12"/>
+      <c r="M88" s="17">
+        <v>7</v>
+      </c>
+      <c r="N88" s="18"/>
+      <c r="O88" s="18"/>
+      <c r="P88" s="17"/>
+      <c r="Q88" s="17"/>
+      <c r="R88" s="17"/>
+      <c r="S88" s="17"/>
+      <c r="T88" s="17"/>
+      <c r="U88" s="18"/>
+      <c r="V88" s="18"/>
+      <c r="W88" s="17"/>
+      <c r="X88" s="17"/>
+      <c r="Y88" s="17"/>
+      <c r="Z88" s="17"/>
+      <c r="AA88" s="17"/>
       <c r="AB88" s="13" t="s">
         <v>20</v>
       </c>
@@ -18023,35 +18029,35 @@
       <c r="H89" s="10">
         <v>0.30399999999999999</v>
       </c>
-      <c r="I89" s="12">
-        <v>1</v>
-      </c>
-      <c r="J89" s="12">
+      <c r="I89" s="17">
+        <v>1</v>
+      </c>
+      <c r="J89" s="17">
         <v>3</v>
       </c>
-      <c r="K89" s="12">
-        <v>8</v>
-      </c>
-      <c r="L89" s="12">
+      <c r="K89" s="17">
+        <v>8</v>
+      </c>
+      <c r="L89" s="17">
         <v>4</v>
       </c>
-      <c r="M89" s="12">
-        <v>7</v>
-      </c>
-      <c r="N89" s="13"/>
-      <c r="O89" s="13"/>
-      <c r="P89" s="12"/>
-      <c r="Q89" s="12"/>
-      <c r="R89" s="12"/>
-      <c r="S89" s="12"/>
-      <c r="T89" s="12"/>
-      <c r="U89" s="13"/>
-      <c r="V89" s="13"/>
-      <c r="W89" s="12"/>
-      <c r="X89" s="12"/>
-      <c r="Y89" s="12"/>
-      <c r="Z89" s="12"/>
-      <c r="AA89" s="12"/>
+      <c r="M89" s="17">
+        <v>7</v>
+      </c>
+      <c r="N89" s="18"/>
+      <c r="O89" s="18"/>
+      <c r="P89" s="17"/>
+      <c r="Q89" s="17"/>
+      <c r="R89" s="17"/>
+      <c r="S89" s="17"/>
+      <c r="T89" s="17"/>
+      <c r="U89" s="18"/>
+      <c r="V89" s="18"/>
+      <c r="W89" s="17"/>
+      <c r="X89" s="17"/>
+      <c r="Y89" s="17"/>
+      <c r="Z89" s="17"/>
+      <c r="AA89" s="17"/>
       <c r="AB89" s="13" t="s">
         <v>20</v>
       </c>
@@ -18087,31 +18093,31 @@
       <c r="H90" s="10">
         <v>0.254</v>
       </c>
-      <c r="I90" s="12">
-        <v>7</v>
-      </c>
-      <c r="J90" s="12">
-        <v>2</v>
-      </c>
-      <c r="K90" s="12">
-        <v>8</v>
-      </c>
-      <c r="L90" s="12"/>
-      <c r="M90" s="12"/>
-      <c r="N90" s="13"/>
-      <c r="O90" s="13"/>
-      <c r="P90" s="12"/>
-      <c r="Q90" s="12"/>
-      <c r="R90" s="12"/>
-      <c r="S90" s="12"/>
-      <c r="T90" s="12"/>
-      <c r="U90" s="13"/>
-      <c r="V90" s="13"/>
-      <c r="W90" s="12"/>
-      <c r="X90" s="12"/>
-      <c r="Y90" s="12"/>
-      <c r="Z90" s="12"/>
-      <c r="AA90" s="12"/>
+      <c r="I90" s="17">
+        <v>7</v>
+      </c>
+      <c r="J90" s="17">
+        <v>2</v>
+      </c>
+      <c r="K90" s="17">
+        <v>8</v>
+      </c>
+      <c r="L90" s="17"/>
+      <c r="M90" s="17"/>
+      <c r="N90" s="18"/>
+      <c r="O90" s="18"/>
+      <c r="P90" s="17"/>
+      <c r="Q90" s="17"/>
+      <c r="R90" s="17"/>
+      <c r="S90" s="17"/>
+      <c r="T90" s="17"/>
+      <c r="U90" s="18"/>
+      <c r="V90" s="18"/>
+      <c r="W90" s="17"/>
+      <c r="X90" s="17"/>
+      <c r="Y90" s="17"/>
+      <c r="Z90" s="17"/>
+      <c r="AA90" s="17"/>
       <c r="AB90" s="13" t="s">
         <v>20</v>
       </c>
@@ -18147,31 +18153,31 @@
       <c r="H91" s="10">
         <v>0.254</v>
       </c>
-      <c r="I91" s="12">
-        <v>7</v>
-      </c>
-      <c r="J91" s="12">
-        <v>2</v>
-      </c>
-      <c r="K91" s="12">
-        <v>8</v>
-      </c>
-      <c r="L91" s="12"/>
-      <c r="M91" s="12"/>
-      <c r="N91" s="13"/>
-      <c r="O91" s="13"/>
-      <c r="P91" s="12"/>
-      <c r="Q91" s="12"/>
-      <c r="R91" s="12"/>
-      <c r="S91" s="12"/>
-      <c r="T91" s="12"/>
-      <c r="U91" s="13"/>
-      <c r="V91" s="13"/>
-      <c r="W91" s="12"/>
-      <c r="X91" s="12"/>
-      <c r="Y91" s="12"/>
-      <c r="Z91" s="12"/>
-      <c r="AA91" s="12"/>
+      <c r="I91" s="17">
+        <v>7</v>
+      </c>
+      <c r="J91" s="17">
+        <v>2</v>
+      </c>
+      <c r="K91" s="17">
+        <v>8</v>
+      </c>
+      <c r="L91" s="17"/>
+      <c r="M91" s="17"/>
+      <c r="N91" s="18"/>
+      <c r="O91" s="18"/>
+      <c r="P91" s="17"/>
+      <c r="Q91" s="17"/>
+      <c r="R91" s="17"/>
+      <c r="S91" s="17"/>
+      <c r="T91" s="17"/>
+      <c r="U91" s="18"/>
+      <c r="V91" s="18"/>
+      <c r="W91" s="17"/>
+      <c r="X91" s="17"/>
+      <c r="Y91" s="17"/>
+      <c r="Z91" s="17"/>
+      <c r="AA91" s="17"/>
       <c r="AB91" s="13" t="s">
         <v>20</v>
       </c>
@@ -18207,31 +18213,31 @@
       <c r="H92" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I92" s="12">
-        <v>1</v>
-      </c>
-      <c r="J92" s="12">
+      <c r="I92" s="17">
+        <v>1</v>
+      </c>
+      <c r="J92" s="17">
         <v>6</v>
       </c>
-      <c r="K92" s="12">
-        <v>7</v>
-      </c>
-      <c r="L92" s="12"/>
-      <c r="M92" s="12"/>
-      <c r="N92" s="13"/>
-      <c r="O92" s="13"/>
-      <c r="P92" s="12"/>
-      <c r="Q92" s="12"/>
-      <c r="R92" s="12"/>
-      <c r="S92" s="12"/>
-      <c r="T92" s="12"/>
-      <c r="U92" s="13"/>
-      <c r="V92" s="13"/>
-      <c r="W92" s="12"/>
-      <c r="X92" s="12"/>
-      <c r="Y92" s="12"/>
-      <c r="Z92" s="12"/>
-      <c r="AA92" s="12"/>
+      <c r="K92" s="17">
+        <v>7</v>
+      </c>
+      <c r="L92" s="17"/>
+      <c r="M92" s="17"/>
+      <c r="N92" s="18"/>
+      <c r="O92" s="18"/>
+      <c r="P92" s="17"/>
+      <c r="Q92" s="17"/>
+      <c r="R92" s="17"/>
+      <c r="S92" s="17"/>
+      <c r="T92" s="17"/>
+      <c r="U92" s="18"/>
+      <c r="V92" s="18"/>
+      <c r="W92" s="17"/>
+      <c r="X92" s="17"/>
+      <c r="Y92" s="17"/>
+      <c r="Z92" s="17"/>
+      <c r="AA92" s="17"/>
       <c r="AB92" s="13" t="s">
         <v>20</v>
       </c>
@@ -18267,35 +18273,35 @@
       <c r="H93" s="10">
         <v>0.254</v>
       </c>
-      <c r="I93" s="12">
-        <v>1</v>
-      </c>
-      <c r="J93" s="12">
-        <v>2</v>
-      </c>
-      <c r="K93" s="12">
-        <v>7</v>
-      </c>
-      <c r="L93" s="12">
-        <v>2</v>
-      </c>
-      <c r="M93" s="12">
+      <c r="I93" s="17">
+        <v>1</v>
+      </c>
+      <c r="J93" s="17">
+        <v>2</v>
+      </c>
+      <c r="K93" s="17">
+        <v>7</v>
+      </c>
+      <c r="L93" s="17">
+        <v>2</v>
+      </c>
+      <c r="M93" s="17">
         <v>6</v>
       </c>
-      <c r="N93" s="13"/>
-      <c r="O93" s="13"/>
-      <c r="P93" s="12"/>
-      <c r="Q93" s="12"/>
-      <c r="R93" s="12"/>
-      <c r="S93" s="12"/>
-      <c r="T93" s="12"/>
-      <c r="U93" s="13"/>
-      <c r="V93" s="13"/>
-      <c r="W93" s="12"/>
-      <c r="X93" s="12"/>
-      <c r="Y93" s="12"/>
-      <c r="Z93" s="12"/>
-      <c r="AA93" s="12"/>
+      <c r="N93" s="18"/>
+      <c r="O93" s="18"/>
+      <c r="P93" s="17"/>
+      <c r="Q93" s="17"/>
+      <c r="R93" s="17"/>
+      <c r="S93" s="17"/>
+      <c r="T93" s="17"/>
+      <c r="U93" s="18"/>
+      <c r="V93" s="18"/>
+      <c r="W93" s="17"/>
+      <c r="X93" s="17"/>
+      <c r="Y93" s="17"/>
+      <c r="Z93" s="17"/>
+      <c r="AA93" s="17"/>
       <c r="AB93" s="13" t="s">
         <v>20</v>
       </c>
@@ -18331,31 +18337,31 @@
       <c r="H94" s="10">
         <v>0.254</v>
       </c>
-      <c r="I94" s="12">
-        <v>1</v>
-      </c>
-      <c r="J94" s="12">
+      <c r="I94" s="17">
+        <v>1</v>
+      </c>
+      <c r="J94" s="17">
         <v>4</v>
       </c>
-      <c r="K94" s="12">
-        <v>7</v>
-      </c>
-      <c r="L94" s="12"/>
-      <c r="M94" s="12"/>
-      <c r="N94" s="13"/>
-      <c r="O94" s="13"/>
-      <c r="P94" s="12"/>
-      <c r="Q94" s="12"/>
-      <c r="R94" s="12"/>
-      <c r="S94" s="12"/>
-      <c r="T94" s="12"/>
-      <c r="U94" s="13"/>
-      <c r="V94" s="13"/>
-      <c r="W94" s="12"/>
-      <c r="X94" s="12"/>
-      <c r="Y94" s="12"/>
-      <c r="Z94" s="12"/>
-      <c r="AA94" s="12"/>
+      <c r="K94" s="17">
+        <v>7</v>
+      </c>
+      <c r="L94" s="17"/>
+      <c r="M94" s="17"/>
+      <c r="N94" s="18"/>
+      <c r="O94" s="18"/>
+      <c r="P94" s="17"/>
+      <c r="Q94" s="17"/>
+      <c r="R94" s="17"/>
+      <c r="S94" s="17"/>
+      <c r="T94" s="17"/>
+      <c r="U94" s="18"/>
+      <c r="V94" s="18"/>
+      <c r="W94" s="17"/>
+      <c r="X94" s="17"/>
+      <c r="Y94" s="17"/>
+      <c r="Z94" s="17"/>
+      <c r="AA94" s="17"/>
       <c r="AB94" s="13" t="s">
         <v>20</v>
       </c>
@@ -18391,35 +18397,35 @@
       <c r="H95" s="10">
         <v>0.254</v>
       </c>
-      <c r="I95" s="12">
-        <v>1</v>
-      </c>
-      <c r="J95" s="12">
-        <v>2</v>
-      </c>
-      <c r="K95" s="12">
-        <v>8</v>
-      </c>
-      <c r="L95" s="12">
-        <v>1</v>
-      </c>
-      <c r="M95" s="12">
-        <v>7</v>
-      </c>
-      <c r="N95" s="13"/>
-      <c r="O95" s="13"/>
-      <c r="P95" s="12"/>
-      <c r="Q95" s="12"/>
-      <c r="R95" s="12"/>
-      <c r="S95" s="12"/>
-      <c r="T95" s="12"/>
-      <c r="U95" s="13"/>
-      <c r="V95" s="13"/>
-      <c r="W95" s="12"/>
-      <c r="X95" s="12"/>
-      <c r="Y95" s="12"/>
-      <c r="Z95" s="12"/>
-      <c r="AA95" s="12"/>
+      <c r="I95" s="17">
+        <v>1</v>
+      </c>
+      <c r="J95" s="17">
+        <v>2</v>
+      </c>
+      <c r="K95" s="17">
+        <v>8</v>
+      </c>
+      <c r="L95" s="17">
+        <v>1</v>
+      </c>
+      <c r="M95" s="17">
+        <v>7</v>
+      </c>
+      <c r="N95" s="18"/>
+      <c r="O95" s="18"/>
+      <c r="P95" s="17"/>
+      <c r="Q95" s="17"/>
+      <c r="R95" s="17"/>
+      <c r="S95" s="17"/>
+      <c r="T95" s="17"/>
+      <c r="U95" s="18"/>
+      <c r="V95" s="18"/>
+      <c r="W95" s="17"/>
+      <c r="X95" s="17"/>
+      <c r="Y95" s="17"/>
+      <c r="Z95" s="17"/>
+      <c r="AA95" s="17"/>
       <c r="AB95" s="13" t="s">
         <v>20</v>
       </c>
@@ -18455,35 +18461,35 @@
       <c r="H96" s="10">
         <v>0.254</v>
       </c>
-      <c r="I96" s="12">
-        <v>1</v>
-      </c>
-      <c r="J96" s="12">
-        <v>2</v>
-      </c>
-      <c r="K96" s="12">
-        <v>7</v>
-      </c>
-      <c r="L96" s="12">
-        <v>2</v>
-      </c>
-      <c r="M96" s="12">
+      <c r="I96" s="17">
+        <v>1</v>
+      </c>
+      <c r="J96" s="17">
+        <v>2</v>
+      </c>
+      <c r="K96" s="17">
+        <v>7</v>
+      </c>
+      <c r="L96" s="17">
+        <v>2</v>
+      </c>
+      <c r="M96" s="17">
         <v>6</v>
       </c>
-      <c r="N96" s="13"/>
-      <c r="O96" s="13"/>
-      <c r="P96" s="12"/>
-      <c r="Q96" s="12"/>
-      <c r="R96" s="12"/>
-      <c r="S96" s="12"/>
-      <c r="T96" s="12"/>
-      <c r="U96" s="13"/>
-      <c r="V96" s="13"/>
-      <c r="W96" s="12"/>
-      <c r="X96" s="12"/>
-      <c r="Y96" s="12"/>
-      <c r="Z96" s="12"/>
-      <c r="AA96" s="12"/>
+      <c r="N96" s="18"/>
+      <c r="O96" s="18"/>
+      <c r="P96" s="17"/>
+      <c r="Q96" s="17"/>
+      <c r="R96" s="17"/>
+      <c r="S96" s="17"/>
+      <c r="T96" s="17"/>
+      <c r="U96" s="18"/>
+      <c r="V96" s="18"/>
+      <c r="W96" s="17"/>
+      <c r="X96" s="17"/>
+      <c r="Y96" s="17"/>
+      <c r="Z96" s="17"/>
+      <c r="AA96" s="17"/>
       <c r="AB96" s="13" t="s">
         <v>20</v>
       </c>
@@ -18519,31 +18525,31 @@
       <c r="H97" s="10">
         <v>0.44</v>
       </c>
-      <c r="I97" s="12">
-        <v>1</v>
-      </c>
-      <c r="J97" s="12">
-        <v>7</v>
-      </c>
-      <c r="K97" s="12">
-        <v>8</v>
-      </c>
-      <c r="L97" s="12"/>
-      <c r="M97" s="12"/>
-      <c r="N97" s="13"/>
-      <c r="O97" s="13"/>
-      <c r="P97" s="12"/>
-      <c r="Q97" s="12"/>
-      <c r="R97" s="12"/>
-      <c r="S97" s="12"/>
-      <c r="T97" s="12"/>
-      <c r="U97" s="13"/>
-      <c r="V97" s="13"/>
-      <c r="W97" s="12"/>
-      <c r="X97" s="12"/>
-      <c r="Y97" s="12"/>
-      <c r="Z97" s="12"/>
-      <c r="AA97" s="12"/>
+      <c r="I97" s="17">
+        <v>1</v>
+      </c>
+      <c r="J97" s="17">
+        <v>7</v>
+      </c>
+      <c r="K97" s="17">
+        <v>8</v>
+      </c>
+      <c r="L97" s="17"/>
+      <c r="M97" s="17"/>
+      <c r="N97" s="18"/>
+      <c r="O97" s="18"/>
+      <c r="P97" s="17"/>
+      <c r="Q97" s="17"/>
+      <c r="R97" s="17"/>
+      <c r="S97" s="17"/>
+      <c r="T97" s="17"/>
+      <c r="U97" s="18"/>
+      <c r="V97" s="18"/>
+      <c r="W97" s="17"/>
+      <c r="X97" s="17"/>
+      <c r="Y97" s="17"/>
+      <c r="Z97" s="17"/>
+      <c r="AA97" s="17"/>
       <c r="AB97" s="13" t="s">
         <v>20</v>
       </c>
@@ -18579,35 +18585,35 @@
       <c r="H98" s="10">
         <v>0.254</v>
       </c>
-      <c r="I98" s="12">
-        <v>1</v>
-      </c>
-      <c r="J98" s="12">
+      <c r="I98" s="17">
+        <v>1</v>
+      </c>
+      <c r="J98" s="17">
         <v>5</v>
       </c>
-      <c r="K98" s="12">
-        <v>8</v>
-      </c>
-      <c r="L98" s="12">
-        <v>1</v>
-      </c>
-      <c r="M98" s="12">
-        <v>7</v>
-      </c>
-      <c r="N98" s="13"/>
-      <c r="O98" s="13"/>
-      <c r="P98" s="12"/>
-      <c r="Q98" s="12"/>
-      <c r="R98" s="12"/>
-      <c r="S98" s="12"/>
-      <c r="T98" s="12"/>
-      <c r="U98" s="13"/>
-      <c r="V98" s="13"/>
-      <c r="W98" s="12"/>
-      <c r="X98" s="12"/>
-      <c r="Y98" s="12"/>
-      <c r="Z98" s="12"/>
-      <c r="AA98" s="12"/>
+      <c r="K98" s="17">
+        <v>8</v>
+      </c>
+      <c r="L98" s="17">
+        <v>1</v>
+      </c>
+      <c r="M98" s="17">
+        <v>7</v>
+      </c>
+      <c r="N98" s="18"/>
+      <c r="O98" s="18"/>
+      <c r="P98" s="17"/>
+      <c r="Q98" s="17"/>
+      <c r="R98" s="17"/>
+      <c r="S98" s="17"/>
+      <c r="T98" s="17"/>
+      <c r="U98" s="18"/>
+      <c r="V98" s="18"/>
+      <c r="W98" s="17"/>
+      <c r="X98" s="17"/>
+      <c r="Y98" s="17"/>
+      <c r="Z98" s="17"/>
+      <c r="AA98" s="17"/>
       <c r="AB98" s="13" t="s">
         <v>20</v>
       </c>
@@ -18643,35 +18649,35 @@
       <c r="H99" s="10">
         <v>0.254</v>
       </c>
-      <c r="I99" s="12">
-        <v>1</v>
-      </c>
-      <c r="J99" s="12">
+      <c r="I99" s="17">
+        <v>1</v>
+      </c>
+      <c r="J99" s="17">
         <v>5</v>
       </c>
-      <c r="K99" s="12">
-        <v>8</v>
-      </c>
-      <c r="L99" s="12">
-        <v>1</v>
-      </c>
-      <c r="M99" s="12">
-        <v>7</v>
-      </c>
-      <c r="N99" s="13"/>
-      <c r="O99" s="13"/>
-      <c r="P99" s="12"/>
-      <c r="Q99" s="12"/>
-      <c r="R99" s="12"/>
-      <c r="S99" s="12"/>
-      <c r="T99" s="12"/>
-      <c r="U99" s="13"/>
-      <c r="V99" s="13"/>
-      <c r="W99" s="12"/>
-      <c r="X99" s="12"/>
-      <c r="Y99" s="12"/>
-      <c r="Z99" s="12"/>
-      <c r="AA99" s="12"/>
+      <c r="K99" s="17">
+        <v>8</v>
+      </c>
+      <c r="L99" s="17">
+        <v>1</v>
+      </c>
+      <c r="M99" s="17">
+        <v>7</v>
+      </c>
+      <c r="N99" s="18"/>
+      <c r="O99" s="18"/>
+      <c r="P99" s="17"/>
+      <c r="Q99" s="17"/>
+      <c r="R99" s="17"/>
+      <c r="S99" s="17"/>
+      <c r="T99" s="17"/>
+      <c r="U99" s="18"/>
+      <c r="V99" s="18"/>
+      <c r="W99" s="17"/>
+      <c r="X99" s="17"/>
+      <c r="Y99" s="17"/>
+      <c r="Z99" s="17"/>
+      <c r="AA99" s="17"/>
       <c r="AB99" s="13" t="s">
         <v>20</v>
       </c>
@@ -18707,35 +18713,35 @@
       <c r="H100" s="10">
         <v>0.254</v>
       </c>
-      <c r="I100" s="12">
-        <v>1</v>
-      </c>
-      <c r="J100" s="12">
+      <c r="I100" s="17">
+        <v>1</v>
+      </c>
+      <c r="J100" s="17">
         <v>5</v>
       </c>
-      <c r="K100" s="12">
-        <v>8</v>
-      </c>
-      <c r="L100" s="12">
-        <v>1</v>
-      </c>
-      <c r="M100" s="12">
-        <v>7</v>
-      </c>
-      <c r="N100" s="13"/>
-      <c r="O100" s="13"/>
-      <c r="P100" s="12"/>
-      <c r="Q100" s="12"/>
-      <c r="R100" s="12"/>
-      <c r="S100" s="12"/>
-      <c r="T100" s="12"/>
-      <c r="U100" s="13"/>
-      <c r="V100" s="13"/>
-      <c r="W100" s="12"/>
-      <c r="X100" s="12"/>
-      <c r="Y100" s="12"/>
-      <c r="Z100" s="12"/>
-      <c r="AA100" s="12"/>
+      <c r="K100" s="17">
+        <v>8</v>
+      </c>
+      <c r="L100" s="17">
+        <v>1</v>
+      </c>
+      <c r="M100" s="17">
+        <v>7</v>
+      </c>
+      <c r="N100" s="18"/>
+      <c r="O100" s="18"/>
+      <c r="P100" s="17"/>
+      <c r="Q100" s="17"/>
+      <c r="R100" s="17"/>
+      <c r="S100" s="17"/>
+      <c r="T100" s="17"/>
+      <c r="U100" s="18"/>
+      <c r="V100" s="18"/>
+      <c r="W100" s="17"/>
+      <c r="X100" s="17"/>
+      <c r="Y100" s="17"/>
+      <c r="Z100" s="17"/>
+      <c r="AA100" s="17"/>
       <c r="AB100" s="13" t="s">
         <v>20</v>
       </c>
@@ -18771,35 +18777,35 @@
       <c r="H101" s="10">
         <v>0.254</v>
       </c>
-      <c r="I101" s="12">
-        <v>1</v>
-      </c>
-      <c r="J101" s="12">
-        <v>2</v>
-      </c>
-      <c r="K101" s="12">
-        <v>8</v>
-      </c>
-      <c r="L101" s="12">
+      <c r="I101" s="17">
+        <v>1</v>
+      </c>
+      <c r="J101" s="17">
+        <v>2</v>
+      </c>
+      <c r="K101" s="17">
+        <v>8</v>
+      </c>
+      <c r="L101" s="17">
         <v>4</v>
       </c>
-      <c r="M101" s="12">
-        <v>7</v>
-      </c>
-      <c r="N101" s="13"/>
-      <c r="O101" s="13"/>
-      <c r="P101" s="12"/>
-      <c r="Q101" s="12"/>
-      <c r="R101" s="12"/>
-      <c r="S101" s="12"/>
-      <c r="T101" s="12"/>
-      <c r="U101" s="13"/>
-      <c r="V101" s="13"/>
-      <c r="W101" s="12"/>
-      <c r="X101" s="12"/>
-      <c r="Y101" s="12"/>
-      <c r="Z101" s="12"/>
-      <c r="AA101" s="12"/>
+      <c r="M101" s="17">
+        <v>7</v>
+      </c>
+      <c r="N101" s="18"/>
+      <c r="O101" s="18"/>
+      <c r="P101" s="17"/>
+      <c r="Q101" s="17"/>
+      <c r="R101" s="17"/>
+      <c r="S101" s="17"/>
+      <c r="T101" s="17"/>
+      <c r="U101" s="18"/>
+      <c r="V101" s="18"/>
+      <c r="W101" s="17"/>
+      <c r="X101" s="17"/>
+      <c r="Y101" s="17"/>
+      <c r="Z101" s="17"/>
+      <c r="AA101" s="17"/>
       <c r="AB101" s="13" t="s">
         <v>20</v>
       </c>
@@ -18835,35 +18841,35 @@
       <c r="H102" s="10">
         <v>0.254</v>
       </c>
-      <c r="I102" s="12">
-        <v>1</v>
-      </c>
-      <c r="J102" s="12">
-        <v>2</v>
-      </c>
-      <c r="K102" s="12">
-        <v>8</v>
-      </c>
-      <c r="L102" s="12">
+      <c r="I102" s="17">
+        <v>1</v>
+      </c>
+      <c r="J102" s="17">
+        <v>2</v>
+      </c>
+      <c r="K102" s="17">
+        <v>8</v>
+      </c>
+      <c r="L102" s="17">
         <v>4</v>
       </c>
-      <c r="M102" s="12">
-        <v>7</v>
-      </c>
-      <c r="N102" s="13"/>
-      <c r="O102" s="13"/>
-      <c r="P102" s="12"/>
-      <c r="Q102" s="12"/>
-      <c r="R102" s="12"/>
-      <c r="S102" s="12"/>
-      <c r="T102" s="12"/>
-      <c r="U102" s="13"/>
-      <c r="V102" s="13"/>
-      <c r="W102" s="12"/>
-      <c r="X102" s="12"/>
-      <c r="Y102" s="12"/>
-      <c r="Z102" s="12"/>
-      <c r="AA102" s="12"/>
+      <c r="M102" s="17">
+        <v>7</v>
+      </c>
+      <c r="N102" s="18"/>
+      <c r="O102" s="18"/>
+      <c r="P102" s="17"/>
+      <c r="Q102" s="17"/>
+      <c r="R102" s="17"/>
+      <c r="S102" s="17"/>
+      <c r="T102" s="17"/>
+      <c r="U102" s="18"/>
+      <c r="V102" s="18"/>
+      <c r="W102" s="17"/>
+      <c r="X102" s="17"/>
+      <c r="Y102" s="17"/>
+      <c r="Z102" s="17"/>
+      <c r="AA102" s="17"/>
       <c r="AB102" s="13" t="s">
         <v>20</v>
       </c>
@@ -18899,35 +18905,35 @@
       <c r="H103" s="10">
         <v>0.30399999999999999</v>
       </c>
-      <c r="I103" s="12">
-        <v>1</v>
-      </c>
-      <c r="J103" s="12">
+      <c r="I103" s="17">
+        <v>1</v>
+      </c>
+      <c r="J103" s="17">
         <v>3</v>
       </c>
-      <c r="K103" s="12">
-        <v>8</v>
-      </c>
-      <c r="L103" s="12">
+      <c r="K103" s="17">
+        <v>8</v>
+      </c>
+      <c r="L103" s="17">
         <v>4</v>
       </c>
-      <c r="M103" s="12">
-        <v>7</v>
-      </c>
-      <c r="N103" s="13"/>
-      <c r="O103" s="13"/>
-      <c r="P103" s="12"/>
-      <c r="Q103" s="12"/>
-      <c r="R103" s="12"/>
-      <c r="S103" s="12"/>
-      <c r="T103" s="12"/>
-      <c r="U103" s="13"/>
-      <c r="V103" s="13"/>
-      <c r="W103" s="12"/>
-      <c r="X103" s="12"/>
-      <c r="Y103" s="12"/>
-      <c r="Z103" s="12"/>
-      <c r="AA103" s="12"/>
+      <c r="M103" s="17">
+        <v>7</v>
+      </c>
+      <c r="N103" s="18"/>
+      <c r="O103" s="18"/>
+      <c r="P103" s="17"/>
+      <c r="Q103" s="17"/>
+      <c r="R103" s="17"/>
+      <c r="S103" s="17"/>
+      <c r="T103" s="17"/>
+      <c r="U103" s="18"/>
+      <c r="V103" s="18"/>
+      <c r="W103" s="17"/>
+      <c r="X103" s="17"/>
+      <c r="Y103" s="17"/>
+      <c r="Z103" s="17"/>
+      <c r="AA103" s="17"/>
       <c r="AB103" s="13" t="s">
         <v>20</v>
       </c>
@@ -18963,35 +18969,35 @@
       <c r="H104" s="10">
         <v>0.30399999999999999</v>
       </c>
-      <c r="I104" s="12">
-        <v>1</v>
-      </c>
-      <c r="J104" s="12">
+      <c r="I104" s="17">
+        <v>1</v>
+      </c>
+      <c r="J104" s="17">
         <v>3</v>
       </c>
-      <c r="K104" s="12">
-        <v>8</v>
-      </c>
-      <c r="L104" s="12">
+      <c r="K104" s="17">
+        <v>8</v>
+      </c>
+      <c r="L104" s="17">
         <v>4</v>
       </c>
-      <c r="M104" s="12">
-        <v>7</v>
-      </c>
-      <c r="N104" s="13"/>
-      <c r="O104" s="13"/>
-      <c r="P104" s="12"/>
-      <c r="Q104" s="12"/>
-      <c r="R104" s="12"/>
-      <c r="S104" s="12"/>
-      <c r="T104" s="12"/>
-      <c r="U104" s="13"/>
-      <c r="V104" s="13"/>
-      <c r="W104" s="12"/>
-      <c r="X104" s="12"/>
-      <c r="Y104" s="12"/>
-      <c r="Z104" s="12"/>
-      <c r="AA104" s="12"/>
+      <c r="M104" s="17">
+        <v>7</v>
+      </c>
+      <c r="N104" s="18"/>
+      <c r="O104" s="18"/>
+      <c r="P104" s="17"/>
+      <c r="Q104" s="17"/>
+      <c r="R104" s="17"/>
+      <c r="S104" s="17"/>
+      <c r="T104" s="17"/>
+      <c r="U104" s="18"/>
+      <c r="V104" s="18"/>
+      <c r="W104" s="17"/>
+      <c r="X104" s="17"/>
+      <c r="Y104" s="17"/>
+      <c r="Z104" s="17"/>
+      <c r="AA104" s="17"/>
       <c r="AB104" s="13" t="s">
         <v>20</v>
       </c>
@@ -19027,35 +19033,35 @@
       <c r="H105" s="10">
         <v>0.30399999999999999</v>
       </c>
-      <c r="I105" s="12">
-        <v>1</v>
-      </c>
-      <c r="J105" s="12">
+      <c r="I105" s="17">
+        <v>1</v>
+      </c>
+      <c r="J105" s="17">
         <v>3</v>
       </c>
-      <c r="K105" s="12">
-        <v>8</v>
-      </c>
-      <c r="L105" s="12">
+      <c r="K105" s="17">
+        <v>8</v>
+      </c>
+      <c r="L105" s="17">
         <v>4</v>
       </c>
-      <c r="M105" s="12">
-        <v>7</v>
-      </c>
-      <c r="N105" s="13"/>
-      <c r="O105" s="13"/>
-      <c r="P105" s="12"/>
-      <c r="Q105" s="12"/>
-      <c r="R105" s="12"/>
-      <c r="S105" s="12"/>
-      <c r="T105" s="12"/>
-      <c r="U105" s="13"/>
-      <c r="V105" s="13"/>
-      <c r="W105" s="12"/>
-      <c r="X105" s="12"/>
-      <c r="Y105" s="12"/>
-      <c r="Z105" s="12"/>
-      <c r="AA105" s="12"/>
+      <c r="M105" s="17">
+        <v>7</v>
+      </c>
+      <c r="N105" s="18"/>
+      <c r="O105" s="18"/>
+      <c r="P105" s="17"/>
+      <c r="Q105" s="17"/>
+      <c r="R105" s="17"/>
+      <c r="S105" s="17"/>
+      <c r="T105" s="17"/>
+      <c r="U105" s="18"/>
+      <c r="V105" s="18"/>
+      <c r="W105" s="17"/>
+      <c r="X105" s="17"/>
+      <c r="Y105" s="17"/>
+      <c r="Z105" s="17"/>
+      <c r="AA105" s="17"/>
       <c r="AB105" s="13" t="s">
         <v>20</v>
       </c>
@@ -19091,31 +19097,31 @@
       <c r="H106" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I106" s="12">
-        <v>1</v>
-      </c>
-      <c r="J106" s="12">
+      <c r="I106" s="17">
+        <v>1</v>
+      </c>
+      <c r="J106" s="17">
         <v>4</v>
       </c>
-      <c r="K106" s="12">
-        <v>7</v>
-      </c>
-      <c r="L106" s="12"/>
-      <c r="M106" s="12"/>
-      <c r="N106" s="13"/>
-      <c r="O106" s="13"/>
-      <c r="P106" s="12"/>
-      <c r="Q106" s="12"/>
-      <c r="R106" s="12"/>
-      <c r="S106" s="12"/>
-      <c r="T106" s="12"/>
-      <c r="U106" s="13"/>
-      <c r="V106" s="13"/>
-      <c r="W106" s="12"/>
-      <c r="X106" s="12"/>
-      <c r="Y106" s="12"/>
-      <c r="Z106" s="12"/>
-      <c r="AA106" s="12"/>
+      <c r="K106" s="17">
+        <v>7</v>
+      </c>
+      <c r="L106" s="17"/>
+      <c r="M106" s="17"/>
+      <c r="N106" s="18"/>
+      <c r="O106" s="18"/>
+      <c r="P106" s="17"/>
+      <c r="Q106" s="17"/>
+      <c r="R106" s="17"/>
+      <c r="S106" s="17"/>
+      <c r="T106" s="17"/>
+      <c r="U106" s="18"/>
+      <c r="V106" s="18"/>
+      <c r="W106" s="17"/>
+      <c r="X106" s="17"/>
+      <c r="Y106" s="17"/>
+      <c r="Z106" s="17"/>
+      <c r="AA106" s="17"/>
       <c r="AB106" s="13" t="s">
         <v>20</v>
       </c>
@@ -19151,31 +19157,31 @@
       <c r="H107" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I107" s="12">
-        <v>1</v>
-      </c>
-      <c r="J107" s="12">
+      <c r="I107" s="17">
+        <v>1</v>
+      </c>
+      <c r="J107" s="17">
         <v>4</v>
       </c>
-      <c r="K107" s="12">
-        <v>7</v>
-      </c>
-      <c r="L107" s="12"/>
-      <c r="M107" s="12"/>
-      <c r="N107" s="13"/>
-      <c r="O107" s="13"/>
-      <c r="P107" s="12"/>
-      <c r="Q107" s="12"/>
-      <c r="R107" s="12"/>
-      <c r="S107" s="12"/>
-      <c r="T107" s="12"/>
-      <c r="U107" s="13"/>
-      <c r="V107" s="13"/>
-      <c r="W107" s="12"/>
-      <c r="X107" s="12"/>
-      <c r="Y107" s="12"/>
-      <c r="Z107" s="12"/>
-      <c r="AA107" s="12"/>
+      <c r="K107" s="17">
+        <v>7</v>
+      </c>
+      <c r="L107" s="17"/>
+      <c r="M107" s="17"/>
+      <c r="N107" s="18"/>
+      <c r="O107" s="18"/>
+      <c r="P107" s="17"/>
+      <c r="Q107" s="17"/>
+      <c r="R107" s="17"/>
+      <c r="S107" s="17"/>
+      <c r="T107" s="17"/>
+      <c r="U107" s="18"/>
+      <c r="V107" s="18"/>
+      <c r="W107" s="17"/>
+      <c r="X107" s="17"/>
+      <c r="Y107" s="17"/>
+      <c r="Z107" s="17"/>
+      <c r="AA107" s="17"/>
       <c r="AB107" s="13" t="s">
         <v>20</v>
       </c>
@@ -19211,31 +19217,31 @@
       <c r="H108" s="10">
         <v>0.254</v>
       </c>
-      <c r="I108" s="12">
-        <v>1</v>
-      </c>
-      <c r="J108" s="12">
+      <c r="I108" s="17">
+        <v>1</v>
+      </c>
+      <c r="J108" s="17">
         <v>4</v>
       </c>
-      <c r="K108" s="12">
-        <v>7</v>
-      </c>
-      <c r="L108" s="12"/>
-      <c r="M108" s="12"/>
-      <c r="N108" s="13"/>
-      <c r="O108" s="13"/>
-      <c r="P108" s="12"/>
-      <c r="Q108" s="12"/>
-      <c r="R108" s="12"/>
-      <c r="S108" s="12"/>
-      <c r="T108" s="12"/>
-      <c r="U108" s="13"/>
-      <c r="V108" s="13"/>
-      <c r="W108" s="12"/>
-      <c r="X108" s="12"/>
-      <c r="Y108" s="12"/>
-      <c r="Z108" s="12"/>
-      <c r="AA108" s="12"/>
+      <c r="K108" s="17">
+        <v>7</v>
+      </c>
+      <c r="L108" s="17"/>
+      <c r="M108" s="17"/>
+      <c r="N108" s="18"/>
+      <c r="O108" s="18"/>
+      <c r="P108" s="17"/>
+      <c r="Q108" s="17"/>
+      <c r="R108" s="17"/>
+      <c r="S108" s="17"/>
+      <c r="T108" s="17"/>
+      <c r="U108" s="18"/>
+      <c r="V108" s="18"/>
+      <c r="W108" s="17"/>
+      <c r="X108" s="17"/>
+      <c r="Y108" s="17"/>
+      <c r="Z108" s="17"/>
+      <c r="AA108" s="17"/>
       <c r="AB108" s="13" t="s">
         <v>20</v>
       </c>
@@ -19271,35 +19277,35 @@
       <c r="H109" s="10">
         <v>0.254</v>
       </c>
-      <c r="I109" s="12">
-        <v>1</v>
-      </c>
-      <c r="J109" s="12">
+      <c r="I109" s="17">
+        <v>1</v>
+      </c>
+      <c r="J109" s="17">
         <v>5</v>
       </c>
-      <c r="K109" s="12">
-        <v>8</v>
-      </c>
-      <c r="L109" s="12">
-        <v>1</v>
-      </c>
-      <c r="M109" s="12">
-        <v>7</v>
-      </c>
-      <c r="N109" s="13"/>
-      <c r="O109" s="13"/>
-      <c r="P109" s="12"/>
-      <c r="Q109" s="12"/>
-      <c r="R109" s="12"/>
-      <c r="S109" s="12"/>
-      <c r="T109" s="12"/>
-      <c r="U109" s="13"/>
-      <c r="V109" s="13"/>
-      <c r="W109" s="12"/>
-      <c r="X109" s="12"/>
-      <c r="Y109" s="12"/>
-      <c r="Z109" s="12"/>
-      <c r="AA109" s="12"/>
+      <c r="K109" s="17">
+        <v>8</v>
+      </c>
+      <c r="L109" s="17">
+        <v>1</v>
+      </c>
+      <c r="M109" s="17">
+        <v>7</v>
+      </c>
+      <c r="N109" s="18"/>
+      <c r="O109" s="18"/>
+      <c r="P109" s="17"/>
+      <c r="Q109" s="17"/>
+      <c r="R109" s="17"/>
+      <c r="S109" s="17"/>
+      <c r="T109" s="17"/>
+      <c r="U109" s="18"/>
+      <c r="V109" s="18"/>
+      <c r="W109" s="17"/>
+      <c r="X109" s="17"/>
+      <c r="Y109" s="17"/>
+      <c r="Z109" s="17"/>
+      <c r="AA109" s="17"/>
       <c r="AB109" s="13" t="s">
         <v>20</v>
       </c>
@@ -19335,35 +19341,35 @@
       <c r="H110" s="10">
         <v>0.254</v>
       </c>
-      <c r="I110" s="12">
-        <v>1</v>
-      </c>
-      <c r="J110" s="12">
-        <v>2</v>
-      </c>
-      <c r="K110" s="12">
-        <v>8</v>
-      </c>
-      <c r="L110" s="12">
+      <c r="I110" s="17">
+        <v>1</v>
+      </c>
+      <c r="J110" s="17">
+        <v>2</v>
+      </c>
+      <c r="K110" s="17">
+        <v>8</v>
+      </c>
+      <c r="L110" s="17">
         <v>4</v>
       </c>
-      <c r="M110" s="12">
-        <v>7</v>
-      </c>
-      <c r="N110" s="13"/>
-      <c r="O110" s="13"/>
-      <c r="P110" s="12"/>
-      <c r="Q110" s="12"/>
-      <c r="R110" s="12"/>
-      <c r="S110" s="12"/>
-      <c r="T110" s="12"/>
-      <c r="U110" s="13"/>
-      <c r="V110" s="13"/>
-      <c r="W110" s="12"/>
-      <c r="X110" s="12"/>
-      <c r="Y110" s="12"/>
-      <c r="Z110" s="12"/>
-      <c r="AA110" s="12"/>
+      <c r="M110" s="17">
+        <v>7</v>
+      </c>
+      <c r="N110" s="18"/>
+      <c r="O110" s="18"/>
+      <c r="P110" s="17"/>
+      <c r="Q110" s="17"/>
+      <c r="R110" s="17"/>
+      <c r="S110" s="17"/>
+      <c r="T110" s="17"/>
+      <c r="U110" s="18"/>
+      <c r="V110" s="18"/>
+      <c r="W110" s="17"/>
+      <c r="X110" s="17"/>
+      <c r="Y110" s="17"/>
+      <c r="Z110" s="17"/>
+      <c r="AA110" s="17"/>
       <c r="AB110" s="13" t="s">
         <v>20</v>
       </c>
@@ -19399,35 +19405,35 @@
       <c r="H111" s="10">
         <v>0.30399999999999999</v>
       </c>
-      <c r="I111" s="12">
-        <v>1</v>
-      </c>
-      <c r="J111" s="12">
+      <c r="I111" s="17">
+        <v>1</v>
+      </c>
+      <c r="J111" s="17">
         <v>3</v>
       </c>
-      <c r="K111" s="12">
-        <v>8</v>
-      </c>
-      <c r="L111" s="12">
+      <c r="K111" s="17">
+        <v>8</v>
+      </c>
+      <c r="L111" s="17">
         <v>4</v>
       </c>
-      <c r="M111" s="12">
-        <v>7</v>
-      </c>
-      <c r="N111" s="13"/>
-      <c r="O111" s="13"/>
-      <c r="P111" s="12"/>
-      <c r="Q111" s="12"/>
-      <c r="R111" s="12"/>
-      <c r="S111" s="12"/>
-      <c r="T111" s="12"/>
-      <c r="U111" s="13"/>
-      <c r="V111" s="13"/>
-      <c r="W111" s="12"/>
-      <c r="X111" s="12"/>
-      <c r="Y111" s="12"/>
-      <c r="Z111" s="12"/>
-      <c r="AA111" s="12"/>
+      <c r="M111" s="17">
+        <v>7</v>
+      </c>
+      <c r="N111" s="18"/>
+      <c r="O111" s="18"/>
+      <c r="P111" s="17"/>
+      <c r="Q111" s="17"/>
+      <c r="R111" s="17"/>
+      <c r="S111" s="17"/>
+      <c r="T111" s="17"/>
+      <c r="U111" s="18"/>
+      <c r="V111" s="18"/>
+      <c r="W111" s="17"/>
+      <c r="X111" s="17"/>
+      <c r="Y111" s="17"/>
+      <c r="Z111" s="17"/>
+      <c r="AA111" s="17"/>
       <c r="AB111" s="13" t="s">
         <v>20</v>
       </c>
@@ -19463,35 +19469,35 @@
       <c r="H112" s="10">
         <v>0.30399999999999999</v>
       </c>
-      <c r="I112" s="12">
-        <v>1</v>
-      </c>
-      <c r="J112" s="12">
+      <c r="I112" s="17">
+        <v>1</v>
+      </c>
+      <c r="J112" s="17">
         <v>3</v>
       </c>
-      <c r="K112" s="12">
-        <v>8</v>
-      </c>
-      <c r="L112" s="12">
+      <c r="K112" s="17">
+        <v>8</v>
+      </c>
+      <c r="L112" s="17">
         <v>4</v>
       </c>
-      <c r="M112" s="12">
-        <v>7</v>
-      </c>
-      <c r="N112" s="13"/>
-      <c r="O112" s="13"/>
-      <c r="P112" s="12"/>
-      <c r="Q112" s="12"/>
-      <c r="R112" s="12"/>
-      <c r="S112" s="12"/>
-      <c r="T112" s="12"/>
-      <c r="U112" s="13"/>
-      <c r="V112" s="13"/>
-      <c r="W112" s="12"/>
-      <c r="X112" s="12"/>
-      <c r="Y112" s="12"/>
-      <c r="Z112" s="12"/>
-      <c r="AA112" s="12"/>
+      <c r="M112" s="17">
+        <v>7</v>
+      </c>
+      <c r="N112" s="18"/>
+      <c r="O112" s="18"/>
+      <c r="P112" s="17"/>
+      <c r="Q112" s="17"/>
+      <c r="R112" s="17"/>
+      <c r="S112" s="17"/>
+      <c r="T112" s="17"/>
+      <c r="U112" s="18"/>
+      <c r="V112" s="18"/>
+      <c r="W112" s="17"/>
+      <c r="X112" s="17"/>
+      <c r="Y112" s="17"/>
+      <c r="Z112" s="17"/>
+      <c r="AA112" s="17"/>
       <c r="AB112" s="13" t="s">
         <v>20</v>
       </c>
@@ -19527,35 +19533,35 @@
       <c r="H113" s="10">
         <v>0.30399999999999999</v>
       </c>
-      <c r="I113" s="12">
-        <v>1</v>
-      </c>
-      <c r="J113" s="12">
+      <c r="I113" s="17">
+        <v>1</v>
+      </c>
+      <c r="J113" s="17">
         <v>3</v>
       </c>
-      <c r="K113" s="12">
-        <v>8</v>
-      </c>
-      <c r="L113" s="12">
+      <c r="K113" s="17">
+        <v>8</v>
+      </c>
+      <c r="L113" s="17">
         <v>4</v>
       </c>
-      <c r="M113" s="12">
-        <v>7</v>
-      </c>
-      <c r="N113" s="13"/>
-      <c r="O113" s="13"/>
-      <c r="P113" s="12"/>
-      <c r="Q113" s="12"/>
-      <c r="R113" s="12"/>
-      <c r="S113" s="12"/>
-      <c r="T113" s="12"/>
-      <c r="U113" s="13"/>
-      <c r="V113" s="13"/>
-      <c r="W113" s="12"/>
-      <c r="X113" s="12"/>
-      <c r="Y113" s="12"/>
-      <c r="Z113" s="12"/>
-      <c r="AA113" s="12"/>
+      <c r="M113" s="17">
+        <v>7</v>
+      </c>
+      <c r="N113" s="18"/>
+      <c r="O113" s="18"/>
+      <c r="P113" s="17"/>
+      <c r="Q113" s="17"/>
+      <c r="R113" s="17"/>
+      <c r="S113" s="17"/>
+      <c r="T113" s="17"/>
+      <c r="U113" s="18"/>
+      <c r="V113" s="18"/>
+      <c r="W113" s="17"/>
+      <c r="X113" s="17"/>
+      <c r="Y113" s="17"/>
+      <c r="Z113" s="17"/>
+      <c r="AA113" s="17"/>
       <c r="AB113" s="13" t="s">
         <v>20</v>
       </c>
@@ -19591,35 +19597,35 @@
       <c r="H114" s="10">
         <v>0.30399999999999999</v>
       </c>
-      <c r="I114" s="12">
-        <v>1</v>
-      </c>
-      <c r="J114" s="12">
+      <c r="I114" s="17">
+        <v>1</v>
+      </c>
+      <c r="J114" s="17">
         <v>3</v>
       </c>
-      <c r="K114" s="12">
-        <v>8</v>
-      </c>
-      <c r="L114" s="12">
+      <c r="K114" s="17">
+        <v>8</v>
+      </c>
+      <c r="L114" s="17">
         <v>4</v>
       </c>
-      <c r="M114" s="12">
-        <v>7</v>
-      </c>
-      <c r="N114" s="13"/>
-      <c r="O114" s="13"/>
-      <c r="P114" s="12"/>
-      <c r="Q114" s="12"/>
-      <c r="R114" s="12"/>
-      <c r="S114" s="12"/>
-      <c r="T114" s="12"/>
-      <c r="U114" s="13"/>
-      <c r="V114" s="13"/>
-      <c r="W114" s="12"/>
-      <c r="X114" s="12"/>
-      <c r="Y114" s="12"/>
-      <c r="Z114" s="12"/>
-      <c r="AA114" s="12"/>
+      <c r="M114" s="17">
+        <v>7</v>
+      </c>
+      <c r="N114" s="18"/>
+      <c r="O114" s="18"/>
+      <c r="P114" s="17"/>
+      <c r="Q114" s="17"/>
+      <c r="R114" s="17"/>
+      <c r="S114" s="17"/>
+      <c r="T114" s="17"/>
+      <c r="U114" s="18"/>
+      <c r="V114" s="18"/>
+      <c r="W114" s="17"/>
+      <c r="X114" s="17"/>
+      <c r="Y114" s="17"/>
+      <c r="Z114" s="17"/>
+      <c r="AA114" s="17"/>
       <c r="AB114" s="13" t="s">
         <v>20</v>
       </c>
@@ -19655,31 +19661,31 @@
       <c r="H115" s="10">
         <v>0.44</v>
       </c>
-      <c r="I115" s="12">
-        <v>1</v>
-      </c>
-      <c r="J115" s="12">
-        <v>7</v>
-      </c>
-      <c r="K115" s="12">
-        <v>8</v>
-      </c>
-      <c r="L115" s="12"/>
-      <c r="M115" s="12"/>
-      <c r="N115" s="13"/>
-      <c r="O115" s="13"/>
-      <c r="P115" s="12"/>
-      <c r="Q115" s="12"/>
-      <c r="R115" s="12"/>
-      <c r="S115" s="12"/>
-      <c r="T115" s="12"/>
-      <c r="U115" s="13"/>
-      <c r="V115" s="13"/>
-      <c r="W115" s="12"/>
-      <c r="X115" s="12"/>
-      <c r="Y115" s="12"/>
-      <c r="Z115" s="12"/>
-      <c r="AA115" s="12"/>
+      <c r="I115" s="17">
+        <v>1</v>
+      </c>
+      <c r="J115" s="17">
+        <v>7</v>
+      </c>
+      <c r="K115" s="17">
+        <v>8</v>
+      </c>
+      <c r="L115" s="17"/>
+      <c r="M115" s="17"/>
+      <c r="N115" s="18"/>
+      <c r="O115" s="18"/>
+      <c r="P115" s="17"/>
+      <c r="Q115" s="17"/>
+      <c r="R115" s="17"/>
+      <c r="S115" s="17"/>
+      <c r="T115" s="17"/>
+      <c r="U115" s="18"/>
+      <c r="V115" s="18"/>
+      <c r="W115" s="17"/>
+      <c r="X115" s="17"/>
+      <c r="Y115" s="17"/>
+      <c r="Z115" s="17"/>
+      <c r="AA115" s="17"/>
       <c r="AB115" s="13" t="s">
         <v>20</v>
       </c>
@@ -19715,31 +19721,31 @@
       <c r="H116" s="10">
         <v>0.44</v>
       </c>
-      <c r="I116" s="12">
-        <v>1</v>
-      </c>
-      <c r="J116" s="12">
-        <v>7</v>
-      </c>
-      <c r="K116" s="12">
-        <v>8</v>
-      </c>
-      <c r="L116" s="12"/>
-      <c r="M116" s="12"/>
-      <c r="N116" s="13"/>
-      <c r="O116" s="13"/>
-      <c r="P116" s="12"/>
-      <c r="Q116" s="12"/>
-      <c r="R116" s="12"/>
-      <c r="S116" s="12"/>
-      <c r="T116" s="12"/>
-      <c r="U116" s="13"/>
-      <c r="V116" s="13"/>
-      <c r="W116" s="12"/>
-      <c r="X116" s="12"/>
-      <c r="Y116" s="12"/>
-      <c r="Z116" s="12"/>
-      <c r="AA116" s="12"/>
+      <c r="I116" s="17">
+        <v>1</v>
+      </c>
+      <c r="J116" s="17">
+        <v>7</v>
+      </c>
+      <c r="K116" s="17">
+        <v>8</v>
+      </c>
+      <c r="L116" s="17"/>
+      <c r="M116" s="17"/>
+      <c r="N116" s="18"/>
+      <c r="O116" s="18"/>
+      <c r="P116" s="17"/>
+      <c r="Q116" s="17"/>
+      <c r="R116" s="17"/>
+      <c r="S116" s="17"/>
+      <c r="T116" s="17"/>
+      <c r="U116" s="18"/>
+      <c r="V116" s="18"/>
+      <c r="W116" s="17"/>
+      <c r="X116" s="17"/>
+      <c r="Y116" s="17"/>
+      <c r="Z116" s="17"/>
+      <c r="AA116" s="17"/>
       <c r="AB116" s="13" t="s">
         <v>20</v>
       </c>
@@ -19775,31 +19781,31 @@
       <c r="H117" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I117" s="12">
-        <v>7</v>
-      </c>
-      <c r="J117" s="12">
+      <c r="I117" s="17">
+        <v>7</v>
+      </c>
+      <c r="J117" s="17">
         <v>4</v>
       </c>
-      <c r="K117" s="12">
-        <v>8</v>
-      </c>
-      <c r="L117" s="12"/>
-      <c r="M117" s="12"/>
-      <c r="N117" s="13"/>
-      <c r="O117" s="13"/>
-      <c r="P117" s="12"/>
-      <c r="Q117" s="12"/>
-      <c r="R117" s="12"/>
-      <c r="S117" s="12"/>
-      <c r="T117" s="12"/>
-      <c r="U117" s="13"/>
-      <c r="V117" s="13"/>
-      <c r="W117" s="12"/>
-      <c r="X117" s="12"/>
-      <c r="Y117" s="12"/>
-      <c r="Z117" s="12"/>
-      <c r="AA117" s="12"/>
+      <c r="K117" s="17">
+        <v>8</v>
+      </c>
+      <c r="L117" s="17"/>
+      <c r="M117" s="17"/>
+      <c r="N117" s="18"/>
+      <c r="O117" s="18"/>
+      <c r="P117" s="17"/>
+      <c r="Q117" s="17"/>
+      <c r="R117" s="17"/>
+      <c r="S117" s="17"/>
+      <c r="T117" s="17"/>
+      <c r="U117" s="18"/>
+      <c r="V117" s="18"/>
+      <c r="W117" s="17"/>
+      <c r="X117" s="17"/>
+      <c r="Y117" s="17"/>
+      <c r="Z117" s="17"/>
+      <c r="AA117" s="17"/>
       <c r="AB117" s="13" t="s">
         <v>20</v>
       </c>
@@ -19835,31 +19841,31 @@
       <c r="H118" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I118" s="12">
-        <v>1</v>
-      </c>
-      <c r="J118" s="12">
+      <c r="I118" s="17">
+        <v>1</v>
+      </c>
+      <c r="J118" s="17">
         <v>6</v>
       </c>
-      <c r="K118" s="12">
-        <v>7</v>
-      </c>
-      <c r="L118" s="12"/>
-      <c r="M118" s="12"/>
-      <c r="N118" s="13"/>
-      <c r="O118" s="13"/>
-      <c r="P118" s="12"/>
-      <c r="Q118" s="12"/>
-      <c r="R118" s="12"/>
-      <c r="S118" s="12"/>
-      <c r="T118" s="12"/>
-      <c r="U118" s="13"/>
-      <c r="V118" s="13"/>
-      <c r="W118" s="12"/>
-      <c r="X118" s="12"/>
-      <c r="Y118" s="12"/>
-      <c r="Z118" s="12"/>
-      <c r="AA118" s="12"/>
+      <c r="K118" s="17">
+        <v>7</v>
+      </c>
+      <c r="L118" s="17"/>
+      <c r="M118" s="17"/>
+      <c r="N118" s="18"/>
+      <c r="O118" s="18"/>
+      <c r="P118" s="17"/>
+      <c r="Q118" s="17"/>
+      <c r="R118" s="17"/>
+      <c r="S118" s="17"/>
+      <c r="T118" s="17"/>
+      <c r="U118" s="18"/>
+      <c r="V118" s="18"/>
+      <c r="W118" s="17"/>
+      <c r="X118" s="17"/>
+      <c r="Y118" s="17"/>
+      <c r="Z118" s="17"/>
+      <c r="AA118" s="17"/>
       <c r="AB118" s="13" t="s">
         <v>20</v>
       </c>
@@ -19895,31 +19901,31 @@
       <c r="H119" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I119" s="12">
-        <v>1</v>
-      </c>
-      <c r="J119" s="12">
+      <c r="I119" s="17">
+        <v>1</v>
+      </c>
+      <c r="J119" s="17">
         <v>6</v>
       </c>
-      <c r="K119" s="12">
-        <v>7</v>
-      </c>
-      <c r="L119" s="12"/>
-      <c r="M119" s="12"/>
-      <c r="N119" s="13"/>
-      <c r="O119" s="13"/>
-      <c r="P119" s="12"/>
-      <c r="Q119" s="12"/>
-      <c r="R119" s="12"/>
-      <c r="S119" s="12"/>
-      <c r="T119" s="12"/>
-      <c r="U119" s="13"/>
-      <c r="V119" s="13"/>
-      <c r="W119" s="12"/>
-      <c r="X119" s="12"/>
-      <c r="Y119" s="12"/>
-      <c r="Z119" s="12"/>
-      <c r="AA119" s="12"/>
+      <c r="K119" s="17">
+        <v>7</v>
+      </c>
+      <c r="L119" s="17"/>
+      <c r="M119" s="17"/>
+      <c r="N119" s="18"/>
+      <c r="O119" s="18"/>
+      <c r="P119" s="17"/>
+      <c r="Q119" s="17"/>
+      <c r="R119" s="17"/>
+      <c r="S119" s="17"/>
+      <c r="T119" s="17"/>
+      <c r="U119" s="18"/>
+      <c r="V119" s="18"/>
+      <c r="W119" s="17"/>
+      <c r="X119" s="17"/>
+      <c r="Y119" s="17"/>
+      <c r="Z119" s="17"/>
+      <c r="AA119" s="17"/>
       <c r="AB119" s="13" t="s">
         <v>20</v>
       </c>
@@ -19955,31 +19961,31 @@
       <c r="H120" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I120" s="12">
-        <v>1</v>
-      </c>
-      <c r="J120" s="12">
+      <c r="I120" s="17">
+        <v>1</v>
+      </c>
+      <c r="J120" s="17">
         <v>6</v>
       </c>
-      <c r="K120" s="12">
-        <v>7</v>
-      </c>
-      <c r="L120" s="12"/>
-      <c r="M120" s="12"/>
-      <c r="N120" s="13"/>
-      <c r="O120" s="13"/>
-      <c r="P120" s="12"/>
-      <c r="Q120" s="12"/>
-      <c r="R120" s="12"/>
-      <c r="S120" s="12"/>
-      <c r="T120" s="12"/>
-      <c r="U120" s="13"/>
-      <c r="V120" s="13"/>
-      <c r="W120" s="12"/>
-      <c r="X120" s="12"/>
-      <c r="Y120" s="12"/>
-      <c r="Z120" s="12"/>
-      <c r="AA120" s="12"/>
+      <c r="K120" s="17">
+        <v>7</v>
+      </c>
+      <c r="L120" s="17"/>
+      <c r="M120" s="17"/>
+      <c r="N120" s="18"/>
+      <c r="O120" s="18"/>
+      <c r="P120" s="17"/>
+      <c r="Q120" s="17"/>
+      <c r="R120" s="17"/>
+      <c r="S120" s="17"/>
+      <c r="T120" s="17"/>
+      <c r="U120" s="18"/>
+      <c r="V120" s="18"/>
+      <c r="W120" s="17"/>
+      <c r="X120" s="17"/>
+      <c r="Y120" s="17"/>
+      <c r="Z120" s="17"/>
+      <c r="AA120" s="17"/>
       <c r="AB120" s="13" t="s">
         <v>20</v>
       </c>
@@ -20015,31 +20021,31 @@
       <c r="H121" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I121" s="12">
-        <v>1</v>
-      </c>
-      <c r="J121" s="12">
+      <c r="I121" s="17">
+        <v>1</v>
+      </c>
+      <c r="J121" s="17">
         <v>6</v>
       </c>
-      <c r="K121" s="12">
-        <v>7</v>
-      </c>
-      <c r="L121" s="12"/>
-      <c r="M121" s="12"/>
-      <c r="N121" s="13"/>
-      <c r="O121" s="13"/>
-      <c r="P121" s="12"/>
-      <c r="Q121" s="12"/>
-      <c r="R121" s="12"/>
-      <c r="S121" s="12"/>
-      <c r="T121" s="12"/>
-      <c r="U121" s="13"/>
-      <c r="V121" s="13"/>
-      <c r="W121" s="12"/>
-      <c r="X121" s="12"/>
-      <c r="Y121" s="12"/>
-      <c r="Z121" s="12"/>
-      <c r="AA121" s="12"/>
+      <c r="K121" s="17">
+        <v>7</v>
+      </c>
+      <c r="L121" s="17"/>
+      <c r="M121" s="17"/>
+      <c r="N121" s="18"/>
+      <c r="O121" s="18"/>
+      <c r="P121" s="17"/>
+      <c r="Q121" s="17"/>
+      <c r="R121" s="17"/>
+      <c r="S121" s="17"/>
+      <c r="T121" s="17"/>
+      <c r="U121" s="18"/>
+      <c r="V121" s="18"/>
+      <c r="W121" s="17"/>
+      <c r="X121" s="17"/>
+      <c r="Y121" s="17"/>
+      <c r="Z121" s="17"/>
+      <c r="AA121" s="17"/>
       <c r="AB121" s="13" t="s">
         <v>20</v>
       </c>
@@ -20075,35 +20081,35 @@
       <c r="H122" s="10">
         <v>0.254</v>
       </c>
-      <c r="I122" s="12">
-        <v>1</v>
-      </c>
-      <c r="J122" s="12">
-        <v>2</v>
-      </c>
-      <c r="K122" s="12">
-        <v>8</v>
-      </c>
-      <c r="L122" s="12">
-        <v>1</v>
-      </c>
-      <c r="M122" s="12">
-        <v>7</v>
-      </c>
-      <c r="N122" s="13"/>
-      <c r="O122" s="13"/>
-      <c r="P122" s="12"/>
-      <c r="Q122" s="12"/>
-      <c r="R122" s="12"/>
-      <c r="S122" s="12"/>
-      <c r="T122" s="12"/>
-      <c r="U122" s="13"/>
-      <c r="V122" s="13"/>
-      <c r="W122" s="12"/>
-      <c r="X122" s="12"/>
-      <c r="Y122" s="12"/>
-      <c r="Z122" s="12"/>
-      <c r="AA122" s="12"/>
+      <c r="I122" s="17">
+        <v>1</v>
+      </c>
+      <c r="J122" s="17">
+        <v>2</v>
+      </c>
+      <c r="K122" s="17">
+        <v>8</v>
+      </c>
+      <c r="L122" s="17">
+        <v>1</v>
+      </c>
+      <c r="M122" s="17">
+        <v>7</v>
+      </c>
+      <c r="N122" s="18"/>
+      <c r="O122" s="18"/>
+      <c r="P122" s="17"/>
+      <c r="Q122" s="17"/>
+      <c r="R122" s="17"/>
+      <c r="S122" s="17"/>
+      <c r="T122" s="17"/>
+      <c r="U122" s="18"/>
+      <c r="V122" s="18"/>
+      <c r="W122" s="17"/>
+      <c r="X122" s="17"/>
+      <c r="Y122" s="17"/>
+      <c r="Z122" s="17"/>
+      <c r="AA122" s="17"/>
       <c r="AB122" s="13" t="s">
         <v>20</v>
       </c>
@@ -20139,35 +20145,35 @@
       <c r="H123" s="10">
         <v>0.254</v>
       </c>
-      <c r="I123" s="12">
-        <v>1</v>
-      </c>
-      <c r="J123" s="12">
-        <v>2</v>
-      </c>
-      <c r="K123" s="12">
-        <v>8</v>
-      </c>
-      <c r="L123" s="12">
-        <v>1</v>
-      </c>
-      <c r="M123" s="12">
-        <v>7</v>
-      </c>
-      <c r="N123" s="13"/>
-      <c r="O123" s="13"/>
-      <c r="P123" s="12"/>
-      <c r="Q123" s="12"/>
-      <c r="R123" s="12"/>
-      <c r="S123" s="12"/>
-      <c r="T123" s="12"/>
-      <c r="U123" s="13"/>
-      <c r="V123" s="13"/>
-      <c r="W123" s="12"/>
-      <c r="X123" s="12"/>
-      <c r="Y123" s="12"/>
-      <c r="Z123" s="12"/>
-      <c r="AA123" s="12"/>
+      <c r="I123" s="17">
+        <v>1</v>
+      </c>
+      <c r="J123" s="17">
+        <v>2</v>
+      </c>
+      <c r="K123" s="17">
+        <v>8</v>
+      </c>
+      <c r="L123" s="17">
+        <v>1</v>
+      </c>
+      <c r="M123" s="17">
+        <v>7</v>
+      </c>
+      <c r="N123" s="18"/>
+      <c r="O123" s="18"/>
+      <c r="P123" s="17"/>
+      <c r="Q123" s="17"/>
+      <c r="R123" s="17"/>
+      <c r="S123" s="17"/>
+      <c r="T123" s="17"/>
+      <c r="U123" s="18"/>
+      <c r="V123" s="18"/>
+      <c r="W123" s="17"/>
+      <c r="X123" s="17"/>
+      <c r="Y123" s="17"/>
+      <c r="Z123" s="17"/>
+      <c r="AA123" s="17"/>
       <c r="AB123" s="13" t="s">
         <v>20</v>
       </c>
@@ -20203,35 +20209,35 @@
       <c r="H124" s="10">
         <v>0.254</v>
       </c>
-      <c r="I124" s="12">
-        <v>1</v>
-      </c>
-      <c r="J124" s="12">
+      <c r="I124" s="17">
+        <v>1</v>
+      </c>
+      <c r="J124" s="17">
         <v>3</v>
       </c>
-      <c r="K124" s="12">
-        <v>8</v>
-      </c>
-      <c r="L124" s="12">
-        <v>2</v>
-      </c>
-      <c r="M124" s="12">
-        <v>7</v>
-      </c>
-      <c r="N124" s="13"/>
-      <c r="O124" s="13"/>
-      <c r="P124" s="12"/>
-      <c r="Q124" s="12"/>
-      <c r="R124" s="12"/>
-      <c r="S124" s="12"/>
-      <c r="T124" s="12"/>
-      <c r="U124" s="13"/>
-      <c r="V124" s="13"/>
-      <c r="W124" s="12"/>
-      <c r="X124" s="12"/>
-      <c r="Y124" s="12"/>
-      <c r="Z124" s="12"/>
-      <c r="AA124" s="12"/>
+      <c r="K124" s="17">
+        <v>8</v>
+      </c>
+      <c r="L124" s="17">
+        <v>2</v>
+      </c>
+      <c r="M124" s="17">
+        <v>7</v>
+      </c>
+      <c r="N124" s="18"/>
+      <c r="O124" s="18"/>
+      <c r="P124" s="17"/>
+      <c r="Q124" s="17"/>
+      <c r="R124" s="17"/>
+      <c r="S124" s="17"/>
+      <c r="T124" s="17"/>
+      <c r="U124" s="18"/>
+      <c r="V124" s="18"/>
+      <c r="W124" s="17"/>
+      <c r="X124" s="17"/>
+      <c r="Y124" s="17"/>
+      <c r="Z124" s="17"/>
+      <c r="AA124" s="17"/>
       <c r="AB124" s="13" t="s">
         <v>20</v>
       </c>
@@ -20267,35 +20273,35 @@
       <c r="H125" s="10">
         <v>0.254</v>
       </c>
-      <c r="I125" s="12">
-        <v>1</v>
-      </c>
-      <c r="J125" s="12">
-        <v>2</v>
-      </c>
-      <c r="K125" s="12">
-        <v>8</v>
-      </c>
-      <c r="L125" s="12">
-        <v>1</v>
-      </c>
-      <c r="M125" s="12">
-        <v>7</v>
-      </c>
-      <c r="N125" s="13"/>
-      <c r="O125" s="13"/>
-      <c r="P125" s="12"/>
-      <c r="Q125" s="12"/>
-      <c r="R125" s="12"/>
-      <c r="S125" s="12"/>
-      <c r="T125" s="12"/>
-      <c r="U125" s="13"/>
-      <c r="V125" s="13"/>
-      <c r="W125" s="12"/>
-      <c r="X125" s="12"/>
-      <c r="Y125" s="12"/>
-      <c r="Z125" s="12"/>
-      <c r="AA125" s="12"/>
+      <c r="I125" s="17">
+        <v>1</v>
+      </c>
+      <c r="J125" s="17">
+        <v>2</v>
+      </c>
+      <c r="K125" s="17">
+        <v>8</v>
+      </c>
+      <c r="L125" s="17">
+        <v>1</v>
+      </c>
+      <c r="M125" s="17">
+        <v>7</v>
+      </c>
+      <c r="N125" s="18"/>
+      <c r="O125" s="18"/>
+      <c r="P125" s="17"/>
+      <c r="Q125" s="17"/>
+      <c r="R125" s="17"/>
+      <c r="S125" s="17"/>
+      <c r="T125" s="17"/>
+      <c r="U125" s="18"/>
+      <c r="V125" s="18"/>
+      <c r="W125" s="17"/>
+      <c r="X125" s="17"/>
+      <c r="Y125" s="17"/>
+      <c r="Z125" s="17"/>
+      <c r="AA125" s="17"/>
       <c r="AB125" s="13" t="s">
         <v>20</v>
       </c>
@@ -20331,31 +20337,31 @@
       <c r="H126" s="10">
         <v>0.254</v>
       </c>
-      <c r="I126" s="12">
-        <v>1</v>
-      </c>
-      <c r="J126" s="12">
+      <c r="I126" s="17">
+        <v>1</v>
+      </c>
+      <c r="J126" s="17">
         <v>4</v>
       </c>
-      <c r="K126" s="12">
-        <v>7</v>
-      </c>
-      <c r="L126" s="12"/>
-      <c r="M126" s="12"/>
-      <c r="N126" s="13"/>
-      <c r="O126" s="13"/>
-      <c r="P126" s="12"/>
-      <c r="Q126" s="12"/>
-      <c r="R126" s="12"/>
-      <c r="S126" s="12"/>
-      <c r="T126" s="12"/>
-      <c r="U126" s="13"/>
-      <c r="V126" s="13"/>
-      <c r="W126" s="12"/>
-      <c r="X126" s="12"/>
-      <c r="Y126" s="12"/>
-      <c r="Z126" s="12"/>
-      <c r="AA126" s="12"/>
+      <c r="K126" s="17">
+        <v>7</v>
+      </c>
+      <c r="L126" s="17"/>
+      <c r="M126" s="17"/>
+      <c r="N126" s="18"/>
+      <c r="O126" s="18"/>
+      <c r="P126" s="17"/>
+      <c r="Q126" s="17"/>
+      <c r="R126" s="17"/>
+      <c r="S126" s="17"/>
+      <c r="T126" s="17"/>
+      <c r="U126" s="18"/>
+      <c r="V126" s="18"/>
+      <c r="W126" s="17"/>
+      <c r="X126" s="17"/>
+      <c r="Y126" s="17"/>
+      <c r="Z126" s="17"/>
+      <c r="AA126" s="17"/>
       <c r="AB126" s="13" t="s">
         <v>20</v>
       </c>
@@ -20391,31 +20397,31 @@
       <c r="H127" s="10">
         <v>0.254</v>
       </c>
-      <c r="I127" s="12">
-        <v>1</v>
-      </c>
-      <c r="J127" s="12">
+      <c r="I127" s="17">
+        <v>1</v>
+      </c>
+      <c r="J127" s="17">
         <v>4</v>
       </c>
-      <c r="K127" s="12">
-        <v>7</v>
-      </c>
-      <c r="L127" s="12"/>
-      <c r="M127" s="12"/>
-      <c r="N127" s="13"/>
-      <c r="O127" s="13"/>
-      <c r="P127" s="12"/>
-      <c r="Q127" s="12"/>
-      <c r="R127" s="12"/>
-      <c r="S127" s="12"/>
-      <c r="T127" s="12"/>
-      <c r="U127" s="13"/>
-      <c r="V127" s="13"/>
-      <c r="W127" s="12"/>
-      <c r="X127" s="12"/>
-      <c r="Y127" s="12"/>
-      <c r="Z127" s="12"/>
-      <c r="AA127" s="12"/>
+      <c r="K127" s="17">
+        <v>7</v>
+      </c>
+      <c r="L127" s="17"/>
+      <c r="M127" s="17"/>
+      <c r="N127" s="18"/>
+      <c r="O127" s="18"/>
+      <c r="P127" s="17"/>
+      <c r="Q127" s="17"/>
+      <c r="R127" s="17"/>
+      <c r="S127" s="17"/>
+      <c r="T127" s="17"/>
+      <c r="U127" s="18"/>
+      <c r="V127" s="18"/>
+      <c r="W127" s="17"/>
+      <c r="X127" s="17"/>
+      <c r="Y127" s="17"/>
+      <c r="Z127" s="17"/>
+      <c r="AA127" s="17"/>
       <c r="AB127" s="13" t="s">
         <v>20</v>
       </c>
@@ -20451,31 +20457,31 @@
       <c r="H128" s="10">
         <v>0.254</v>
       </c>
-      <c r="I128" s="12">
-        <v>1</v>
-      </c>
-      <c r="J128" s="12">
+      <c r="I128" s="17">
+        <v>1</v>
+      </c>
+      <c r="J128" s="17">
         <v>4</v>
       </c>
-      <c r="K128" s="12">
-        <v>7</v>
-      </c>
-      <c r="L128" s="12"/>
-      <c r="M128" s="12"/>
-      <c r="N128" s="13"/>
-      <c r="O128" s="13"/>
-      <c r="P128" s="12"/>
-      <c r="Q128" s="12"/>
-      <c r="R128" s="12"/>
-      <c r="S128" s="12"/>
-      <c r="T128" s="12"/>
-      <c r="U128" s="13"/>
-      <c r="V128" s="13"/>
-      <c r="W128" s="12"/>
-      <c r="X128" s="12"/>
-      <c r="Y128" s="12"/>
-      <c r="Z128" s="12"/>
-      <c r="AA128" s="12"/>
+      <c r="K128" s="17">
+        <v>7</v>
+      </c>
+      <c r="L128" s="17"/>
+      <c r="M128" s="17"/>
+      <c r="N128" s="18"/>
+      <c r="O128" s="18"/>
+      <c r="P128" s="17"/>
+      <c r="Q128" s="17"/>
+      <c r="R128" s="17"/>
+      <c r="S128" s="17"/>
+      <c r="T128" s="17"/>
+      <c r="U128" s="18"/>
+      <c r="V128" s="18"/>
+      <c r="W128" s="17"/>
+      <c r="X128" s="17"/>
+      <c r="Y128" s="17"/>
+      <c r="Z128" s="17"/>
+      <c r="AA128" s="17"/>
       <c r="AB128" s="13" t="s">
         <v>20</v>
       </c>
@@ -20511,35 +20517,35 @@
       <c r="H129" s="10">
         <v>0.254</v>
       </c>
-      <c r="I129" s="12">
-        <v>1</v>
-      </c>
-      <c r="J129" s="12">
-        <v>2</v>
-      </c>
-      <c r="K129" s="12">
-        <v>8</v>
-      </c>
-      <c r="L129" s="12">
-        <v>1</v>
-      </c>
-      <c r="M129" s="12">
-        <v>7</v>
-      </c>
-      <c r="N129" s="13"/>
-      <c r="O129" s="13"/>
-      <c r="P129" s="12"/>
-      <c r="Q129" s="12"/>
-      <c r="R129" s="12"/>
-      <c r="S129" s="12"/>
-      <c r="T129" s="12"/>
-      <c r="U129" s="13"/>
-      <c r="V129" s="13"/>
-      <c r="W129" s="12"/>
-      <c r="X129" s="12"/>
-      <c r="Y129" s="12"/>
-      <c r="Z129" s="12"/>
-      <c r="AA129" s="12"/>
+      <c r="I129" s="17">
+        <v>1</v>
+      </c>
+      <c r="J129" s="17">
+        <v>2</v>
+      </c>
+      <c r="K129" s="17">
+        <v>8</v>
+      </c>
+      <c r="L129" s="17">
+        <v>1</v>
+      </c>
+      <c r="M129" s="17">
+        <v>7</v>
+      </c>
+      <c r="N129" s="18"/>
+      <c r="O129" s="18"/>
+      <c r="P129" s="17"/>
+      <c r="Q129" s="17"/>
+      <c r="R129" s="17"/>
+      <c r="S129" s="17"/>
+      <c r="T129" s="17"/>
+      <c r="U129" s="18"/>
+      <c r="V129" s="18"/>
+      <c r="W129" s="17"/>
+      <c r="X129" s="17"/>
+      <c r="Y129" s="17"/>
+      <c r="Z129" s="17"/>
+      <c r="AA129" s="17"/>
       <c r="AB129" s="13" t="s">
         <v>20</v>
       </c>
@@ -20575,31 +20581,31 @@
       <c r="H130" s="10">
         <v>0.44</v>
       </c>
-      <c r="I130" s="12">
-        <v>1</v>
-      </c>
-      <c r="J130" s="12">
-        <v>7</v>
-      </c>
-      <c r="K130" s="12">
-        <v>8</v>
-      </c>
-      <c r="L130" s="12"/>
-      <c r="M130" s="12"/>
-      <c r="N130" s="13"/>
-      <c r="O130" s="13"/>
-      <c r="P130" s="12"/>
-      <c r="Q130" s="12"/>
-      <c r="R130" s="12"/>
-      <c r="S130" s="12"/>
-      <c r="T130" s="12"/>
-      <c r="U130" s="13"/>
-      <c r="V130" s="13"/>
-      <c r="W130" s="12"/>
-      <c r="X130" s="12"/>
-      <c r="Y130" s="12"/>
-      <c r="Z130" s="12"/>
-      <c r="AA130" s="12"/>
+      <c r="I130" s="17">
+        <v>1</v>
+      </c>
+      <c r="J130" s="17">
+        <v>7</v>
+      </c>
+      <c r="K130" s="17">
+        <v>8</v>
+      </c>
+      <c r="L130" s="17"/>
+      <c r="M130" s="17"/>
+      <c r="N130" s="18"/>
+      <c r="O130" s="18"/>
+      <c r="P130" s="17"/>
+      <c r="Q130" s="17"/>
+      <c r="R130" s="17"/>
+      <c r="S130" s="17"/>
+      <c r="T130" s="17"/>
+      <c r="U130" s="18"/>
+      <c r="V130" s="18"/>
+      <c r="W130" s="17"/>
+      <c r="X130" s="17"/>
+      <c r="Y130" s="17"/>
+      <c r="Z130" s="17"/>
+      <c r="AA130" s="17"/>
       <c r="AB130" s="13" t="s">
         <v>20</v>
       </c>
@@ -20635,31 +20641,31 @@
       <c r="H131" s="10">
         <v>0.44</v>
       </c>
-      <c r="I131" s="12">
-        <v>1</v>
-      </c>
-      <c r="J131" s="12">
-        <v>7</v>
-      </c>
-      <c r="K131" s="12">
-        <v>8</v>
-      </c>
-      <c r="L131" s="12"/>
-      <c r="M131" s="12"/>
-      <c r="N131" s="13"/>
-      <c r="O131" s="13"/>
-      <c r="P131" s="12"/>
-      <c r="Q131" s="12"/>
-      <c r="R131" s="12"/>
-      <c r="S131" s="12"/>
-      <c r="T131" s="12"/>
-      <c r="U131" s="13"/>
-      <c r="V131" s="13"/>
-      <c r="W131" s="12"/>
-      <c r="X131" s="12"/>
-      <c r="Y131" s="12"/>
-      <c r="Z131" s="12"/>
-      <c r="AA131" s="12"/>
+      <c r="I131" s="17">
+        <v>1</v>
+      </c>
+      <c r="J131" s="17">
+        <v>7</v>
+      </c>
+      <c r="K131" s="17">
+        <v>8</v>
+      </c>
+      <c r="L131" s="17"/>
+      <c r="M131" s="17"/>
+      <c r="N131" s="18"/>
+      <c r="O131" s="18"/>
+      <c r="P131" s="17"/>
+      <c r="Q131" s="17"/>
+      <c r="R131" s="17"/>
+      <c r="S131" s="17"/>
+      <c r="T131" s="17"/>
+      <c r="U131" s="18"/>
+      <c r="V131" s="18"/>
+      <c r="W131" s="17"/>
+      <c r="X131" s="17"/>
+      <c r="Y131" s="17"/>
+      <c r="Z131" s="17"/>
+      <c r="AA131" s="17"/>
       <c r="AB131" s="13" t="s">
         <v>20</v>
       </c>
@@ -20695,35 +20701,35 @@
       <c r="H132" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I132" s="12">
-        <v>1</v>
-      </c>
-      <c r="J132" s="12">
+      <c r="I132" s="17">
+        <v>1</v>
+      </c>
+      <c r="J132" s="17">
         <v>3</v>
       </c>
-      <c r="K132" s="12">
-        <v>7</v>
-      </c>
-      <c r="L132" s="12">
+      <c r="K132" s="17">
+        <v>7</v>
+      </c>
+      <c r="L132" s="17">
         <v>5</v>
       </c>
-      <c r="M132" s="12">
-        <v>8</v>
-      </c>
-      <c r="N132" s="13"/>
-      <c r="O132" s="13"/>
-      <c r="P132" s="12"/>
-      <c r="Q132" s="12"/>
-      <c r="R132" s="12"/>
-      <c r="S132" s="12"/>
-      <c r="T132" s="12"/>
-      <c r="U132" s="13"/>
-      <c r="V132" s="13"/>
-      <c r="W132" s="12"/>
-      <c r="X132" s="12"/>
-      <c r="Y132" s="12"/>
-      <c r="Z132" s="12"/>
-      <c r="AA132" s="12"/>
+      <c r="M132" s="17">
+        <v>8</v>
+      </c>
+      <c r="N132" s="18"/>
+      <c r="O132" s="18"/>
+      <c r="P132" s="17"/>
+      <c r="Q132" s="17"/>
+      <c r="R132" s="17"/>
+      <c r="S132" s="17"/>
+      <c r="T132" s="17"/>
+      <c r="U132" s="18"/>
+      <c r="V132" s="18"/>
+      <c r="W132" s="17"/>
+      <c r="X132" s="17"/>
+      <c r="Y132" s="17"/>
+      <c r="Z132" s="17"/>
+      <c r="AA132" s="17"/>
       <c r="AB132" s="13" t="s">
         <v>20</v>
       </c>
@@ -20759,35 +20765,35 @@
       <c r="H133" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I133" s="12">
-        <v>1</v>
-      </c>
-      <c r="J133" s="12">
+      <c r="I133" s="17">
+        <v>1</v>
+      </c>
+      <c r="J133" s="17">
         <v>3</v>
       </c>
-      <c r="K133" s="12">
-        <v>7</v>
-      </c>
-      <c r="L133" s="12">
+      <c r="K133" s="17">
+        <v>7</v>
+      </c>
+      <c r="L133" s="17">
         <v>5</v>
       </c>
-      <c r="M133" s="12">
-        <v>8</v>
-      </c>
-      <c r="N133" s="13"/>
-      <c r="O133" s="13"/>
-      <c r="P133" s="12"/>
-      <c r="Q133" s="12"/>
-      <c r="R133" s="12"/>
-      <c r="S133" s="12"/>
-      <c r="T133" s="12"/>
-      <c r="U133" s="13"/>
-      <c r="V133" s="13"/>
-      <c r="W133" s="12"/>
-      <c r="X133" s="12"/>
-      <c r="Y133" s="12"/>
-      <c r="Z133" s="12"/>
-      <c r="AA133" s="12"/>
+      <c r="M133" s="17">
+        <v>8</v>
+      </c>
+      <c r="N133" s="18"/>
+      <c r="O133" s="18"/>
+      <c r="P133" s="17"/>
+      <c r="Q133" s="17"/>
+      <c r="R133" s="17"/>
+      <c r="S133" s="17"/>
+      <c r="T133" s="17"/>
+      <c r="U133" s="18"/>
+      <c r="V133" s="18"/>
+      <c r="W133" s="17"/>
+      <c r="X133" s="17"/>
+      <c r="Y133" s="17"/>
+      <c r="Z133" s="17"/>
+      <c r="AA133" s="17"/>
       <c r="AB133" s="13" t="s">
         <v>20</v>
       </c>
@@ -20823,31 +20829,31 @@
       <c r="H134" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I134" s="12">
+      <c r="I134" s="17">
         <v>4</v>
       </c>
-      <c r="J134" s="12">
+      <c r="J134" s="17">
         <v>3</v>
       </c>
-      <c r="K134" s="12">
-        <v>7</v>
-      </c>
-      <c r="L134" s="12"/>
-      <c r="M134" s="12"/>
-      <c r="N134" s="13"/>
-      <c r="O134" s="13"/>
-      <c r="P134" s="12"/>
-      <c r="Q134" s="12"/>
-      <c r="R134" s="12"/>
-      <c r="S134" s="12"/>
-      <c r="T134" s="12"/>
-      <c r="U134" s="13"/>
-      <c r="V134" s="13"/>
-      <c r="W134" s="12"/>
-      <c r="X134" s="12"/>
-      <c r="Y134" s="12"/>
-      <c r="Z134" s="12"/>
-      <c r="AA134" s="12"/>
+      <c r="K134" s="17">
+        <v>7</v>
+      </c>
+      <c r="L134" s="17"/>
+      <c r="M134" s="17"/>
+      <c r="N134" s="18"/>
+      <c r="O134" s="18"/>
+      <c r="P134" s="17"/>
+      <c r="Q134" s="17"/>
+      <c r="R134" s="17"/>
+      <c r="S134" s="17"/>
+      <c r="T134" s="17"/>
+      <c r="U134" s="18"/>
+      <c r="V134" s="18"/>
+      <c r="W134" s="17"/>
+      <c r="X134" s="17"/>
+      <c r="Y134" s="17"/>
+      <c r="Z134" s="17"/>
+      <c r="AA134" s="17"/>
       <c r="AB134" s="13" t="s">
         <v>20</v>
       </c>
@@ -20883,35 +20889,35 @@
       <c r="H135" s="10">
         <v>0.254</v>
       </c>
-      <c r="I135" s="12">
-        <v>1</v>
-      </c>
-      <c r="J135" s="12">
+      <c r="I135" s="17">
+        <v>1</v>
+      </c>
+      <c r="J135" s="17">
         <v>3</v>
       </c>
-      <c r="K135" s="12">
-        <v>8</v>
-      </c>
-      <c r="L135" s="12">
-        <v>2</v>
-      </c>
-      <c r="M135" s="12">
-        <v>7</v>
-      </c>
-      <c r="N135" s="13"/>
-      <c r="O135" s="13"/>
-      <c r="P135" s="12"/>
-      <c r="Q135" s="12"/>
-      <c r="R135" s="12"/>
-      <c r="S135" s="12"/>
-      <c r="T135" s="12"/>
-      <c r="U135" s="13"/>
-      <c r="V135" s="13"/>
-      <c r="W135" s="12"/>
-      <c r="X135" s="12"/>
-      <c r="Y135" s="12"/>
-      <c r="Z135" s="12"/>
-      <c r="AA135" s="12"/>
+      <c r="K135" s="17">
+        <v>8</v>
+      </c>
+      <c r="L135" s="17">
+        <v>2</v>
+      </c>
+      <c r="M135" s="17">
+        <v>7</v>
+      </c>
+      <c r="N135" s="18"/>
+      <c r="O135" s="18"/>
+      <c r="P135" s="17"/>
+      <c r="Q135" s="17"/>
+      <c r="R135" s="17"/>
+      <c r="S135" s="17"/>
+      <c r="T135" s="17"/>
+      <c r="U135" s="18"/>
+      <c r="V135" s="18"/>
+      <c r="W135" s="17"/>
+      <c r="X135" s="17"/>
+      <c r="Y135" s="17"/>
+      <c r="Z135" s="17"/>
+      <c r="AA135" s="17"/>
       <c r="AB135" s="13" t="s">
         <v>20</v>
       </c>
@@ -20947,31 +20953,31 @@
       <c r="H136" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I136" s="12">
-        <v>1</v>
-      </c>
-      <c r="J136" s="12">
+      <c r="I136" s="17">
+        <v>1</v>
+      </c>
+      <c r="J136" s="17">
         <v>4</v>
       </c>
-      <c r="K136" s="12">
-        <v>7</v>
-      </c>
-      <c r="L136" s="12"/>
-      <c r="M136" s="12"/>
-      <c r="N136" s="13"/>
-      <c r="O136" s="13"/>
-      <c r="P136" s="12"/>
-      <c r="Q136" s="12"/>
-      <c r="R136" s="12"/>
-      <c r="S136" s="12"/>
-      <c r="T136" s="12"/>
-      <c r="U136" s="13"/>
-      <c r="V136" s="13"/>
-      <c r="W136" s="12"/>
-      <c r="X136" s="12"/>
-      <c r="Y136" s="12"/>
-      <c r="Z136" s="12"/>
-      <c r="AA136" s="12"/>
+      <c r="K136" s="17">
+        <v>7</v>
+      </c>
+      <c r="L136" s="17"/>
+      <c r="M136" s="17"/>
+      <c r="N136" s="18"/>
+      <c r="O136" s="18"/>
+      <c r="P136" s="17"/>
+      <c r="Q136" s="17"/>
+      <c r="R136" s="17"/>
+      <c r="S136" s="17"/>
+      <c r="T136" s="17"/>
+      <c r="U136" s="18"/>
+      <c r="V136" s="18"/>
+      <c r="W136" s="17"/>
+      <c r="X136" s="17"/>
+      <c r="Y136" s="17"/>
+      <c r="Z136" s="17"/>
+      <c r="AA136" s="17"/>
       <c r="AB136" s="13" t="s">
         <v>20</v>
       </c>
@@ -21007,31 +21013,31 @@
       <c r="H137" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I137" s="12">
-        <v>1</v>
-      </c>
-      <c r="J137" s="12">
+      <c r="I137" s="17">
+        <v>1</v>
+      </c>
+      <c r="J137" s="17">
         <v>4</v>
       </c>
-      <c r="K137" s="12">
-        <v>7</v>
-      </c>
-      <c r="L137" s="12"/>
-      <c r="M137" s="12"/>
-      <c r="N137" s="13"/>
-      <c r="O137" s="13"/>
-      <c r="P137" s="12"/>
-      <c r="Q137" s="12"/>
-      <c r="R137" s="12"/>
-      <c r="S137" s="12"/>
-      <c r="T137" s="12"/>
-      <c r="U137" s="13"/>
-      <c r="V137" s="13"/>
-      <c r="W137" s="12"/>
-      <c r="X137" s="12"/>
-      <c r="Y137" s="12"/>
-      <c r="Z137" s="12"/>
-      <c r="AA137" s="12"/>
+      <c r="K137" s="17">
+        <v>7</v>
+      </c>
+      <c r="L137" s="17"/>
+      <c r="M137" s="17"/>
+      <c r="N137" s="18"/>
+      <c r="O137" s="18"/>
+      <c r="P137" s="17"/>
+      <c r="Q137" s="17"/>
+      <c r="R137" s="17"/>
+      <c r="S137" s="17"/>
+      <c r="T137" s="17"/>
+      <c r="U137" s="18"/>
+      <c r="V137" s="18"/>
+      <c r="W137" s="17"/>
+      <c r="X137" s="17"/>
+      <c r="Y137" s="17"/>
+      <c r="Z137" s="17"/>
+      <c r="AA137" s="17"/>
       <c r="AB137" s="13" t="s">
         <v>20</v>
       </c>
@@ -21067,35 +21073,35 @@
       <c r="H138" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I138" s="12">
+      <c r="I138" s="17">
         <v>6</v>
       </c>
-      <c r="J138" s="12">
+      <c r="J138" s="17">
         <v>6</v>
       </c>
-      <c r="K138" s="12">
-        <v>8</v>
-      </c>
-      <c r="L138" s="12">
-        <v>2</v>
-      </c>
-      <c r="M138" s="12">
-        <v>7</v>
-      </c>
-      <c r="N138" s="13"/>
-      <c r="O138" s="13"/>
-      <c r="P138" s="12"/>
-      <c r="Q138" s="12"/>
-      <c r="R138" s="12"/>
-      <c r="S138" s="12"/>
-      <c r="T138" s="12"/>
-      <c r="U138" s="13"/>
-      <c r="V138" s="13"/>
-      <c r="W138" s="12"/>
-      <c r="X138" s="12"/>
-      <c r="Y138" s="12"/>
-      <c r="Z138" s="12"/>
-      <c r="AA138" s="12"/>
+      <c r="K138" s="17">
+        <v>8</v>
+      </c>
+      <c r="L138" s="17">
+        <v>2</v>
+      </c>
+      <c r="M138" s="17">
+        <v>7</v>
+      </c>
+      <c r="N138" s="18"/>
+      <c r="O138" s="18"/>
+      <c r="P138" s="17"/>
+      <c r="Q138" s="17"/>
+      <c r="R138" s="17"/>
+      <c r="S138" s="17"/>
+      <c r="T138" s="17"/>
+      <c r="U138" s="18"/>
+      <c r="V138" s="18"/>
+      <c r="W138" s="17"/>
+      <c r="X138" s="17"/>
+      <c r="Y138" s="17"/>
+      <c r="Z138" s="17"/>
+      <c r="AA138" s="17"/>
       <c r="AB138" s="13" t="s">
         <v>20</v>
       </c>
@@ -21131,31 +21137,31 @@
       <c r="H139" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I139" s="12">
-        <v>1</v>
-      </c>
-      <c r="J139" s="12">
+      <c r="I139" s="17">
+        <v>1</v>
+      </c>
+      <c r="J139" s="17">
         <v>6</v>
       </c>
-      <c r="K139" s="12">
+      <c r="K139" s="17">
         <v>6</v>
       </c>
-      <c r="L139" s="12"/>
-      <c r="M139" s="12"/>
-      <c r="N139" s="13"/>
-      <c r="O139" s="13"/>
-      <c r="P139" s="12"/>
-      <c r="Q139" s="12"/>
-      <c r="R139" s="12"/>
-      <c r="S139" s="12"/>
-      <c r="T139" s="12"/>
-      <c r="U139" s="13"/>
-      <c r="V139" s="13"/>
-      <c r="W139" s="12"/>
-      <c r="X139" s="12"/>
-      <c r="Y139" s="12"/>
-      <c r="Z139" s="12"/>
-      <c r="AA139" s="12"/>
+      <c r="L139" s="17"/>
+      <c r="M139" s="17"/>
+      <c r="N139" s="18"/>
+      <c r="O139" s="18"/>
+      <c r="P139" s="17"/>
+      <c r="Q139" s="17"/>
+      <c r="R139" s="17"/>
+      <c r="S139" s="17"/>
+      <c r="T139" s="17"/>
+      <c r="U139" s="18"/>
+      <c r="V139" s="18"/>
+      <c r="W139" s="17"/>
+      <c r="X139" s="17"/>
+      <c r="Y139" s="17"/>
+      <c r="Z139" s="17"/>
+      <c r="AA139" s="17"/>
       <c r="AB139" s="13" t="s">
         <v>20</v>
       </c>
@@ -21191,31 +21197,31 @@
       <c r="H140" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I140" s="12">
-        <v>1</v>
-      </c>
-      <c r="J140" s="12">
+      <c r="I140" s="17">
+        <v>1</v>
+      </c>
+      <c r="J140" s="17">
         <v>6</v>
       </c>
-      <c r="K140" s="12">
-        <v>7</v>
-      </c>
-      <c r="L140" s="12"/>
-      <c r="M140" s="12"/>
-      <c r="N140" s="13"/>
-      <c r="O140" s="13"/>
-      <c r="P140" s="12"/>
-      <c r="Q140" s="12"/>
-      <c r="R140" s="12"/>
-      <c r="S140" s="12"/>
-      <c r="T140" s="12"/>
-      <c r="U140" s="13"/>
-      <c r="V140" s="13"/>
-      <c r="W140" s="12"/>
-      <c r="X140" s="12"/>
-      <c r="Y140" s="12"/>
-      <c r="Z140" s="12"/>
-      <c r="AA140" s="12"/>
+      <c r="K140" s="17">
+        <v>7</v>
+      </c>
+      <c r="L140" s="17"/>
+      <c r="M140" s="17"/>
+      <c r="N140" s="18"/>
+      <c r="O140" s="18"/>
+      <c r="P140" s="17"/>
+      <c r="Q140" s="17"/>
+      <c r="R140" s="17"/>
+      <c r="S140" s="17"/>
+      <c r="T140" s="17"/>
+      <c r="U140" s="18"/>
+      <c r="V140" s="18"/>
+      <c r="W140" s="17"/>
+      <c r="X140" s="17"/>
+      <c r="Y140" s="17"/>
+      <c r="Z140" s="17"/>
+      <c r="AA140" s="17"/>
       <c r="AB140" s="13" t="s">
         <v>20</v>
       </c>
@@ -21251,31 +21257,31 @@
       <c r="H141" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I141" s="12">
-        <v>1</v>
-      </c>
-      <c r="J141" s="12">
+      <c r="I141" s="17">
+        <v>1</v>
+      </c>
+      <c r="J141" s="17">
         <v>6</v>
       </c>
-      <c r="K141" s="12">
-        <v>7</v>
-      </c>
-      <c r="L141" s="12"/>
-      <c r="M141" s="12"/>
-      <c r="N141" s="13"/>
-      <c r="O141" s="13"/>
-      <c r="P141" s="12"/>
-      <c r="Q141" s="12"/>
-      <c r="R141" s="12"/>
-      <c r="S141" s="12"/>
-      <c r="T141" s="12"/>
-      <c r="U141" s="13"/>
-      <c r="V141" s="13"/>
-      <c r="W141" s="12"/>
-      <c r="X141" s="12"/>
-      <c r="Y141" s="12"/>
-      <c r="Z141" s="12"/>
-      <c r="AA141" s="12"/>
+      <c r="K141" s="17">
+        <v>7</v>
+      </c>
+      <c r="L141" s="17"/>
+      <c r="M141" s="17"/>
+      <c r="N141" s="18"/>
+      <c r="O141" s="18"/>
+      <c r="P141" s="17"/>
+      <c r="Q141" s="17"/>
+      <c r="R141" s="17"/>
+      <c r="S141" s="17"/>
+      <c r="T141" s="17"/>
+      <c r="U141" s="18"/>
+      <c r="V141" s="18"/>
+      <c r="W141" s="17"/>
+      <c r="X141" s="17"/>
+      <c r="Y141" s="17"/>
+      <c r="Z141" s="17"/>
+      <c r="AA141" s="17"/>
       <c r="AB141" s="13" t="s">
         <v>20</v>
       </c>
@@ -21311,31 +21317,31 @@
       <c r="H142" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I142" s="12">
-        <v>1</v>
-      </c>
-      <c r="J142" s="12">
+      <c r="I142" s="17">
+        <v>1</v>
+      </c>
+      <c r="J142" s="17">
         <v>6</v>
       </c>
-      <c r="K142" s="12">
+      <c r="K142" s="17">
         <v>6</v>
       </c>
-      <c r="L142" s="12"/>
-      <c r="M142" s="12"/>
-      <c r="N142" s="13"/>
-      <c r="O142" s="13"/>
-      <c r="P142" s="12"/>
-      <c r="Q142" s="12"/>
-      <c r="R142" s="12"/>
-      <c r="S142" s="12"/>
-      <c r="T142" s="12"/>
-      <c r="U142" s="13"/>
-      <c r="V142" s="13"/>
-      <c r="W142" s="12"/>
-      <c r="X142" s="12"/>
-      <c r="Y142" s="12"/>
-      <c r="Z142" s="12"/>
-      <c r="AA142" s="12"/>
+      <c r="L142" s="17"/>
+      <c r="M142" s="17"/>
+      <c r="N142" s="18"/>
+      <c r="O142" s="18"/>
+      <c r="P142" s="17"/>
+      <c r="Q142" s="17"/>
+      <c r="R142" s="17"/>
+      <c r="S142" s="17"/>
+      <c r="T142" s="17"/>
+      <c r="U142" s="18"/>
+      <c r="V142" s="18"/>
+      <c r="W142" s="17"/>
+      <c r="X142" s="17"/>
+      <c r="Y142" s="17"/>
+      <c r="Z142" s="17"/>
+      <c r="AA142" s="17"/>
       <c r="AB142" s="13" t="s">
         <v>20</v>
       </c>
@@ -21371,31 +21377,31 @@
       <c r="H143" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I143" s="12">
-        <v>1</v>
-      </c>
-      <c r="J143" s="12">
+      <c r="I143" s="17">
+        <v>1</v>
+      </c>
+      <c r="J143" s="17">
         <v>6</v>
       </c>
-      <c r="K143" s="12">
+      <c r="K143" s="17">
         <v>6</v>
       </c>
-      <c r="L143" s="12"/>
-      <c r="M143" s="12"/>
-      <c r="N143" s="13"/>
-      <c r="O143" s="13"/>
-      <c r="P143" s="12"/>
-      <c r="Q143" s="12"/>
-      <c r="R143" s="12"/>
-      <c r="S143" s="12"/>
-      <c r="T143" s="12"/>
-      <c r="U143" s="13"/>
-      <c r="V143" s="13"/>
-      <c r="W143" s="12"/>
-      <c r="X143" s="12"/>
-      <c r="Y143" s="12"/>
-      <c r="Z143" s="12"/>
-      <c r="AA143" s="12"/>
+      <c r="L143" s="17"/>
+      <c r="M143" s="17"/>
+      <c r="N143" s="18"/>
+      <c r="O143" s="18"/>
+      <c r="P143" s="17"/>
+      <c r="Q143" s="17"/>
+      <c r="R143" s="17"/>
+      <c r="S143" s="17"/>
+      <c r="T143" s="17"/>
+      <c r="U143" s="18"/>
+      <c r="V143" s="18"/>
+      <c r="W143" s="17"/>
+      <c r="X143" s="17"/>
+      <c r="Y143" s="17"/>
+      <c r="Z143" s="17"/>
+      <c r="AA143" s="17"/>
       <c r="AB143" s="13" t="s">
         <v>20</v>
       </c>
@@ -21431,35 +21437,35 @@
       <c r="H144" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I144" s="12">
-        <v>1</v>
-      </c>
-      <c r="J144" s="12">
-        <v>1</v>
-      </c>
-      <c r="K144" s="12">
-        <v>8</v>
-      </c>
-      <c r="L144" s="12">
+      <c r="I144" s="17">
+        <v>1</v>
+      </c>
+      <c r="J144" s="17">
+        <v>1</v>
+      </c>
+      <c r="K144" s="17">
+        <v>8</v>
+      </c>
+      <c r="L144" s="17">
         <v>3</v>
       </c>
-      <c r="M144" s="12">
-        <v>7</v>
-      </c>
-      <c r="N144" s="13"/>
-      <c r="O144" s="13"/>
-      <c r="P144" s="12"/>
-      <c r="Q144" s="12"/>
-      <c r="R144" s="12"/>
-      <c r="S144" s="12"/>
-      <c r="T144" s="12"/>
-      <c r="U144" s="13"/>
-      <c r="V144" s="13"/>
-      <c r="W144" s="12"/>
-      <c r="X144" s="12"/>
-      <c r="Y144" s="12"/>
-      <c r="Z144" s="12"/>
-      <c r="AA144" s="12"/>
+      <c r="M144" s="17">
+        <v>7</v>
+      </c>
+      <c r="N144" s="18"/>
+      <c r="O144" s="18"/>
+      <c r="P144" s="17"/>
+      <c r="Q144" s="17"/>
+      <c r="R144" s="17"/>
+      <c r="S144" s="17"/>
+      <c r="T144" s="17"/>
+      <c r="U144" s="18"/>
+      <c r="V144" s="18"/>
+      <c r="W144" s="17"/>
+      <c r="X144" s="17"/>
+      <c r="Y144" s="17"/>
+      <c r="Z144" s="17"/>
+      <c r="AA144" s="17"/>
       <c r="AB144" s="13" t="s">
         <v>20</v>
       </c>
@@ -21495,31 +21501,31 @@
       <c r="H145" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I145" s="12">
-        <v>1</v>
-      </c>
-      <c r="J145" s="12">
+      <c r="I145" s="17">
+        <v>1</v>
+      </c>
+      <c r="J145" s="17">
         <v>4</v>
       </c>
-      <c r="K145" s="12">
-        <v>7</v>
-      </c>
-      <c r="L145" s="12"/>
-      <c r="M145" s="12"/>
-      <c r="N145" s="13"/>
-      <c r="O145" s="13"/>
-      <c r="P145" s="12"/>
-      <c r="Q145" s="12"/>
-      <c r="R145" s="12"/>
-      <c r="S145" s="12"/>
-      <c r="T145" s="12"/>
-      <c r="U145" s="13"/>
-      <c r="V145" s="13"/>
-      <c r="W145" s="12"/>
-      <c r="X145" s="12"/>
-      <c r="Y145" s="12"/>
-      <c r="Z145" s="12"/>
-      <c r="AA145" s="12"/>
+      <c r="K145" s="17">
+        <v>7</v>
+      </c>
+      <c r="L145" s="17"/>
+      <c r="M145" s="17"/>
+      <c r="N145" s="18"/>
+      <c r="O145" s="18"/>
+      <c r="P145" s="17"/>
+      <c r="Q145" s="17"/>
+      <c r="R145" s="17"/>
+      <c r="S145" s="17"/>
+      <c r="T145" s="17"/>
+      <c r="U145" s="18"/>
+      <c r="V145" s="18"/>
+      <c r="W145" s="17"/>
+      <c r="X145" s="17"/>
+      <c r="Y145" s="17"/>
+      <c r="Z145" s="17"/>
+      <c r="AA145" s="17"/>
       <c r="AB145" s="13" t="s">
         <v>20</v>
       </c>
@@ -21555,31 +21561,31 @@
       <c r="H146" s="10">
         <v>0.254</v>
       </c>
-      <c r="I146" s="12">
-        <v>1</v>
-      </c>
-      <c r="J146" s="12">
-        <v>2</v>
-      </c>
-      <c r="K146" s="12">
-        <v>8</v>
-      </c>
-      <c r="L146" s="12"/>
-      <c r="M146" s="12"/>
-      <c r="N146" s="13"/>
-      <c r="O146" s="13"/>
-      <c r="P146" s="12"/>
-      <c r="Q146" s="12"/>
-      <c r="R146" s="12"/>
-      <c r="S146" s="12"/>
-      <c r="T146" s="12"/>
-      <c r="U146" s="13"/>
-      <c r="V146" s="13"/>
-      <c r="W146" s="12"/>
-      <c r="X146" s="12"/>
-      <c r="Y146" s="12"/>
-      <c r="Z146" s="12"/>
-      <c r="AA146" s="12"/>
+      <c r="I146" s="17">
+        <v>1</v>
+      </c>
+      <c r="J146" s="17">
+        <v>2</v>
+      </c>
+      <c r="K146" s="17">
+        <v>8</v>
+      </c>
+      <c r="L146" s="17"/>
+      <c r="M146" s="17"/>
+      <c r="N146" s="18"/>
+      <c r="O146" s="18"/>
+      <c r="P146" s="17"/>
+      <c r="Q146" s="17"/>
+      <c r="R146" s="17"/>
+      <c r="S146" s="17"/>
+      <c r="T146" s="17"/>
+      <c r="U146" s="18"/>
+      <c r="V146" s="18"/>
+      <c r="W146" s="17"/>
+      <c r="X146" s="17"/>
+      <c r="Y146" s="17"/>
+      <c r="Z146" s="17"/>
+      <c r="AA146" s="17"/>
       <c r="AB146" s="13" t="s">
         <v>20</v>
       </c>
@@ -21615,31 +21621,31 @@
       <c r="H147" s="10">
         <v>0.254</v>
       </c>
-      <c r="I147" s="12">
-        <v>1</v>
-      </c>
-      <c r="J147" s="12">
-        <v>2</v>
-      </c>
-      <c r="K147" s="12">
-        <v>8</v>
-      </c>
-      <c r="L147" s="12"/>
-      <c r="M147" s="12"/>
-      <c r="N147" s="13"/>
-      <c r="O147" s="13"/>
-      <c r="P147" s="12"/>
-      <c r="Q147" s="12"/>
-      <c r="R147" s="12"/>
-      <c r="S147" s="12"/>
-      <c r="T147" s="12"/>
-      <c r="U147" s="13"/>
-      <c r="V147" s="13"/>
-      <c r="W147" s="12"/>
-      <c r="X147" s="12"/>
-      <c r="Y147" s="12"/>
-      <c r="Z147" s="12"/>
-      <c r="AA147" s="12"/>
+      <c r="I147" s="17">
+        <v>1</v>
+      </c>
+      <c r="J147" s="17">
+        <v>2</v>
+      </c>
+      <c r="K147" s="17">
+        <v>8</v>
+      </c>
+      <c r="L147" s="17"/>
+      <c r="M147" s="17"/>
+      <c r="N147" s="18"/>
+      <c r="O147" s="18"/>
+      <c r="P147" s="17"/>
+      <c r="Q147" s="17"/>
+      <c r="R147" s="17"/>
+      <c r="S147" s="17"/>
+      <c r="T147" s="17"/>
+      <c r="U147" s="18"/>
+      <c r="V147" s="18"/>
+      <c r="W147" s="17"/>
+      <c r="X147" s="17"/>
+      <c r="Y147" s="17"/>
+      <c r="Z147" s="17"/>
+      <c r="AA147" s="17"/>
       <c r="AB147" s="13" t="s">
         <v>20</v>
       </c>
@@ -21675,31 +21681,31 @@
       <c r="H148" s="10">
         <v>0.27400000000000002</v>
       </c>
-      <c r="I148" s="12">
-        <v>1</v>
-      </c>
-      <c r="J148" s="12">
-        <v>2</v>
-      </c>
-      <c r="K148" s="12">
-        <v>8</v>
-      </c>
-      <c r="L148" s="12"/>
-      <c r="M148" s="12"/>
-      <c r="N148" s="13"/>
-      <c r="O148" s="13"/>
-      <c r="P148" s="12"/>
-      <c r="Q148" s="12"/>
-      <c r="R148" s="12"/>
-      <c r="S148" s="12"/>
-      <c r="T148" s="12"/>
-      <c r="U148" s="13"/>
-      <c r="V148" s="13"/>
-      <c r="W148" s="12"/>
-      <c r="X148" s="12"/>
-      <c r="Y148" s="12"/>
-      <c r="Z148" s="12"/>
-      <c r="AA148" s="12"/>
+      <c r="I148" s="17">
+        <v>1</v>
+      </c>
+      <c r="J148" s="17">
+        <v>2</v>
+      </c>
+      <c r="K148" s="17">
+        <v>8</v>
+      </c>
+      <c r="L148" s="17"/>
+      <c r="M148" s="17"/>
+      <c r="N148" s="18"/>
+      <c r="O148" s="18"/>
+      <c r="P148" s="17"/>
+      <c r="Q148" s="17"/>
+      <c r="R148" s="17"/>
+      <c r="S148" s="17"/>
+      <c r="T148" s="17"/>
+      <c r="U148" s="18"/>
+      <c r="V148" s="18"/>
+      <c r="W148" s="17"/>
+      <c r="X148" s="17"/>
+      <c r="Y148" s="17"/>
+      <c r="Z148" s="17"/>
+      <c r="AA148" s="17"/>
       <c r="AB148" s="13" t="s">
         <v>513</v>
       </c>
@@ -21735,31 +21741,31 @@
       <c r="H149" s="10">
         <v>0.27500000000000002</v>
       </c>
-      <c r="I149" s="12">
-        <v>1</v>
-      </c>
-      <c r="J149" s="12">
-        <v>2</v>
-      </c>
-      <c r="K149" s="12">
-        <v>8</v>
-      </c>
-      <c r="L149" s="12"/>
-      <c r="M149" s="12"/>
-      <c r="N149" s="13"/>
-      <c r="O149" s="13"/>
-      <c r="P149" s="12"/>
-      <c r="Q149" s="12"/>
-      <c r="R149" s="12"/>
-      <c r="S149" s="12"/>
-      <c r="T149" s="12"/>
-      <c r="U149" s="13"/>
-      <c r="V149" s="13"/>
-      <c r="W149" s="12"/>
-      <c r="X149" s="12"/>
-      <c r="Y149" s="12"/>
-      <c r="Z149" s="12"/>
-      <c r="AA149" s="12"/>
+      <c r="I149" s="17">
+        <v>1</v>
+      </c>
+      <c r="J149" s="17">
+        <v>2</v>
+      </c>
+      <c r="K149" s="17">
+        <v>8</v>
+      </c>
+      <c r="L149" s="17"/>
+      <c r="M149" s="17"/>
+      <c r="N149" s="18"/>
+      <c r="O149" s="18"/>
+      <c r="P149" s="17"/>
+      <c r="Q149" s="17"/>
+      <c r="R149" s="17"/>
+      <c r="S149" s="17"/>
+      <c r="T149" s="17"/>
+      <c r="U149" s="18"/>
+      <c r="V149" s="18"/>
+      <c r="W149" s="17"/>
+      <c r="X149" s="17"/>
+      <c r="Y149" s="17"/>
+      <c r="Z149" s="17"/>
+      <c r="AA149" s="17"/>
       <c r="AB149" s="13" t="s">
         <v>20</v>
       </c>
@@ -21795,31 +21801,31 @@
       <c r="H150" s="10">
         <v>0.30199999999999999</v>
       </c>
-      <c r="I150" s="12">
-        <v>1</v>
-      </c>
-      <c r="J150" s="12">
-        <v>2</v>
-      </c>
-      <c r="K150" s="12">
-        <v>8</v>
-      </c>
-      <c r="L150" s="12"/>
-      <c r="M150" s="12"/>
-      <c r="N150" s="13"/>
-      <c r="O150" s="13"/>
-      <c r="P150" s="12"/>
-      <c r="Q150" s="12"/>
-      <c r="R150" s="12"/>
-      <c r="S150" s="12"/>
-      <c r="T150" s="12"/>
-      <c r="U150" s="13"/>
-      <c r="V150" s="13"/>
-      <c r="W150" s="12"/>
-      <c r="X150" s="12"/>
-      <c r="Y150" s="12"/>
-      <c r="Z150" s="12"/>
-      <c r="AA150" s="12"/>
+      <c r="I150" s="17">
+        <v>1</v>
+      </c>
+      <c r="J150" s="17">
+        <v>2</v>
+      </c>
+      <c r="K150" s="17">
+        <v>8</v>
+      </c>
+      <c r="L150" s="17"/>
+      <c r="M150" s="17"/>
+      <c r="N150" s="18"/>
+      <c r="O150" s="18"/>
+      <c r="P150" s="17"/>
+      <c r="Q150" s="17"/>
+      <c r="R150" s="17"/>
+      <c r="S150" s="17"/>
+      <c r="T150" s="17"/>
+      <c r="U150" s="18"/>
+      <c r="V150" s="18"/>
+      <c r="W150" s="17"/>
+      <c r="X150" s="17"/>
+      <c r="Y150" s="17"/>
+      <c r="Z150" s="17"/>
+      <c r="AA150" s="17"/>
       <c r="AB150" s="13" t="s">
         <v>20</v>
       </c>
@@ -21855,31 +21861,31 @@
       <c r="H151" s="10">
         <v>0.254</v>
       </c>
-      <c r="I151" s="12">
-        <v>1</v>
-      </c>
-      <c r="J151" s="12">
+      <c r="I151" s="17">
+        <v>1</v>
+      </c>
+      <c r="J151" s="17">
         <v>3</v>
       </c>
-      <c r="K151" s="12">
-        <v>8</v>
-      </c>
-      <c r="L151" s="12"/>
-      <c r="M151" s="12"/>
-      <c r="N151" s="13"/>
-      <c r="O151" s="13"/>
-      <c r="P151" s="12"/>
-      <c r="Q151" s="12"/>
-      <c r="R151" s="12"/>
-      <c r="S151" s="12"/>
-      <c r="T151" s="12"/>
-      <c r="U151" s="13"/>
-      <c r="V151" s="13"/>
-      <c r="W151" s="12"/>
-      <c r="X151" s="12"/>
-      <c r="Y151" s="12"/>
-      <c r="Z151" s="12"/>
-      <c r="AA151" s="12"/>
+      <c r="K151" s="17">
+        <v>8</v>
+      </c>
+      <c r="L151" s="17"/>
+      <c r="M151" s="17"/>
+      <c r="N151" s="18"/>
+      <c r="O151" s="18"/>
+      <c r="P151" s="17"/>
+      <c r="Q151" s="17"/>
+      <c r="R151" s="17"/>
+      <c r="S151" s="17"/>
+      <c r="T151" s="17"/>
+      <c r="U151" s="18"/>
+      <c r="V151" s="18"/>
+      <c r="W151" s="17"/>
+      <c r="X151" s="17"/>
+      <c r="Y151" s="17"/>
+      <c r="Z151" s="17"/>
+      <c r="AA151" s="17"/>
       <c r="AB151" s="13" t="s">
         <v>20</v>
       </c>
@@ -21915,31 +21921,31 @@
       <c r="H152" s="10">
         <v>0.254</v>
       </c>
-      <c r="I152" s="12">
-        <v>1</v>
-      </c>
-      <c r="J152" s="12">
+      <c r="I152" s="17">
+        <v>1</v>
+      </c>
+      <c r="J152" s="17">
         <v>3</v>
       </c>
-      <c r="K152" s="12">
-        <v>8</v>
-      </c>
-      <c r="L152" s="12"/>
-      <c r="M152" s="12"/>
-      <c r="N152" s="13"/>
-      <c r="O152" s="13"/>
-      <c r="P152" s="12"/>
-      <c r="Q152" s="12"/>
-      <c r="R152" s="12"/>
-      <c r="S152" s="12"/>
-      <c r="T152" s="12"/>
-      <c r="U152" s="13"/>
-      <c r="V152" s="13"/>
-      <c r="W152" s="12"/>
-      <c r="X152" s="12"/>
-      <c r="Y152" s="12"/>
-      <c r="Z152" s="12"/>
-      <c r="AA152" s="12"/>
+      <c r="K152" s="17">
+        <v>8</v>
+      </c>
+      <c r="L152" s="17"/>
+      <c r="M152" s="17"/>
+      <c r="N152" s="18"/>
+      <c r="O152" s="18"/>
+      <c r="P152" s="17"/>
+      <c r="Q152" s="17"/>
+      <c r="R152" s="17"/>
+      <c r="S152" s="17"/>
+      <c r="T152" s="17"/>
+      <c r="U152" s="18"/>
+      <c r="V152" s="18"/>
+      <c r="W152" s="17"/>
+      <c r="X152" s="17"/>
+      <c r="Y152" s="17"/>
+      <c r="Z152" s="17"/>
+      <c r="AA152" s="17"/>
       <c r="AB152" s="13" t="s">
         <v>20</v>
       </c>
@@ -21975,31 +21981,31 @@
       <c r="H153" s="10">
         <v>0.254</v>
       </c>
-      <c r="I153" s="12">
-        <v>1</v>
-      </c>
-      <c r="J153" s="12">
+      <c r="I153" s="17">
+        <v>1</v>
+      </c>
+      <c r="J153" s="17">
         <v>3</v>
       </c>
-      <c r="K153" s="12">
-        <v>8</v>
-      </c>
-      <c r="L153" s="12"/>
-      <c r="M153" s="12"/>
-      <c r="N153" s="13"/>
-      <c r="O153" s="13"/>
-      <c r="P153" s="12"/>
-      <c r="Q153" s="12"/>
-      <c r="R153" s="12"/>
-      <c r="S153" s="12"/>
-      <c r="T153" s="12"/>
-      <c r="U153" s="13"/>
-      <c r="V153" s="13"/>
-      <c r="W153" s="12"/>
-      <c r="X153" s="12"/>
-      <c r="Y153" s="12"/>
-      <c r="Z153" s="12"/>
-      <c r="AA153" s="12"/>
+      <c r="K153" s="17">
+        <v>8</v>
+      </c>
+      <c r="L153" s="17"/>
+      <c r="M153" s="17"/>
+      <c r="N153" s="18"/>
+      <c r="O153" s="18"/>
+      <c r="P153" s="17"/>
+      <c r="Q153" s="17"/>
+      <c r="R153" s="17"/>
+      <c r="S153" s="17"/>
+      <c r="T153" s="17"/>
+      <c r="U153" s="18"/>
+      <c r="V153" s="18"/>
+      <c r="W153" s="17"/>
+      <c r="X153" s="17"/>
+      <c r="Y153" s="17"/>
+      <c r="Z153" s="17"/>
+      <c r="AA153" s="17"/>
       <c r="AB153" s="13" t="s">
         <v>20</v>
       </c>
@@ -22035,31 +22041,31 @@
       <c r="H154" s="10">
         <v>0.254</v>
       </c>
-      <c r="I154" s="12">
-        <v>1</v>
-      </c>
-      <c r="J154" s="12">
+      <c r="I154" s="17">
+        <v>1</v>
+      </c>
+      <c r="J154" s="17">
         <v>3</v>
       </c>
-      <c r="K154" s="12">
-        <v>8</v>
-      </c>
-      <c r="L154" s="12"/>
-      <c r="M154" s="12"/>
-      <c r="N154" s="13"/>
-      <c r="O154" s="13"/>
-      <c r="P154" s="12"/>
-      <c r="Q154" s="12"/>
-      <c r="R154" s="12"/>
-      <c r="S154" s="12"/>
-      <c r="T154" s="12"/>
-      <c r="U154" s="13"/>
-      <c r="V154" s="13"/>
-      <c r="W154" s="12"/>
-      <c r="X154" s="12"/>
-      <c r="Y154" s="12"/>
-      <c r="Z154" s="12"/>
-      <c r="AA154" s="12"/>
+      <c r="K154" s="17">
+        <v>8</v>
+      </c>
+      <c r="L154" s="17"/>
+      <c r="M154" s="17"/>
+      <c r="N154" s="18"/>
+      <c r="O154" s="18"/>
+      <c r="P154" s="17"/>
+      <c r="Q154" s="17"/>
+      <c r="R154" s="17"/>
+      <c r="S154" s="17"/>
+      <c r="T154" s="17"/>
+      <c r="U154" s="18"/>
+      <c r="V154" s="18"/>
+      <c r="W154" s="17"/>
+      <c r="X154" s="17"/>
+      <c r="Y154" s="17"/>
+      <c r="Z154" s="17"/>
+      <c r="AA154" s="17"/>
       <c r="AB154" s="13" t="s">
         <v>20</v>
       </c>
@@ -22095,31 +22101,31 @@
       <c r="H155" s="10">
         <v>0.27500000000000002</v>
       </c>
-      <c r="I155" s="12">
-        <v>1</v>
-      </c>
-      <c r="J155" s="12">
+      <c r="I155" s="17">
+        <v>1</v>
+      </c>
+      <c r="J155" s="17">
         <v>3</v>
       </c>
-      <c r="K155" s="12">
-        <v>8</v>
-      </c>
-      <c r="L155" s="12"/>
-      <c r="M155" s="12"/>
-      <c r="N155" s="13"/>
-      <c r="O155" s="13"/>
-      <c r="P155" s="12"/>
-      <c r="Q155" s="12"/>
-      <c r="R155" s="12"/>
-      <c r="S155" s="12"/>
-      <c r="T155" s="12"/>
-      <c r="U155" s="13"/>
-      <c r="V155" s="13"/>
-      <c r="W155" s="12"/>
-      <c r="X155" s="12"/>
-      <c r="Y155" s="12"/>
-      <c r="Z155" s="12"/>
-      <c r="AA155" s="12"/>
+      <c r="K155" s="17">
+        <v>8</v>
+      </c>
+      <c r="L155" s="17"/>
+      <c r="M155" s="17"/>
+      <c r="N155" s="18"/>
+      <c r="O155" s="18"/>
+      <c r="P155" s="17"/>
+      <c r="Q155" s="17"/>
+      <c r="R155" s="17"/>
+      <c r="S155" s="17"/>
+      <c r="T155" s="17"/>
+      <c r="U155" s="18"/>
+      <c r="V155" s="18"/>
+      <c r="W155" s="17"/>
+      <c r="X155" s="17"/>
+      <c r="Y155" s="17"/>
+      <c r="Z155" s="17"/>
+      <c r="AA155" s="17"/>
       <c r="AB155" s="13" t="s">
         <v>20</v>
       </c>
@@ -22155,31 +22161,31 @@
       <c r="H156" s="10">
         <v>0.254</v>
       </c>
-      <c r="I156" s="12">
-        <v>1</v>
-      </c>
-      <c r="J156" s="12">
+      <c r="I156" s="17">
+        <v>1</v>
+      </c>
+      <c r="J156" s="17">
         <v>5</v>
       </c>
-      <c r="K156" s="12">
-        <v>8</v>
-      </c>
-      <c r="L156" s="12"/>
-      <c r="M156" s="12"/>
-      <c r="N156" s="13"/>
-      <c r="O156" s="13"/>
-      <c r="P156" s="12"/>
-      <c r="Q156" s="12"/>
-      <c r="R156" s="12"/>
-      <c r="S156" s="12"/>
-      <c r="T156" s="12"/>
-      <c r="U156" s="13"/>
-      <c r="V156" s="13"/>
-      <c r="W156" s="12"/>
-      <c r="X156" s="12"/>
-      <c r="Y156" s="12"/>
-      <c r="Z156" s="12"/>
-      <c r="AA156" s="12"/>
+      <c r="K156" s="17">
+        <v>8</v>
+      </c>
+      <c r="L156" s="17"/>
+      <c r="M156" s="17"/>
+      <c r="N156" s="18"/>
+      <c r="O156" s="18"/>
+      <c r="P156" s="17"/>
+      <c r="Q156" s="17"/>
+      <c r="R156" s="17"/>
+      <c r="S156" s="17"/>
+      <c r="T156" s="17"/>
+      <c r="U156" s="18"/>
+      <c r="V156" s="18"/>
+      <c r="W156" s="17"/>
+      <c r="X156" s="17"/>
+      <c r="Y156" s="17"/>
+      <c r="Z156" s="17"/>
+      <c r="AA156" s="17"/>
       <c r="AB156" s="13" t="s">
         <v>20</v>
       </c>
@@ -22215,31 +22221,31 @@
       <c r="H157" s="10">
         <v>0.254</v>
       </c>
-      <c r="I157" s="12">
-        <v>1</v>
-      </c>
-      <c r="J157" s="12">
+      <c r="I157" s="17">
+        <v>1</v>
+      </c>
+      <c r="J157" s="17">
         <v>5</v>
       </c>
-      <c r="K157" s="12">
-        <v>8</v>
-      </c>
-      <c r="L157" s="12"/>
-      <c r="M157" s="12"/>
-      <c r="N157" s="13"/>
-      <c r="O157" s="13"/>
-      <c r="P157" s="12"/>
-      <c r="Q157" s="12"/>
-      <c r="R157" s="12"/>
-      <c r="S157" s="12"/>
-      <c r="T157" s="12"/>
-      <c r="U157" s="13"/>
-      <c r="V157" s="13"/>
-      <c r="W157" s="12"/>
-      <c r="X157" s="12"/>
-      <c r="Y157" s="12"/>
-      <c r="Z157" s="12"/>
-      <c r="AA157" s="12"/>
+      <c r="K157" s="17">
+        <v>8</v>
+      </c>
+      <c r="L157" s="17"/>
+      <c r="M157" s="17"/>
+      <c r="N157" s="18"/>
+      <c r="O157" s="18"/>
+      <c r="P157" s="17"/>
+      <c r="Q157" s="17"/>
+      <c r="R157" s="17"/>
+      <c r="S157" s="17"/>
+      <c r="T157" s="17"/>
+      <c r="U157" s="18"/>
+      <c r="V157" s="18"/>
+      <c r="W157" s="17"/>
+      <c r="X157" s="17"/>
+      <c r="Y157" s="17"/>
+      <c r="Z157" s="17"/>
+      <c r="AA157" s="17"/>
       <c r="AB157" s="13" t="s">
         <v>20</v>
       </c>
@@ -22275,31 +22281,31 @@
       <c r="H158" s="10">
         <v>0.254</v>
       </c>
-      <c r="I158" s="12">
-        <v>1</v>
-      </c>
-      <c r="J158" s="12">
+      <c r="I158" s="17">
+        <v>1</v>
+      </c>
+      <c r="J158" s="17">
         <v>5</v>
       </c>
-      <c r="K158" s="12">
-        <v>8</v>
-      </c>
-      <c r="L158" s="12"/>
-      <c r="M158" s="12"/>
-      <c r="N158" s="13"/>
-      <c r="O158" s="13"/>
-      <c r="P158" s="12"/>
-      <c r="Q158" s="12"/>
-      <c r="R158" s="12"/>
-      <c r="S158" s="12"/>
-      <c r="T158" s="12"/>
-      <c r="U158" s="13"/>
-      <c r="V158" s="13"/>
-      <c r="W158" s="12"/>
-      <c r="X158" s="12"/>
-      <c r="Y158" s="12"/>
-      <c r="Z158" s="12"/>
-      <c r="AA158" s="12"/>
+      <c r="K158" s="17">
+        <v>8</v>
+      </c>
+      <c r="L158" s="17"/>
+      <c r="M158" s="17"/>
+      <c r="N158" s="18"/>
+      <c r="O158" s="18"/>
+      <c r="P158" s="17"/>
+      <c r="Q158" s="17"/>
+      <c r="R158" s="17"/>
+      <c r="S158" s="17"/>
+      <c r="T158" s="17"/>
+      <c r="U158" s="18"/>
+      <c r="V158" s="18"/>
+      <c r="W158" s="17"/>
+      <c r="X158" s="17"/>
+      <c r="Y158" s="17"/>
+      <c r="Z158" s="17"/>
+      <c r="AA158" s="17"/>
       <c r="AB158" s="13" t="s">
         <v>20</v>
       </c>
@@ -22335,31 +22341,31 @@
       <c r="H159" s="10">
         <v>0.254</v>
       </c>
-      <c r="I159" s="12">
-        <v>1</v>
-      </c>
-      <c r="J159" s="12">
+      <c r="I159" s="17">
+        <v>1</v>
+      </c>
+      <c r="J159" s="17">
         <v>6</v>
       </c>
-      <c r="K159" s="12">
-        <v>8</v>
-      </c>
-      <c r="L159" s="12"/>
-      <c r="M159" s="12"/>
-      <c r="N159" s="13"/>
-      <c r="O159" s="13"/>
-      <c r="P159" s="12"/>
-      <c r="Q159" s="12"/>
-      <c r="R159" s="12"/>
-      <c r="S159" s="12"/>
-      <c r="T159" s="12"/>
-      <c r="U159" s="13"/>
-      <c r="V159" s="13"/>
-      <c r="W159" s="12"/>
-      <c r="X159" s="12"/>
-      <c r="Y159" s="12"/>
-      <c r="Z159" s="12"/>
-      <c r="AA159" s="12"/>
+      <c r="K159" s="17">
+        <v>8</v>
+      </c>
+      <c r="L159" s="17"/>
+      <c r="M159" s="17"/>
+      <c r="N159" s="18"/>
+      <c r="O159" s="18"/>
+      <c r="P159" s="17"/>
+      <c r="Q159" s="17"/>
+      <c r="R159" s="17"/>
+      <c r="S159" s="17"/>
+      <c r="T159" s="17"/>
+      <c r="U159" s="18"/>
+      <c r="V159" s="18"/>
+      <c r="W159" s="17"/>
+      <c r="X159" s="17"/>
+      <c r="Y159" s="17"/>
+      <c r="Z159" s="17"/>
+      <c r="AA159" s="17"/>
       <c r="AB159" s="13" t="s">
         <v>20</v>
       </c>
@@ -22395,31 +22401,31 @@
       <c r="H160" s="10">
         <v>0.30199999999999999</v>
       </c>
-      <c r="I160" s="12">
-        <v>1</v>
-      </c>
-      <c r="J160" s="12">
+      <c r="I160" s="17">
+        <v>1</v>
+      </c>
+      <c r="J160" s="17">
         <v>6</v>
       </c>
-      <c r="K160" s="12">
-        <v>8</v>
-      </c>
-      <c r="L160" s="12"/>
-      <c r="M160" s="12"/>
-      <c r="N160" s="13"/>
-      <c r="O160" s="13"/>
-      <c r="P160" s="12"/>
-      <c r="Q160" s="12"/>
-      <c r="R160" s="12"/>
-      <c r="S160" s="12"/>
-      <c r="T160" s="12"/>
-      <c r="U160" s="13"/>
-      <c r="V160" s="13"/>
-      <c r="W160" s="12"/>
-      <c r="X160" s="12"/>
-      <c r="Y160" s="12"/>
-      <c r="Z160" s="12"/>
-      <c r="AA160" s="12"/>
+      <c r="K160" s="17">
+        <v>8</v>
+      </c>
+      <c r="L160" s="17"/>
+      <c r="M160" s="17"/>
+      <c r="N160" s="18"/>
+      <c r="O160" s="18"/>
+      <c r="P160" s="17"/>
+      <c r="Q160" s="17"/>
+      <c r="R160" s="17"/>
+      <c r="S160" s="17"/>
+      <c r="T160" s="17"/>
+      <c r="U160" s="18"/>
+      <c r="V160" s="18"/>
+      <c r="W160" s="17"/>
+      <c r="X160" s="17"/>
+      <c r="Y160" s="17"/>
+      <c r="Z160" s="17"/>
+      <c r="AA160" s="17"/>
       <c r="AB160" s="13" t="s">
         <v>20</v>
       </c>
@@ -22455,31 +22461,31 @@
       <c r="H161" s="10">
         <v>0.32700000000000001</v>
       </c>
-      <c r="I161" s="12">
-        <v>1</v>
-      </c>
-      <c r="J161" s="12">
-        <v>8</v>
-      </c>
-      <c r="K161" s="12">
-        <v>8</v>
-      </c>
-      <c r="L161" s="12"/>
-      <c r="M161" s="12"/>
-      <c r="N161" s="13"/>
-      <c r="O161" s="13"/>
-      <c r="P161" s="12"/>
-      <c r="Q161" s="12"/>
-      <c r="R161" s="12"/>
-      <c r="S161" s="12"/>
-      <c r="T161" s="12"/>
-      <c r="U161" s="13"/>
-      <c r="V161" s="13"/>
-      <c r="W161" s="12"/>
-      <c r="X161" s="12"/>
-      <c r="Y161" s="12"/>
-      <c r="Z161" s="12"/>
-      <c r="AA161" s="12"/>
+      <c r="I161" s="17">
+        <v>1</v>
+      </c>
+      <c r="J161" s="17">
+        <v>8</v>
+      </c>
+      <c r="K161" s="17">
+        <v>8</v>
+      </c>
+      <c r="L161" s="17"/>
+      <c r="M161" s="17"/>
+      <c r="N161" s="18"/>
+      <c r="O161" s="18"/>
+      <c r="P161" s="17"/>
+      <c r="Q161" s="17"/>
+      <c r="R161" s="17"/>
+      <c r="S161" s="17"/>
+      <c r="T161" s="17"/>
+      <c r="U161" s="18"/>
+      <c r="V161" s="18"/>
+      <c r="W161" s="17"/>
+      <c r="X161" s="17"/>
+      <c r="Y161" s="17"/>
+      <c r="Z161" s="17"/>
+      <c r="AA161" s="17"/>
       <c r="AB161" s="13" t="s">
         <v>20</v>
       </c>
@@ -22515,31 +22521,31 @@
       <c r="H162" s="10">
         <v>0.30199999999999999</v>
       </c>
-      <c r="I162" s="12">
-        <v>1</v>
-      </c>
-      <c r="J162" s="12">
-        <v>1</v>
-      </c>
-      <c r="K162" s="12">
-        <v>8</v>
-      </c>
-      <c r="L162" s="12"/>
-      <c r="M162" s="12"/>
-      <c r="N162" s="13"/>
-      <c r="O162" s="13"/>
-      <c r="P162" s="12"/>
-      <c r="Q162" s="12"/>
-      <c r="R162" s="12"/>
-      <c r="S162" s="12"/>
-      <c r="T162" s="12"/>
-      <c r="U162" s="13"/>
-      <c r="V162" s="13"/>
-      <c r="W162" s="12"/>
-      <c r="X162" s="12"/>
-      <c r="Y162" s="12"/>
-      <c r="Z162" s="12"/>
-      <c r="AA162" s="12"/>
+      <c r="I162" s="17">
+        <v>1</v>
+      </c>
+      <c r="J162" s="17">
+        <v>1</v>
+      </c>
+      <c r="K162" s="17">
+        <v>8</v>
+      </c>
+      <c r="L162" s="17"/>
+      <c r="M162" s="17"/>
+      <c r="N162" s="18"/>
+      <c r="O162" s="18"/>
+      <c r="P162" s="17"/>
+      <c r="Q162" s="17"/>
+      <c r="R162" s="17"/>
+      <c r="S162" s="17"/>
+      <c r="T162" s="17"/>
+      <c r="U162" s="18"/>
+      <c r="V162" s="18"/>
+      <c r="W162" s="17"/>
+      <c r="X162" s="17"/>
+      <c r="Y162" s="17"/>
+      <c r="Z162" s="17"/>
+      <c r="AA162" s="17"/>
       <c r="AB162" s="13" t="s">
         <v>20</v>
       </c>

--- a/excel/Заказы.xlsx
+++ b/excel/Заказы.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
-    <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -22563,13 +22562,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>